--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78728</v>
+        <v>79593</v>
       </c>
       <c r="F2" t="n">
-        <v>1580114526097</v>
+        <v>1598364983123</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>37255171517</v>
+        <v>34113961073</v>
       </c>
       <c r="I2" t="n">
-        <v>79432</v>
+        <v>79701</v>
       </c>
       <c r="J2" t="n">
-        <v>77666</v>
+        <v>77888</v>
       </c>
       <c r="K2" t="n">
-        <v>-653.9158031940315</v>
+        <v>1519.73</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8226599999999999</v>
+        <v>1.94656</v>
       </c>
       <c r="M2" t="n">
-        <v>20081584</v>
+        <v>20081850</v>
       </c>
       <c r="N2" t="n">
-        <v>20081628</v>
+        <v>20081881</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2492.64</v>
+        <v>2515.98</v>
       </c>
       <c r="F3" t="n">
-        <v>304020077819</v>
+        <v>307031455725</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11910258184</v>
+        <v>12320334940</v>
       </c>
       <c r="I3" t="n">
-        <v>2505.13</v>
+        <v>2521.51</v>
       </c>
       <c r="J3" t="n">
-        <v>2442.98</v>
+        <v>2457.39</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.542264194355084</v>
+        <v>61.6</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3947</v>
+        <v>2.50979</v>
       </c>
       <c r="M3" t="n">
-        <v>122029704.5242925</v>
+        <v>122032627.1379582</v>
       </c>
       <c r="N3" t="n">
-        <v>122029704.5242924</v>
+        <v>122032627.1379582</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1921100701627806</v>
+        <v>0.1917993586821735</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999915</v>
+        <v>0.999827</v>
       </c>
       <c r="F4" t="n">
-        <v>183444550357</v>
+        <v>183428486563</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>58169765758</v>
+        <v>52915294657</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9998860000000001</v>
+        <v>0.999995</v>
       </c>
       <c r="J4" t="n">
-        <v>0.99953</v>
+        <v>0.99956</v>
       </c>
       <c r="K4" t="n">
-        <v>7.423999999999999e-05</v>
+        <v>0.0002526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00878</v>
+        <v>0.02527</v>
       </c>
       <c r="M4" t="n">
         <v>183460193480.142</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1157742201378774</v>
+        <v>0.1144405688528694</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>750.9400000000001</v>
+        <v>750.04</v>
       </c>
       <c r="F5" t="n">
-        <v>99978566028</v>
+        <v>99876830887</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1257917913</v>
+        <v>923039010</v>
       </c>
       <c r="I5" t="n">
-        <v>760.33</v>
+        <v>757.36</v>
       </c>
       <c r="J5" t="n">
-        <v>737.14</v>
+        <v>746.05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.81</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>1.19041</v>
+        <v>0.38481</v>
       </c>
       <c r="M5" t="n">
-        <v>133161436.94</v>
+        <v>133161358.02</v>
       </c>
       <c r="N5" t="n">
-        <v>133161433.13</v>
+        <v>133161354.33</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0629322629345183</v>
+        <v>0.06214850002029332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="F6" t="n">
-        <v>88631923759</v>
+        <v>90039637527</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2420690203</v>
+        <v>2699115770</v>
       </c>
       <c r="I6" t="n">
         <v>1.45</v>
       </c>
       <c r="J6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008915569999999999</v>
+        <v>0.04390142</v>
       </c>
       <c r="L6" t="n">
-        <v>0.61812</v>
+        <v>3.15584</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05574875231039448</v>
+        <v>0.0559917436024999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.999918</v>
       </c>
       <c r="F7" t="n">
-        <v>74510066780</v>
+        <v>74323444836</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>15182410888</v>
+        <v>14970939745</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999715</v>
+        <v>0.99979</v>
       </c>
       <c r="K7" t="n">
-        <v>9.574e-05</v>
+        <v>0.00010693</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01075</v>
+        <v>0.0107</v>
       </c>
       <c r="M7" t="n">
-        <v>74510139001.71434</v>
+        <v>74329561446.62111</v>
       </c>
       <c r="N7" t="n">
-        <v>74506121772.26845</v>
+        <v>74328339343.75978</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04680826513929905</v>
+        <v>0.04615552643439572</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103.55</v>
+        <v>104.41</v>
       </c>
       <c r="F8" t="n">
-        <v>60664095976</v>
+        <v>61211194221</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2996420083</v>
+        <v>2888831094</v>
       </c>
       <c r="I8" t="n">
-        <v>104.71</v>
+        <v>105.02</v>
       </c>
       <c r="J8" t="n">
-        <v>101.79</v>
+        <v>102.47</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.716759083677232</v>
+        <v>2.02</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.69877</v>
+        <v>1.97109</v>
       </c>
       <c r="M8" t="n">
-        <v>586250953.6924145</v>
+        <v>586250495.4491609</v>
       </c>
       <c r="N8" t="n">
-        <v>633737181.8916483</v>
+        <v>633736725.8982507</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03804244032400697</v>
+        <v>0.03794902584309118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338909</v>
+        <v>0.338701</v>
       </c>
       <c r="F9" t="n">
-        <v>32171779577</v>
+        <v>32156956766</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>389915756</v>
+        <v>332831706</v>
       </c>
       <c r="I9" t="n">
         <v>0.339911</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334612</v>
+        <v>0.337749</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00435562</v>
+        <v>-7.553672881799301e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28692</v>
+        <v>-0.0223</v>
       </c>
       <c r="M9" t="n">
-        <v>94940716339.51509</v>
+        <v>94942033418.39418</v>
       </c>
       <c r="N9" t="n">
-        <v>94941426383.73468</v>
+        <v>94942027879.98538</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02000407684115503</v>
+        <v>0.01976499139658666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1078,13 +1078,13 @@
         <v>1.035</v>
       </c>
       <c r="F10" t="n">
-        <v>23072109188</v>
+        <v>23070630036</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>34091424</v>
+        <v>34613377</v>
       </c>
       <c r="I10" t="n">
         <v>1.051</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01424311449073386</v>
+        <v>0.01407817622869863</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1180.3</v>
+        <v>1280.44</v>
       </c>
       <c r="F11" t="n">
-        <v>19967222607</v>
+        <v>21667506605</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>987804462</v>
+        <v>1394137200</v>
       </c>
       <c r="I11" t="n">
-        <v>1210.35</v>
+        <v>1275.68</v>
       </c>
       <c r="J11" t="n">
-        <v>1117.97</v>
+        <v>1144.42</v>
       </c>
       <c r="K11" t="n">
-        <v>34.76</v>
+        <v>132.62</v>
       </c>
       <c r="L11" t="n">
-        <v>2.96045</v>
+        <v>11.55438</v>
       </c>
       <c r="M11" t="n">
         <v>16921867.3530448</v>
       </c>
       <c r="N11" t="n">
-        <v>16922134.5405448</v>
+        <v>16923028.2905448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01227742409417933</v>
+        <v>0.01320001018350405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>85.58</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>19030923082</v>
+        <v>19250478039</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1050051372</v>
+        <v>1058509523</v>
       </c>
       <c r="I12" t="n">
-        <v>85.8</v>
+        <v>86.98</v>
       </c>
       <c r="J12" t="n">
-        <v>81.66</v>
+        <v>82.44</v>
       </c>
       <c r="K12" t="n">
-        <v>0.321021</v>
+        <v>4.04</v>
       </c>
       <c r="L12" t="n">
-        <v>0.33886</v>
+        <v>4.89902</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01168465687496635</v>
+        <v>0.01168727625715673</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09009399999999999</v>
+        <v>0.091074</v>
       </c>
       <c r="F13" t="n">
-        <v>14017221157</v>
+        <v>14193446782</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>872758169</v>
+        <v>811744469</v>
       </c>
       <c r="I13" t="n">
-        <v>0.091417</v>
+        <v>0.091515</v>
       </c>
       <c r="J13" t="n">
-        <v>0.088076</v>
+        <v>0.089</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001347749905187684</v>
+        <v>0.00247604</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.46593</v>
+        <v>2.79468</v>
       </c>
       <c r="M13" t="n">
-        <v>155835036383.7053</v>
+        <v>155844386383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171549433126.579</v>
+        <v>155844716383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008510503659364737</v>
+        <v>0.008522256672087119</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01614377</v>
+        <v>0.01638259</v>
       </c>
       <c r="F14" t="n">
-        <v>11443659114</v>
+        <v>11618735510</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>21214532</v>
+        <v>39125793</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01702228</v>
+        <v>0.01675249</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01614836</v>
+        <v>0.01591912</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000189746977732479</v>
+        <v>-0.000182873056705439</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.17884</v>
+        <v>-1.10394</v>
       </c>
       <c r="M14" t="n">
-        <v>709209721455.2999</v>
+        <v>709212380117.7289</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408530745.808</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O14" t="n">
         <v>0.01946402</v>
@@ -1379,19 +1379,19 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006881192552215361</v>
+        <v>0.006910834636579719</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.999939</v>
       </c>
       <c r="F15" t="n">
-        <v>9843016686</v>
+        <v>9847281876</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>207540681</v>
+        <v>226871382</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999617</v>
+        <v>0.999628</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00027099</v>
+        <v>0.00022649</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01853</v>
+        <v>0.02266</v>
       </c>
       <c r="M15" t="n">
-        <v>9842539599.706585</v>
+        <v>9847882071.139385</v>
       </c>
       <c r="N15" t="n">
-        <v>9840532124.231136</v>
+        <v>9851780066.236448</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1446,19 +1446,19 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005867832686418278</v>
+        <v>0.005802143556631993</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,28 +1477,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>81.55</v>
+        <v>82.25</v>
       </c>
       <c r="F16" t="n">
-        <v>9609492977</v>
+        <v>9699044618</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>117604843</v>
+        <v>99572519</v>
       </c>
       <c r="I16" t="n">
         <v>82.52</v>
       </c>
       <c r="J16" t="n">
-        <v>75.77</v>
+        <v>79.16</v>
       </c>
       <c r="K16" t="n">
-        <v>4.69</v>
+        <v>2.97</v>
       </c>
       <c r="L16" t="n">
-        <v>6.09555</v>
+        <v>3.74938</v>
       </c>
       <c r="M16" t="n">
         <v>117919967</v>
@@ -1513,153 +1513,153 @@
         <v>46274.03356481482</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0057199898264059</v>
+        <v>0.005709367024124392</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.47</v>
+        <v>498.98</v>
       </c>
       <c r="F17" t="n">
-        <v>9328126456</v>
+        <v>9382098083</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>4292075727</v>
+        <v>115458264</v>
       </c>
       <c r="I17" t="n">
-        <v>12.8</v>
+        <v>507.62</v>
       </c>
       <c r="J17" t="n">
-        <v>12.35</v>
+        <v>491.57</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.330752862079791</v>
+        <v>1.62</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.57113</v>
+        <v>0.32548</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>18802391.73259455</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>18802409.73255417</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>797.73</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>44325.67635416667</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005541857887021651</v>
+        <v>0.005511001236033525</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>496.04</v>
+        <v>12.19</v>
       </c>
       <c r="F18" t="n">
-        <v>9314681900</v>
+        <v>9120564871</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>128601904</v>
+        <v>7088637519</v>
       </c>
       <c r="I18" t="n">
-        <v>525.33</v>
+        <v>12.77</v>
       </c>
       <c r="J18" t="n">
-        <v>493.99</v>
+        <v>11.98</v>
       </c>
       <c r="K18" t="n">
-        <v>-24.21691491878403</v>
+        <v>-0.2184760733722584</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.65139</v>
+        <v>-1.76047</v>
       </c>
       <c r="M18" t="n">
-        <v>18802139.13640226</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N18" t="n">
-        <v>18802170.33633693</v>
+        <v>1000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>797.73</v>
+        <v>52.7</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005533346196199558</v>
+        <v>0.005347316715203172</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.210000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="F19" t="n">
-        <v>8474228006</v>
+        <v>8456838824</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>136526</v>
+        <v>163052</v>
       </c>
       <c r="I19" t="n">
-        <v>9.27</v>
+        <v>9.26</v>
       </c>
       <c r="J19" t="n">
-        <v>9.16</v>
+        <v>9.17</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01405112</v>
+        <v>0.01153524</v>
       </c>
       <c r="L19" t="n">
-        <v>0.18388</v>
+        <v>0.12563</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.005001258435476726</v>
+        <v>0.004931913718639129</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.218716</v>
+        <v>0.220656</v>
       </c>
       <c r="F20" t="n">
-        <v>8194134616</v>
+        <v>8276912044</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>565945088</v>
+        <v>578223441</v>
       </c>
       <c r="I20" t="n">
         <v>0.231823</v>
       </c>
       <c r="J20" t="n">
-        <v>0.215202</v>
+        <v>0.216151</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.003596835227794026</v>
+        <v>0.00384314</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.64603</v>
+        <v>1.77256</v>
       </c>
       <c r="M20" t="n">
         <v>37510482444.2993</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004823932509875903</v>
+        <v>0.004819303818949416</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.18795</v>
+        <v>0.189212</v>
       </c>
       <c r="F21" t="n">
-        <v>6533504983</v>
+        <v>6585243621</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>185787384</v>
+        <v>168338211</v>
       </c>
       <c r="I21" t="n">
         <v>0.19354</v>
       </c>
       <c r="J21" t="n">
-        <v>0.186398</v>
+        <v>0.186697</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.006222802604615635</v>
+        <v>0.00201514</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.32049</v>
+        <v>1.07648</v>
       </c>
       <c r="M21" t="n">
-        <v>34803517247.06119</v>
+        <v>34803513020.29381</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003772595001511706</v>
+        <v>0.003760547521402802</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>257.47</v>
+        <v>259.77</v>
       </c>
       <c r="F22" t="n">
-        <v>5167347357</v>
+        <v>5217902214</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>168047904</v>
+        <v>149663820</v>
       </c>
       <c r="I22" t="n">
-        <v>262.01</v>
+        <v>261.18</v>
       </c>
       <c r="J22" t="n">
-        <v>251.88</v>
+        <v>253.89</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.423866921009051</v>
+        <v>6.49</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.81854</v>
+        <v>2.56148</v>
       </c>
       <c r="M22" t="n">
-        <v>20086506.14665078</v>
+        <v>20086790.52165078</v>
       </c>
       <c r="N22" t="n">
-        <v>20086818.64665078</v>
+        <v>20086793.64665078</v>
       </c>
       <c r="O22" t="n">
         <v>3785.82</v>
@@ -1915,19 +1915,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002907686459589049</v>
+        <v>0.002904776197735139</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,34 +1946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.999844</v>
+        <v>0.999972</v>
       </c>
       <c r="F23" t="n">
-        <v>4580555872</v>
+        <v>4586719903</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>312320539</v>
+        <v>286655800</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.999714</v>
+        <v>0.999723</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.5139892696212e-05</v>
+        <v>0.00011842</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.00218</v>
+        <v>0.01184</v>
       </c>
       <c r="M23" t="n">
-        <v>4580856279.437166</v>
+        <v>4586849364.832944</v>
       </c>
       <c r="N23" t="n">
-        <v>4588997168.727947</v>
+        <v>4586849364.832944</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -1982,19 +1982,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002536191283596831</v>
+        <v>0.002509741191119498</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9998629999999999</v>
+        <v>0.99977</v>
       </c>
       <c r="F24" t="n">
-        <v>4436402611</v>
+        <v>4455091671</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>81570755</v>
+        <v>94194190</v>
       </c>
       <c r="I24" t="n">
-        <v>0.999889</v>
+        <v>0.9999479999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999517</v>
+        <v>0.999565</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00016364</v>
+        <v>0.00019246</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0189</v>
+        <v>0.01925</v>
       </c>
       <c r="M24" t="n">
-        <v>4436863873.39806</v>
+        <v>4456117739.295266</v>
       </c>
       <c r="N24" t="n">
-        <v>4436863873.39806</v>
+        <v>4456117739.295266</v>
       </c>
       <c r="O24" t="n">
         <v>1.034</v>
@@ -2049,19 +2049,19 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002444928471449774</v>
+        <v>0.002427359669025598</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,28 +2080,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999649</v>
+        <v>0.9994729999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>4278383815</v>
+        <v>4277793603</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1145226458</v>
+        <v>1033051569</v>
       </c>
       <c r="I25" t="n">
         <v>0.999799</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999411</v>
+        <v>0.999325</v>
       </c>
       <c r="K25" t="n">
-        <v>8.27e-06</v>
+        <v>-3.5995687306056e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.00412</v>
+        <v>-0.0036</v>
       </c>
       <c r="M25" t="n">
         <v>4280049884.324213</v>
@@ -2116,86 +2116,86 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.00234488744847873</v>
+        <v>0.002316394988544683</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>litecoin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>ltc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.108052</v>
+        <v>54.42</v>
       </c>
       <c r="F26" t="n">
-        <v>4269822447</v>
+        <v>4222703386</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>10101704</v>
+        <v>306495719</v>
       </c>
       <c r="I26" t="n">
-        <v>0.108969</v>
+        <v>55.2</v>
       </c>
       <c r="J26" t="n">
-        <v>0.102222</v>
+        <v>53.64</v>
       </c>
       <c r="K26" t="n">
-        <v>0.00127763</v>
+        <v>-0.518672100140158</v>
       </c>
       <c r="L26" t="n">
-        <v>1.1987</v>
+        <v>-0.94401</v>
       </c>
       <c r="M26" t="n">
-        <v>39554580581.89284</v>
+        <v>77587829.33440471</v>
       </c>
       <c r="N26" t="n">
-        <v>39555502891.265</v>
+        <v>77591373.09434305</v>
       </c>
       <c r="O26" t="n">
-        <v>0.194152</v>
+        <v>410.26</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002339467283065297</v>
+        <v>0.002281915942066697</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,28 +2214,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.76</v>
+        <v>6.72</v>
       </c>
       <c r="F27" t="n">
-        <v>4208825810</v>
+        <v>4185898770</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>580940669</v>
+        <v>523424543</v>
       </c>
       <c r="I27" t="n">
-        <v>7.19</v>
+        <v>6.95</v>
       </c>
       <c r="J27" t="n">
-        <v>6.69</v>
+        <v>6.58</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.2948263907502815</v>
+        <v>-0.1994994738542051</v>
       </c>
       <c r="L27" t="n">
-        <v>-4.37165</v>
+        <v>-2.88455</v>
       </c>
       <c r="M27" t="n">
         <v>623212423.7271129</v>
@@ -2250,86 +2250,86 @@
         <v>44318.89240740741</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002300850573422265</v>
+        <v>0.002258881215852631</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>litecoin</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ltc</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>54.24</v>
+        <v>0.105232</v>
       </c>
       <c r="F28" t="n">
-        <v>4204228691</v>
+        <v>4162833873</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>323072841</v>
+        <v>10056275</v>
       </c>
       <c r="I28" t="n">
-        <v>56.17</v>
+        <v>0.110029</v>
       </c>
       <c r="J28" t="n">
-        <v>53.92</v>
+        <v>0.103497</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.486252265844605</v>
+        <v>0.00191148</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.70348</v>
+        <v>1.85004</v>
       </c>
       <c r="M28" t="n">
-        <v>77586791.83350699</v>
+        <v>39558504215.70418</v>
       </c>
       <c r="N28" t="n">
-        <v>77589485.59046412</v>
+        <v>39559086607.84083</v>
       </c>
       <c r="O28" t="n">
-        <v>410.26</v>
+        <v>0.194152</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>44325.80077546297</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002297940157072304</v>
+        <v>0.002244445700819663</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2348,16 +2348,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="F29" t="n">
-        <v>3882443562</v>
+        <v>3890349973</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>30032376</v>
+        <v>34199995</v>
       </c>
       <c r="I29" t="n">
         <v>1.41</v>
@@ -2366,16 +2366,16 @@
         <v>1.38</v>
       </c>
       <c r="K29" t="n">
-        <v>0.00198856</v>
+        <v>0.01213058</v>
       </c>
       <c r="L29" t="n">
-        <v>0.13204</v>
+        <v>0.87608</v>
       </c>
       <c r="M29" t="n">
-        <v>2784936271.4066</v>
+        <v>2785233859.772825</v>
       </c>
       <c r="N29" t="n">
-        <v>5245781451.720988</v>
+        <v>5246090978.585007</v>
       </c>
       <c r="O29" t="n">
         <v>8.25</v>
@@ -2384,19 +2384,19 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002094219370071562</v>
+        <v>0.002073907526090689</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,31 +2415,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.078864</v>
+        <v>0.07893600000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>3454794519</v>
+        <v>3459896337</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>64246386</v>
+        <v>64047127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.082937</v>
+        <v>0.08085199999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.07874100000000001</v>
+        <v>0.078128</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0038387654230818</v>
+        <v>-0.000481778053392432</v>
       </c>
       <c r="L30" t="n">
-        <v>-4.6854</v>
+        <v>-0.60664</v>
       </c>
       <c r="M30" t="n">
-        <v>43831559702.49809</v>
+        <v>43831559703.02959</v>
       </c>
       <c r="N30" t="n">
         <v>50000000000</v>
@@ -2451,19 +2451,19 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001823476592520541</v>
+        <v>0.001804501600129962</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,28 +2482,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.97</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>3435663564</v>
+        <v>3455358179</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>297047490</v>
+        <v>243337000</v>
       </c>
       <c r="I31" t="n">
-        <v>8.19</v>
+        <v>8.1</v>
       </c>
       <c r="J31" t="n">
-        <v>7.84</v>
+        <v>7.9</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.2117524453894619</v>
+        <v>0.109902</v>
       </c>
       <c r="L31" t="n">
-        <v>-2.58935</v>
+        <v>1.39242</v>
       </c>
       <c r="M31" t="n">
         <v>431771961.1772119</v>
@@ -2518,354 +2518,354 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001811364866845748</v>
+        <v>0.001801661325229493</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.812651</v>
+        <v>2.6</v>
       </c>
       <c r="F32" t="n">
-        <v>3324151496</v>
+        <v>3390650895</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>624688849</v>
+        <v>635060449</v>
       </c>
       <c r="I32" t="n">
-        <v>0.835668</v>
+        <v>2.63</v>
       </c>
       <c r="J32" t="n">
-        <v>0.796664</v>
+        <v>2.27</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.02113090563476905</v>
+        <v>0.332681</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.54035</v>
+        <v>14.69565</v>
       </c>
       <c r="M32" t="n">
-        <v>4096537146.540959</v>
+        <v>1305860723</v>
       </c>
       <c r="N32" t="n">
-        <v>10000000000</v>
+        <v>1305860738</v>
       </c>
       <c r="O32" t="n">
-        <v>5.35</v>
+        <v>20.44</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00174076705418847</v>
+        <v>0.001761163291749242</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.999999</v>
+        <v>0.815164</v>
       </c>
       <c r="F33" t="n">
-        <v>3320763955</v>
+        <v>3339348505</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>1296770750</v>
+        <v>589105572</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.833475</v>
       </c>
       <c r="J33" t="n">
-        <v>0.99987</v>
+        <v>0.802561</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.000131970782920154</v>
+        <v>0.01404872</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.01218</v>
+        <v>1.75365</v>
       </c>
       <c r="M33" t="n">
-        <v>3320823580.330648</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N33" t="n">
-        <v>3320823580.23496</v>
+        <v>10000000000</v>
       </c>
       <c r="O33" t="n">
-        <v>1.65</v>
+        <v>5.35</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001738622416489823</v>
+        <v>0.001729054914153965</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.41e-06</v>
+        <v>0.999949</v>
       </c>
       <c r="F34" t="n">
-        <v>3181936899</v>
+        <v>3320653051</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>70047764</v>
+        <v>1261073479</v>
       </c>
       <c r="I34" t="n">
-        <v>5.52e-06</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>5.35e-06</v>
+        <v>0.999798</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.9611488687e-08</v>
+        <v>-2.142112179526e-06</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.64409</v>
+        <v>-0.00021</v>
       </c>
       <c r="M34" t="n">
-        <v>589239301250526.8</v>
+        <v>3320823580.23496</v>
       </c>
       <c r="N34" t="n">
-        <v>589496238721205.9</v>
+        <v>3319552997.614177</v>
       </c>
       <c r="O34" t="n">
-        <v>8.616e-05</v>
+        <v>1.65</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001650731601916736</v>
+        <v>0.001717354081184055</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.062851</v>
+        <v>5.44e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>3044267162</v>
+        <v>3208258100</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>26576502</v>
+        <v>70982951</v>
       </c>
       <c r="I35" t="n">
-        <v>0.063983</v>
+        <v>5.51e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>0.056688</v>
+        <v>5.36e-06</v>
       </c>
       <c r="K35" t="n">
-        <v>0.00543273</v>
+        <v>5.8784e-08</v>
       </c>
       <c r="L35" t="n">
-        <v>9.56324</v>
+        <v>1.09143</v>
       </c>
       <c r="M35" t="n">
-        <v>48542833098.52356</v>
+        <v>589239301066730.6</v>
       </c>
       <c r="N35" t="n">
-        <v>98909511932.3777</v>
+        <v>589496238721205.9</v>
       </c>
       <c r="O35" t="n">
-        <v>0.891544</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001563573481045883</v>
+        <v>0.001647009999231718</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2.32</v>
+        <v>0.059989</v>
       </c>
       <c r="F36" t="n">
-        <v>3024736252</v>
+        <v>2912083031</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>376513982</v>
+        <v>18003909</v>
       </c>
       <c r="I36" t="n">
-        <v>2.43</v>
+        <v>0.06401</v>
       </c>
       <c r="J36" t="n">
-        <v>2.25</v>
+        <v>0.058574</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.03718487683599214</v>
+        <v>4.7e-05</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.62853</v>
+        <v>0.07840999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>1305806047</v>
+        <v>48543903603.71478</v>
       </c>
       <c r="N36" t="n">
-        <v>1305806047</v>
+        <v>98910623315.97723</v>
       </c>
       <c r="O36" t="n">
-        <v>20.44</v>
+        <v>0.891544</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001551208545573552</v>
+        <v>0.001461644347655651</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2884,34 +2884,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.999926</v>
       </c>
       <c r="F37" t="n">
-        <v>2851876538</v>
+        <v>2833707619</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>53831584</v>
+        <v>51031125</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9996930000000001</v>
+        <v>0.999729</v>
       </c>
       <c r="K37" t="n">
-        <v>0.00023192</v>
+        <v>0.00016007</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02156</v>
+        <v>0.01601</v>
       </c>
       <c r="M37" t="n">
-        <v>2851736158.030534</v>
+        <v>2833916974.830228</v>
       </c>
       <c r="N37" t="n">
-        <v>2851736158.030534</v>
+        <v>2824062986.690228</v>
       </c>
       <c r="O37" t="n">
         <v>1.021</v>
@@ -2920,19 +2920,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001441771800978674</v>
+        <v>0.001412591909305673</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2987,153 +2987,153 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001420112120117006</v>
+        <v>0.001402550896352456</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.21</v>
+        <v>4424.73</v>
       </c>
       <c r="F39" t="n">
-        <v>2754466431</v>
+        <v>2711581738</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>2339118</v>
+        <v>183139145</v>
       </c>
       <c r="I39" t="n">
-        <v>1.25</v>
+        <v>4411.13</v>
       </c>
       <c r="J39" t="n">
-        <v>1.16</v>
+        <v>4343.14</v>
       </c>
       <c r="K39" t="n">
-        <v>0.04348689</v>
+        <v>30.93</v>
       </c>
       <c r="L39" t="n">
-        <v>3.60824</v>
+        <v>0.70395</v>
       </c>
       <c r="M39" t="n">
-        <v>2270654950.054407</v>
+        <v>612823.6595320001</v>
       </c>
       <c r="N39" t="n">
-        <v>5412044796.561632</v>
+        <v>707747.089</v>
       </c>
       <c r="O39" t="n">
-        <v>5.64</v>
+        <v>5504.62</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001380101879433398</v>
+        <v>0.001336157577468424</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368.87</v>
+        <v>1.18</v>
       </c>
       <c r="F40" t="n">
-        <v>2676374901</v>
+        <v>2689559488</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>197514893</v>
+        <v>1456779</v>
       </c>
       <c r="I40" t="n">
-        <v>4438.15</v>
+        <v>1.25</v>
       </c>
       <c r="J40" t="n">
-        <v>4343.14</v>
+        <v>1.17</v>
       </c>
       <c r="K40" t="n">
-        <v>-59.99970916183884</v>
+        <v>0.01616015</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.34871</v>
+        <v>1.3833</v>
       </c>
       <c r="M40" t="n">
-        <v>612823.6595320001</v>
+        <v>2270840076.467913</v>
       </c>
       <c r="N40" t="n">
-        <v>707747.089</v>
+        <v>5412229922.975138</v>
       </c>
       <c r="O40" t="n">
-        <v>5504.62</v>
+        <v>5.64</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001330662466247551</v>
+        <v>0.001322374618848024</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3155,7 +3155,7 @@
         <v>1.14</v>
       </c>
       <c r="F41" t="n">
-        <v>2624518387</v>
+        <v>2624745730</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
@@ -3170,10 +3170,10 @@
         <v>1.14</v>
       </c>
       <c r="K41" t="n">
-        <v>6.584000000000001e-05</v>
+        <v>9.846e-05</v>
       </c>
       <c r="L41" t="n">
-        <v>0.00579</v>
+        <v>0.008659999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>2309010956.409942</v>
@@ -3185,22 +3185,22 @@
         <v>1.14</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46273.54178240741</v>
+        <v>46274.53819444445</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001297832329329711</v>
+        <v>0.001281809947002659</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3219,28 +3219,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>257.61</v>
+        <v>267.37</v>
       </c>
       <c r="F42" t="n">
-        <v>2469747768</v>
+        <v>2566084340</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>219247605</v>
+        <v>264998125</v>
       </c>
       <c r="I42" t="n">
-        <v>269.03</v>
+        <v>269.06</v>
       </c>
       <c r="J42" t="n">
-        <v>249.72</v>
+        <v>251.25</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.5559311026405</v>
+        <v>16.36</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.43081</v>
+        <v>6.51859</v>
       </c>
       <c r="M42" t="n">
         <v>9597491</v>
@@ -3255,19 +3255,19 @@
         <v>45358.44833333333</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001199847713305793</v>
+        <v>0.001245095827828408</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3289,13 +3289,13 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2441711587</v>
+        <v>2437862509</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>204953060</v>
+        <v>226230371</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -3304,16 +3304,16 @@
         <v>0.999768</v>
       </c>
       <c r="K43" t="n">
-        <v>0.00012067</v>
+        <v>0.00011796</v>
       </c>
       <c r="L43" t="n">
-        <v>0.008659999999999999</v>
+        <v>0.0118</v>
       </c>
       <c r="M43" t="n">
-        <v>2441445609.107191</v>
+        <v>2437740048.107196</v>
       </c>
       <c r="N43" t="n">
-        <v>2441445609.107193</v>
+        <v>2434600130.107194</v>
       </c>
       <c r="O43" t="n">
         <v>1.073</v>
@@ -3322,19 +3322,19 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001182098127190472</v>
+        <v>0.001164846253379617</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3353,28 +3353,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>113.88</v>
+        <v>114.34</v>
       </c>
       <c r="F44" t="n">
-        <v>2389519318</v>
+        <v>2401035797</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>25728620</v>
+        <v>20248262</v>
       </c>
       <c r="I44" t="n">
-        <v>117.59</v>
+        <v>114.99</v>
       </c>
       <c r="J44" t="n">
         <v>113.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.073229450690647</v>
+        <v>-0.2677980235424968</v>
       </c>
       <c r="L44" t="n">
-        <v>-2.62206</v>
+        <v>-0.23367</v>
       </c>
       <c r="M44" t="n">
         <v>21000000</v>
@@ -3389,19 +3389,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001149055425220132</v>
+        <v>0.001141797698049377</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,13 +3423,13 @@
         <v>1.14</v>
       </c>
       <c r="F45" t="n">
-        <v>2202607843</v>
+        <v>2204440970</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>4742220</v>
+        <v>5112891</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.000908633043795293</v>
+        <v>0.00221101</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.19357</v>
       </c>
       <c r="M45" t="n">
-        <v>1926010608.264936</v>
+        <v>1926227461.922417</v>
       </c>
       <c r="N45" t="n">
-        <v>1926010608.264935</v>
+        <v>1926227461.922417</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.00103072257091825</v>
+        <v>0.001018755848759425</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,28 +3487,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.632138</v>
+        <v>0.640481</v>
       </c>
       <c r="F46" t="n">
-        <v>2086406982</v>
+        <v>2115055460</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>33835307</v>
+        <v>30688181</v>
       </c>
       <c r="I46" t="n">
-        <v>0.644994</v>
+        <v>0.652427</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6153419999999999</v>
+        <v>0.622271</v>
       </c>
       <c r="K46" t="n">
-        <v>0.00485833</v>
+        <v>0.01789868</v>
       </c>
       <c r="L46" t="n">
-        <v>0.75778</v>
+        <v>2.87491</v>
       </c>
       <c r="M46" t="n">
         <v>3302294382.53684</v>
@@ -3523,354 +3523,354 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009571563034942396</v>
+        <v>0.0009628125738627485</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.2</v>
+        <v>0.751659</v>
       </c>
       <c r="F47" t="n">
-        <v>2038518202</v>
+        <v>2032539231</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>429408655</v>
+        <v>130939381</v>
       </c>
       <c r="I47" t="n">
-        <v>1.28</v>
+        <v>0.765651</v>
       </c>
       <c r="J47" t="n">
-        <v>1.048</v>
+        <v>0.746359</v>
       </c>
       <c r="K47" t="n">
-        <v>0.132157</v>
+        <v>0.00017314</v>
       </c>
       <c r="L47" t="n">
-        <v>12.61476</v>
+        <v>0.02304</v>
       </c>
       <c r="M47" t="n">
-        <v>1701867901.842436</v>
+        <v>2704071066.799731</v>
       </c>
       <c r="N47" t="n">
-        <v>1701886788.079746</v>
+        <v>7803968119.651995</v>
       </c>
       <c r="O47" t="n">
-        <v>54.98</v>
+        <v>2.41</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009268381219784452</v>
+        <v>0.0009111685424936363</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.752704</v>
+        <v>130.38</v>
       </c>
       <c r="F48" t="n">
-        <v>2033391419</v>
+        <v>2011490815</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>150228101</v>
+        <v>188654798</v>
       </c>
       <c r="I48" t="n">
-        <v>0.779274</v>
+        <v>131.05</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7400409999999999</v>
+        <v>127.56</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.0221486954865765</v>
+        <v>2.44</v>
       </c>
       <c r="L48" t="n">
-        <v>-2.86332</v>
+        <v>1.90947</v>
       </c>
       <c r="M48" t="n">
-        <v>2704071066.799731</v>
+        <v>15427520.23413867</v>
       </c>
       <c r="N48" t="n">
-        <v>7803968119.651995</v>
+        <v>16000000</v>
       </c>
       <c r="O48" t="n">
-        <v>2.41</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0009235923776185745</v>
+        <v>0.0008979950726277979</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>129.03</v>
+        <v>1.17</v>
       </c>
       <c r="F49" t="n">
-        <v>1988990798</v>
+        <v>1990773475</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>201580573</v>
+        <v>433366537</v>
       </c>
       <c r="I49" t="n">
-        <v>132.78</v>
+        <v>1.28</v>
       </c>
       <c r="J49" t="n">
-        <v>126.85</v>
+        <v>1.073</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.887534232723254</v>
+        <v>0.103913</v>
       </c>
       <c r="L49" t="n">
-        <v>-2.95</v>
+        <v>9.749879999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>15427489.93418658</v>
+        <v>1701957999.857161</v>
       </c>
       <c r="N49" t="n">
-        <v>16000000</v>
+        <v>1701965018.386449</v>
       </c>
       <c r="O49" t="n">
-        <v>661.6900000000001</v>
+        <v>54.98</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008954825346262911</v>
+        <v>0.000885028811689667</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4371.84</v>
+        <v>0.00462038</v>
       </c>
       <c r="F50" t="n">
-        <v>1890314380</v>
+        <v>1916697613</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>135436742</v>
+        <v>242544269</v>
       </c>
       <c r="I50" t="n">
-        <v>4440.78</v>
+        <v>0.00473928</v>
       </c>
       <c r="J50" t="n">
-        <v>4348.7</v>
+        <v>0.00425383</v>
       </c>
       <c r="K50" t="n">
-        <v>-59.9372061560116</v>
+        <v>0.00034456</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.36356</v>
+        <v>8.05829</v>
       </c>
       <c r="M50" t="n">
-        <v>432503.312051</v>
+        <v>414835547764.7695</v>
       </c>
       <c r="N50" t="n">
-        <v>432503.312051</v>
+        <v>834972366903.9573</v>
       </c>
       <c r="O50" t="n">
-        <v>5619.09</v>
+        <v>0.00881908</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008330109170103817</v>
+        <v>0.0008386673118103884</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.00441357</v>
+        <v>4428.76</v>
       </c>
       <c r="F51" t="n">
-        <v>1829438215</v>
+        <v>1915451805</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>206283923</v>
+        <v>131038731</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00455107</v>
+        <v>4413.97</v>
       </c>
       <c r="J51" t="n">
-        <v>0.00413436</v>
+        <v>4348.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.000113434487260502</v>
+        <v>30.54</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.43126</v>
+        <v>0.69446</v>
       </c>
       <c r="M51" t="n">
-        <v>414921492572.7707</v>
+        <v>432503.312051</v>
       </c>
       <c r="N51" t="n">
-        <v>835038757789.6458</v>
+        <v>432503.312051</v>
       </c>
       <c r="O51" t="n">
-        <v>0.00881908</v>
+        <v>5619.09</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0007944704776745821</v>
+        <v>0.0008378876040097339</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3889,28 +3889,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.373106</v>
+        <v>0.378675</v>
       </c>
       <c r="F52" t="n">
-        <v>1814660521</v>
+        <v>1843892054</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>110430330</v>
+        <v>104045504</v>
       </c>
       <c r="I52" t="n">
-        <v>0.387468</v>
+        <v>0.385685</v>
       </c>
       <c r="J52" t="n">
-        <v>0.370021</v>
+        <v>0.369949</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.01582755146291748</v>
+        <v>0.00512265</v>
       </c>
       <c r="L52" t="n">
-        <v>-4.14836</v>
+        <v>1.37133</v>
       </c>
       <c r="M52" t="n">
         <v>4869330647</v>
@@ -3925,19 +3925,19 @@
         <v>45641.69166666667</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.000785114782894367</v>
+        <v>0.0007931008502984142</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3956,31 +3956,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.05624</v>
+        <v>0.055867</v>
       </c>
       <c r="F53" t="n">
-        <v>1786989361</v>
+        <v>1775278070</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>21981804</v>
+        <v>22120553</v>
       </c>
       <c r="I53" t="n">
-        <v>0.056635</v>
+        <v>0.056457</v>
       </c>
       <c r="J53" t="n">
-        <v>0.055395</v>
+        <v>0.055548</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.00040446709796698</v>
+        <v>0.00026835</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.71307</v>
+        <v>0.48266</v>
       </c>
       <c r="M53" t="n">
-        <v>31777109679</v>
+        <v>31777118978</v>
       </c>
       <c r="N53" t="n">
         <v>100000000000</v>
@@ -3992,19 +3992,19 @@
         <v>45901.18065972222</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007675962900108024</v>
+        <v>0.0007501577494684458</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4023,31 +4023,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.457483</v>
+        <v>0.453082</v>
       </c>
       <c r="F54" t="n">
-        <v>1679380523</v>
+        <v>1666800928</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>311914590</v>
+        <v>242159032</v>
       </c>
       <c r="I54" t="n">
         <v>0.492671</v>
       </c>
       <c r="J54" t="n">
-        <v>0.449748</v>
+        <v>0.44254</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.04328333901993353</v>
+        <v>-0.01373543464551086</v>
       </c>
       <c r="L54" t="n">
-        <v>-8.561059999999999</v>
+        <v>-2.94235</v>
       </c>
       <c r="M54" t="n">
-        <v>3678776941.269424</v>
+        <v>3678803645.0447</v>
       </c>
       <c r="N54" t="n">
         <v>10000000000</v>
@@ -4059,19 +4059,19 @@
         <v>45360.67409722223</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0006994695955494332</v>
+        <v>0.000682265687601687</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4090,28 +4090,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.160295</v>
+        <v>0.163574</v>
       </c>
       <c r="F55" t="n">
-        <v>1616130829</v>
+        <v>1651334608</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>440636575</v>
+        <v>453892663</v>
       </c>
       <c r="I55" t="n">
-        <v>0.168659</v>
+        <v>0.168753</v>
       </c>
       <c r="J55" t="n">
-        <v>0.157077</v>
+        <v>0.15868</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.006530793004761531</v>
+        <v>0.00550579</v>
       </c>
       <c r="L55" t="n">
-        <v>-3.90374</v>
+        <v>3.48317</v>
       </c>
       <c r="M55" t="n">
         <v>10095312500</v>
@@ -4126,354 +4126,354 @@
         <v>45393.21892361111</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006594264851692887</v>
+        <v>0.0006725858570407832</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="F56" t="n">
-        <v>1610750258</v>
+        <v>1618892087</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>78438198</v>
+        <v>32447610</v>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="J56" t="n">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.1454375558612471</v>
+        <v>-0.06501100290062611</v>
       </c>
       <c r="L56" t="n">
-        <v>-4.77913</v>
+        <v>-2.69175</v>
       </c>
       <c r="M56" t="n">
-        <v>556264723.4627383</v>
+        <v>688837052.3557253</v>
       </c>
       <c r="N56" t="n">
-        <v>556264879.1528305</v>
+        <v>1000000000</v>
       </c>
       <c r="O56" t="n">
-        <v>700.65</v>
+        <v>4.17</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006560200687135632</v>
+        <v>0.0006522812140327142</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="F57" t="n">
-        <v>1599100827</v>
+        <v>1603747363</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>32755296</v>
+        <v>63715202</v>
       </c>
       <c r="I57" t="n">
-        <v>2.49</v>
+        <v>3.07</v>
       </c>
       <c r="J57" t="n">
-        <v>2.32</v>
+        <v>2.83</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.1651890632146942</v>
+        <v>-0.1076426999183364</v>
       </c>
       <c r="L57" t="n">
-        <v>-6.66938</v>
+        <v>-3.59925</v>
       </c>
       <c r="M57" t="n">
-        <v>688811955.59319</v>
+        <v>556267110.7903996</v>
       </c>
       <c r="N57" t="n">
-        <v>1000000000</v>
+        <v>556267110.7903996</v>
       </c>
       <c r="O57" t="n">
-        <v>4.17</v>
+        <v>700.65</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R57" t="b">
         <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>0.000648644863840653</v>
+        <v>0.0006428026591979732</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.067241</v>
+        <v>3.7e-06</v>
       </c>
       <c r="F58" t="n">
-        <v>1575619353</v>
+        <v>1558125094</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>6316347</v>
+        <v>233655849</v>
       </c>
       <c r="I58" t="n">
-        <v>0.06948600000000001</v>
+        <v>3.76e-06</v>
       </c>
       <c r="J58" t="n">
-        <v>0.066624</v>
+        <v>3.59e-06</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.002172157813980516</v>
+        <v>1.23124e-07</v>
       </c>
       <c r="L58" t="n">
-        <v>-3.1467</v>
+        <v>3.43864</v>
       </c>
       <c r="M58" t="n">
-        <v>23428151998.06358</v>
+        <v>420690000000000</v>
       </c>
       <c r="N58" t="n">
-        <v>23462665147.36596</v>
+        <v>420690000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>0.100535</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006337788432197391</v>
+        <v>0.000614249271338161</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.64e-06</v>
+        <v>1.69e-06</v>
       </c>
       <c r="F59" t="n">
-        <v>1529740358</v>
+        <v>1516108351</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>226941120</v>
+        <v>25301224</v>
       </c>
       <c r="I59" t="n">
-        <v>3.76e-06</v>
+        <v>1.7e-06</v>
       </c>
       <c r="J59" t="n">
-        <v>3.55e-06</v>
+        <v>1.68e-06</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.978058749e-09</v>
+        <v>-1.1397764713e-08</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.05951</v>
+        <v>-0.67074</v>
       </c>
       <c r="M59" t="n">
-        <v>420690000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N59" t="n">
-        <v>420690000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O59" t="n">
-        <v>2.803e-05</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006047330479797637</v>
+        <v>0.0005879524565198308</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.69e-06</v>
+        <v>0.064594</v>
       </c>
       <c r="F60" t="n">
-        <v>1520561338</v>
+        <v>1513277904</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>42436802</v>
+        <v>8809154</v>
       </c>
       <c r="I60" t="n">
-        <v>1.71e-06</v>
+        <v>0.068149</v>
       </c>
       <c r="J60" t="n">
-        <v>1.67e-06</v>
+        <v>0.064162</v>
       </c>
       <c r="K60" t="n">
-        <v>1.8211e-08</v>
+        <v>-0.002333706369906666</v>
       </c>
       <c r="L60" t="n">
-        <v>1.09062</v>
+        <v>-3.48692</v>
       </c>
       <c r="M60" t="n">
-        <v>898232728634017.2</v>
+        <v>23427606245.71321</v>
       </c>
       <c r="N60" t="n">
-        <v>898232728634017.2</v>
+        <v>23462665147.36596</v>
       </c>
       <c r="O60" t="n">
-        <v>3.75e-06</v>
+        <v>0.100535</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005989218497304638</v>
+        <v>0.0005861809784066392</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4492,34 +4492,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.999687</v>
+        <v>0.999587</v>
       </c>
       <c r="F61" t="n">
-        <v>1498768183</v>
+        <v>1501094917</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>6569475</v>
+        <v>5671237</v>
       </c>
       <c r="I61" t="n">
-        <v>0.999871</v>
+        <v>0.999947</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9987470000000001</v>
+        <v>0.998458</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0005602200000000001</v>
+        <v>-4.678295007543e-05</v>
       </c>
       <c r="L61" t="n">
-        <v>0.05796</v>
+        <v>-0.00468</v>
       </c>
       <c r="M61" t="n">
-        <v>1499053174</v>
+        <v>1501715043</v>
       </c>
       <c r="N61" t="n">
-        <v>1504694206</v>
+        <v>1501818851</v>
       </c>
       <c r="O61" t="n">
         <v>1.24</v>
@@ -4528,19 +4528,19 @@
         <v>46212.39942129629</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005851246966375714</v>
+        <v>0.000578556071519565</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4559,28 +4559,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="F62" t="n">
-        <v>1398812648</v>
+        <v>1393021867</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>12884526</v>
+        <v>11856320</v>
       </c>
       <c r="I62" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="J62" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0052162</v>
+        <v>0.02010862</v>
       </c>
       <c r="L62" t="n">
-        <v>0.27158</v>
+        <v>1.02077</v>
       </c>
       <c r="M62" t="n">
         <v>699992029.6481038</v>
@@ -4595,220 +4595,220 @@
         <v>45653.15375</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005218432755272748</v>
+        <v>0.0005109169167497121</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>8.82</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1390647077</v>
+        <v>1373620824</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>107513986</v>
+        <v>57943024</v>
       </c>
       <c r="I63" t="n">
-        <v>8.859999999999999</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>7.94</v>
+        <v>0.99995</v>
       </c>
       <c r="K63" t="n">
-        <v>0.830053</v>
+        <v>-8.536233971279101e-05</v>
       </c>
       <c r="L63" t="n">
-        <v>10.36207</v>
+        <v>-0.008529999999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>158113953.5287312</v>
+        <v>1373442039.16</v>
       </c>
       <c r="N63" t="n">
-        <v>158114945.222385</v>
+        <v>1373442039.16</v>
       </c>
       <c r="O63" t="n">
-        <v>167.09</v>
+        <v>1.002</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.000516673687499388</v>
+        <v>0.0004987744802202205</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>0.996804</v>
       </c>
       <c r="F64" t="n">
-        <v>1365412722</v>
+        <v>1340178272</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>29514186</v>
+        <v>411225</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0.991216</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.2862651698591e-05</v>
+        <v>0.0001942</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.00584</v>
+        <v>0.01949</v>
       </c>
       <c r="M64" t="n">
-        <v>1365454412.77</v>
+        <v>1344475004.618144</v>
       </c>
       <c r="N64" t="n">
-        <v>1365454412.77</v>
+        <v>1344475004.618144</v>
       </c>
       <c r="O64" t="n">
-        <v>1.002</v>
+        <v>1.075</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46092.00303240741</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005006979254247643</v>
+        <v>0.0004778439526684686</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.997452</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>1340581630</v>
+        <v>1321985283</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>434484</v>
+        <v>119020005</v>
       </c>
       <c r="I65" t="n">
-        <v>1.003</v>
+        <v>9.02</v>
       </c>
       <c r="J65" t="n">
-        <v>0.982128</v>
+        <v>8.25</v>
       </c>
       <c r="K65" t="n">
-        <v>0.00103528</v>
+        <v>0.169357</v>
       </c>
       <c r="L65" t="n">
-        <v>0.10546</v>
+        <v>2.06752</v>
       </c>
       <c r="M65" t="n">
-        <v>1344097428.497996</v>
+        <v>158119477.0392587</v>
       </c>
       <c r="N65" t="n">
-        <v>1344097428.497996</v>
+        <v>158119854.9976587</v>
       </c>
       <c r="O65" t="n">
-        <v>1.075</v>
+        <v>167.09</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.000484977467428311</v>
+        <v>0.0004664575950270656</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4827,28 +4827,28 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.999856</v>
+        <v>0.999678</v>
       </c>
       <c r="F66" t="n">
-        <v>1319809636</v>
+        <v>1319574651</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>2117804</v>
+        <v>2012445</v>
       </c>
       <c r="I66" t="n">
-        <v>0.999939</v>
+        <v>0.99995</v>
       </c>
       <c r="J66" t="n">
-        <v>0.999489</v>
+        <v>0.999519</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00018169</v>
+        <v>0.00013571</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0197</v>
+        <v>0.01358</v>
       </c>
       <c r="M66" t="n">
         <v>1320000000</v>
@@ -4863,19 +4863,19 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.000471826806991002</v>
+        <v>0.0004649488644884053</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4894,34 +4894,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9992180000000001</v>
+        <v>0.999153</v>
       </c>
       <c r="F67" t="n">
-        <v>1291987045</v>
+        <v>1287408036</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>188019271</v>
+        <v>159253867</v>
       </c>
       <c r="I67" t="n">
         <v>0.999421</v>
       </c>
       <c r="J67" t="n">
-        <v>0.998906</v>
+        <v>0.998873</v>
       </c>
       <c r="K67" t="n">
-        <v>5.897e-05</v>
+        <v>9.974e-05</v>
       </c>
       <c r="L67" t="n">
-        <v>0.01396</v>
+        <v>0.009979999999999999</v>
       </c>
       <c r="M67" t="n">
-        <v>1292999307.8</v>
+        <v>1288500007.8</v>
       </c>
       <c r="N67" t="n">
-        <v>1292999307.8</v>
+        <v>1288500007.8</v>
       </c>
       <c r="O67" t="n">
         <v>1.008</v>
@@ -4930,19 +4930,19 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004542124437898992</v>
+        <v>0.0004448169014281671</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4964,7 +4964,7 @@
         <v>1.18</v>
       </c>
       <c r="F68" t="n">
-        <v>1246303864</v>
+        <v>1270222603</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
@@ -4979,16 +4979,16 @@
         <v>1.18</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0001547</v>
+        <v>0.00251157</v>
       </c>
       <c r="L68" t="n">
-        <v>0.01314</v>
+        <v>0.2135</v>
       </c>
       <c r="M68" t="n">
-        <v>1058698463.14974</v>
+        <v>1077468076.07545</v>
       </c>
       <c r="N68" t="n">
-        <v>1058698463.14974</v>
+        <v>1077468076.07545</v>
       </c>
       <c r="O68" t="n">
         <v>1.18</v>
@@ -4997,19 +4997,19 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004252906175546747</v>
+        <v>0.0004340611379656393</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5028,28 +5028,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.83</v>
+        <v>5.06</v>
       </c>
       <c r="F69" t="n">
-        <v>1205771264</v>
+        <v>1265464459</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>121686679</v>
+        <v>121774066</v>
       </c>
       <c r="I69" t="n">
-        <v>4.91</v>
+        <v>5.31</v>
       </c>
       <c r="J69" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="K69" t="n">
-        <v>0.089965</v>
+        <v>0.249492</v>
       </c>
       <c r="L69" t="n">
-        <v>1.92159</v>
+        <v>5.18439</v>
       </c>
       <c r="M69" t="n">
         <v>250000000</v>
@@ -5064,287 +5064,287 @@
         <v>46021.04538194444</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0003996296020911967</v>
+        <v>0.0004310831814960731</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.434703</v>
+        <v>26.01</v>
       </c>
       <c r="F70" t="n">
-        <v>1177588419</v>
+        <v>1245840649</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>10465630</v>
+        <v>339972518</v>
       </c>
       <c r="I70" t="n">
-        <v>0.46133</v>
+        <v>29.19</v>
       </c>
       <c r="J70" t="n">
-        <v>0.429682</v>
+        <v>19.47</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.01493414384523367</v>
+        <v>7.21</v>
       </c>
       <c r="L70" t="n">
-        <v>-3.30759</v>
+        <v>38.35212</v>
       </c>
       <c r="M70" t="n">
-        <v>2708142280.000001</v>
+        <v>47901563.16795567</v>
       </c>
       <c r="N70" t="n">
-        <v>10000000000</v>
+        <v>80972884.09714592</v>
       </c>
       <c r="O70" t="n">
-        <v>0.745279</v>
+        <v>29.19</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46253.4</v>
+        <v>46274.32083333333</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0003817871636256208</v>
+        <v>0.000418801322866524</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>24.36</v>
+        <v>0.449598</v>
       </c>
       <c r="F71" t="n">
-        <v>1172375897</v>
+        <v>1217576685</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>210948140</v>
+        <v>7595620</v>
       </c>
       <c r="I71" t="n">
-        <v>26.08</v>
+        <v>0.46133</v>
       </c>
       <c r="J71" t="n">
-        <v>17.53</v>
+        <v>0.429682</v>
       </c>
       <c r="K71" t="n">
-        <v>5.5</v>
+        <v>0.005923</v>
       </c>
       <c r="L71" t="n">
-        <v>29.31363</v>
+        <v>1.33498</v>
       </c>
       <c r="M71" t="n">
-        <v>47898061.16245246</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N71" t="n">
-        <v>80969463.56188472</v>
+        <v>10000000000</v>
       </c>
       <c r="O71" t="n">
-        <v>26.08</v>
+        <v>0.745279</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46274.00509259259</v>
+        <v>46253.4</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003784871382720605</v>
+        <v>0.0004011118930280439</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.09934800000000001</v>
+        <v>0.166662</v>
       </c>
       <c r="F72" t="n">
-        <v>1105776236</v>
+        <v>1112983043</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>7086318</v>
+        <v>260935944</v>
       </c>
       <c r="I72" t="n">
-        <v>0.098727</v>
+        <v>0.174571</v>
       </c>
       <c r="J72" t="n">
-        <v>0.09424299999999999</v>
+        <v>0.163302</v>
       </c>
       <c r="K72" t="n">
-        <v>0.00502445</v>
+        <v>-0.000870409281804901</v>
       </c>
       <c r="L72" t="n">
-        <v>5.32899</v>
+        <v>-0.51955</v>
       </c>
       <c r="M72" t="n">
-        <v>11141680597.24892</v>
+        <v>6678075931</v>
       </c>
       <c r="N72" t="n">
-        <v>17141047072.69065</v>
+        <v>10000000000</v>
       </c>
       <c r="O72" t="n">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003363231781317441</v>
+        <v>0.0003356503784397114</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.164737</v>
+        <v>0.097941</v>
       </c>
       <c r="F73" t="n">
-        <v>1099640787</v>
+        <v>1091222672</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>274682900</v>
+        <v>6895684</v>
       </c>
       <c r="I73" t="n">
-        <v>0.178199</v>
+        <v>0.09958400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>0.163302</v>
+        <v>0.095987</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.007472498552381857</v>
+        <v>0.00219393</v>
       </c>
       <c r="L73" t="n">
-        <v>-4.5414</v>
+        <v>2.29139</v>
       </c>
       <c r="M73" t="n">
-        <v>6678075931</v>
+        <v>11141680597.24892</v>
       </c>
       <c r="N73" t="n">
-        <v>10000000000</v>
+        <v>17141047072.69065</v>
       </c>
       <c r="O73" t="n">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003324388516472753</v>
+        <v>0.0003220313207567976</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5363,31 +5363,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.09507699999999999</v>
+        <v>0.097224</v>
       </c>
       <c r="F74" t="n">
-        <v>1018154800</v>
+        <v>1041386346</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>56105990</v>
+        <v>89603107</v>
       </c>
       <c r="I74" t="n">
-        <v>0.09886300000000001</v>
+        <v>0.099879</v>
       </c>
       <c r="J74" t="n">
-        <v>0.095009</v>
+        <v>0.094888</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.000739630444359596</v>
+        <v>0.00152497</v>
       </c>
       <c r="L74" t="n">
-        <v>-0.74601</v>
+        <v>1.5935</v>
       </c>
       <c r="M74" t="n">
-        <v>10710616938.28008</v>
+        <v>10711198045.42806</v>
       </c>
       <c r="N74" t="n">
         <v>10711198045.42806</v>
@@ -5399,287 +5399,287 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002808504222728024</v>
+        <v>0.0002908405015148603</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.03597019</v>
+        <v>1.96</v>
       </c>
       <c r="F75" t="n">
-        <v>995961690</v>
+        <v>1037130851</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>25683776</v>
+        <v>117474646</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03715227</v>
+        <v>2.03</v>
       </c>
       <c r="J75" t="n">
-        <v>0.03387269</v>
+        <v>1.71</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.000517054154749008</v>
+        <v>0.231496</v>
       </c>
       <c r="L75" t="n">
-        <v>-1.44756</v>
+        <v>13.40961</v>
       </c>
       <c r="M75" t="n">
-        <v>27686994077.20287</v>
+        <v>529733011.592082</v>
       </c>
       <c r="N75" t="n">
-        <v>27689474176.05729</v>
+        <v>529741698.798252</v>
       </c>
       <c r="O75" t="n">
-        <v>0.207411</v>
+        <v>43.84</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002668000593823719</v>
+        <v>0.0002881771355329867</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>9.18</v>
+        <v>0.03605797</v>
       </c>
       <c r="F76" t="n">
-        <v>976044853</v>
+        <v>998336918</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>1473404</v>
+        <v>18754394</v>
       </c>
       <c r="I76" t="n">
-        <v>9.44</v>
+        <v>0.03715227</v>
       </c>
       <c r="J76" t="n">
-        <v>8.98</v>
+        <v>0.03506837</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.259496493396929</v>
+        <v>0.00088579</v>
       </c>
       <c r="L76" t="n">
-        <v>-2.58581</v>
+        <v>2.51845</v>
       </c>
       <c r="M76" t="n">
-        <v>106621449.456837</v>
+        <v>27686994077.20287</v>
       </c>
       <c r="N76" t="n">
-        <v>118872721.0902001</v>
+        <v>27690422706.12956</v>
       </c>
       <c r="O76" t="n">
-        <v>25.38</v>
+        <v>0.207411</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002541907951792225</v>
+        <v>0.000263897365152505</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>67.17</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>976452044</v>
+        <v>997888828</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>15903458</v>
+        <v>2186375</v>
       </c>
       <c r="I77" t="n">
-        <v>68.78</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>65.54000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="K77" t="n">
-        <v>0.339235</v>
+        <v>0.246251</v>
       </c>
       <c r="L77" t="n">
-        <v>0.51917</v>
+        <v>2.70223</v>
       </c>
       <c r="M77" t="n">
-        <v>14544176.16408117</v>
+        <v>106622060.2754268</v>
       </c>
       <c r="N77" t="n">
-        <v>14612493</v>
+        <v>118873292.382472</v>
       </c>
       <c r="O77" t="n">
-        <v>427.42</v>
+        <v>25.38</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002544485860573697</v>
+        <v>0.0002636169212410875</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1.84</v>
+        <v>67.75</v>
       </c>
       <c r="F78" t="n">
-        <v>974419049</v>
+        <v>985382503</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>82067107</v>
+        <v>17313401</v>
       </c>
       <c r="I78" t="n">
-        <v>1.88</v>
+        <v>69.83</v>
       </c>
       <c r="J78" t="n">
-        <v>1.63</v>
+        <v>66.81</v>
       </c>
       <c r="K78" t="n">
-        <v>0.200092</v>
+        <v>0.553311</v>
       </c>
       <c r="L78" t="n">
-        <v>12.19718</v>
+        <v>0.82341</v>
       </c>
       <c r="M78" t="n">
-        <v>529612766.282018</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N78" t="n">
-        <v>529647532.369335</v>
+        <v>14612493</v>
       </c>
       <c r="O78" t="n">
-        <v>43.84</v>
+        <v>427.42</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002531615056299564</v>
+        <v>0.0002557896483707736</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5734,19 +5734,19 @@
         <v>46273.93067129629</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002505845851108989</v>
+        <v>0.0002463805151234332</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5765,28 +5765,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7.03</v>
+        <v>7.01</v>
       </c>
       <c r="F80" t="n">
-        <v>963242554</v>
+        <v>961354266</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>2796176</v>
+        <v>2742525</v>
       </c>
       <c r="I80" t="n">
         <v>7.05</v>
       </c>
       <c r="J80" t="n">
-        <v>6.96</v>
+        <v>6.95</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.006003967477218985</v>
+        <v>0.02843958</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.09268</v>
+        <v>0.4074</v>
       </c>
       <c r="M80" t="n">
         <v>137155021.2773955</v>
@@ -5801,890 +5801,890 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002460857145131151</v>
+        <v>0.0002407512124120428</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.23</v>
+        <v>0.100637</v>
       </c>
       <c r="F81" t="n">
-        <v>918870851</v>
+        <v>909734560</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>43569879</v>
       </c>
       <c r="I81" t="n">
-        <v>1.23</v>
+        <v>0.103137</v>
       </c>
       <c r="J81" t="n">
-        <v>1.23</v>
+        <v>0.097334</v>
       </c>
       <c r="K81" t="n">
-        <v>0.00023155</v>
+        <v>0.00327804</v>
       </c>
       <c r="L81" t="n">
-        <v>0.01881</v>
+        <v>3.36695</v>
       </c>
       <c r="M81" t="n">
-        <v>746408125.4668601</v>
+        <v>9039728572.301533</v>
       </c>
       <c r="N81" t="n">
-        <v>746408125.4668601</v>
+        <v>9039769730.371443</v>
       </c>
       <c r="O81" t="n">
-        <v>1.26</v>
+        <v>3.56</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002179941793827793</v>
+        <v>0.0002084442377934093</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.10127</v>
+        <v>1.23</v>
       </c>
       <c r="F82" t="n">
-        <v>914911428</v>
+        <v>881844306</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>43579075</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0.103137</v>
+        <v>1.23</v>
       </c>
       <c r="J82" t="n">
-        <v>0.095711</v>
+        <v>1.23</v>
       </c>
       <c r="K82" t="n">
-        <v>0.00358172</v>
+        <v>0.00269621</v>
       </c>
       <c r="L82" t="n">
-        <v>3.6527</v>
+        <v>0.21918</v>
       </c>
       <c r="M82" t="n">
-        <v>9039625216.61013</v>
+        <v>715302976.77384</v>
       </c>
       <c r="N82" t="n">
-        <v>9039655890.736694</v>
+        <v>715302976.77384</v>
       </c>
       <c r="O82" t="n">
-        <v>3.56</v>
+        <v>1.26</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002154874856392383</v>
+        <v>0.0001909887000170949</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.10518</v>
+        <v>0.848105</v>
       </c>
       <c r="F83" t="n">
-        <v>861328408</v>
+        <v>848104647</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>28829056</v>
+        <v>2893581</v>
       </c>
       <c r="I83" t="n">
-        <v>0.110037</v>
+        <v>0.8501069999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>0.103569</v>
+        <v>0.822473</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.001024894409538873</v>
+        <v>0.02610827</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.95516</v>
+        <v>3.1762</v>
       </c>
       <c r="M83" t="n">
-        <v>8188743036.341737</v>
+        <v>1000000000</v>
       </c>
       <c r="N83" t="n">
-        <v>8188743036.341737</v>
+        <v>1000000000</v>
       </c>
       <c r="O83" t="n">
-        <v>0.193254</v>
+        <v>4.07</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001815643051672269</v>
+        <v>0.0001698722235506395</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.838599</v>
+        <v>0.102617</v>
       </c>
       <c r="F84" t="n">
-        <v>838600954</v>
+        <v>840302919</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>2694064</v>
+        <v>24080947</v>
       </c>
       <c r="I84" t="n">
-        <v>0.846306</v>
+        <v>0.110037</v>
       </c>
       <c r="J84" t="n">
-        <v>0.821065</v>
+        <v>0.102905</v>
       </c>
       <c r="K84" t="n">
-        <v>0.00422841</v>
+        <v>-0.004272044566157859</v>
       </c>
       <c r="L84" t="n">
-        <v>0.53445</v>
+        <v>-3.99672</v>
       </c>
       <c r="M84" t="n">
-        <v>1000000000</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N84" t="n">
-        <v>1000000000</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O84" t="n">
-        <v>4.07</v>
+        <v>0.193254</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
-        <v>0.000167175651378931</v>
+        <v>0.0001649893939491404</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11.2</v>
+        <v>64.7</v>
       </c>
       <c r="F85" t="n">
-        <v>820167101</v>
+        <v>830001957</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>191724352</v>
       </c>
       <c r="I85" t="n">
-        <v>11.2</v>
+        <v>66.34</v>
       </c>
       <c r="J85" t="n">
-        <v>11.2</v>
+        <v>61.47</v>
       </c>
       <c r="K85" t="n">
-        <v>0.001061</v>
+        <v>1.94</v>
       </c>
       <c r="L85" t="n">
-        <v>0.009469999999999999</v>
+        <v>3.08551</v>
       </c>
       <c r="M85" t="n">
-        <v>73219020.192689</v>
+        <v>12828352.02901614</v>
       </c>
       <c r="N85" t="n">
-        <v>73251569.883048</v>
+        <v>12828387.07391258</v>
       </c>
       <c r="O85" t="n">
-        <v>11.2</v>
+        <v>1493.59</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46273.67708333334</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001555052579947297</v>
+        <v>0.0001585423809056815</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>hunter-biden-s-laptop-3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Hunter Biden's Laptop</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.242755</v>
+        <v>2.37</v>
       </c>
       <c r="F86" t="n">
-        <v>805117634</v>
+        <v>828030832</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>73388636</v>
+        <v>3456213</v>
       </c>
       <c r="I86" t="n">
-        <v>0.255079</v>
+        <v>199.51</v>
       </c>
       <c r="J86" t="n">
-        <v>0.235435</v>
+        <v>4.15</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.01229588866583547</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>-4.8559</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3320312968.08</v>
+        <v>350000000</v>
       </c>
       <c r="N86" t="n">
-        <v>6862431119.953158</v>
+        <v>1000000000</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>199.51</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>46274.50636574074</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001459775048921875</v>
+        <v>0.0001573087224779262</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>62.34</v>
+        <v>0.249268</v>
       </c>
       <c r="F87" t="n">
-        <v>799221315</v>
+        <v>827648744</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>157696276</v>
+        <v>85872214</v>
       </c>
       <c r="I87" t="n">
-        <v>64.84999999999999</v>
+        <v>0.253844</v>
       </c>
       <c r="J87" t="n">
-        <v>61.47</v>
+        <v>0.237355</v>
       </c>
       <c r="K87" t="n">
-        <v>-1.322632647083324</v>
+        <v>0.00948354</v>
       </c>
       <c r="L87" t="n">
-        <v>-2.23516</v>
+        <v>3.95502</v>
       </c>
       <c r="M87" t="n">
-        <v>12829567.31909475</v>
+        <v>3320312968.08</v>
       </c>
       <c r="N87" t="n">
-        <v>12829661.6155104</v>
+        <v>6862431106.912057</v>
       </c>
       <c r="O87" t="n">
-        <v>1493.59</v>
+        <v>2</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001422445705865521</v>
+        <v>0.0001570695869176019</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.5</v>
+        <v>11.21</v>
       </c>
       <c r="F88" t="n">
-        <v>777341247</v>
+        <v>821035373</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>51235924</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>11.2</v>
       </c>
       <c r="J88" t="n">
-        <v>1.48</v>
+        <v>11.2</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.07515399015466895</v>
+        <v>0.004404</v>
       </c>
       <c r="L88" t="n">
-        <v>-4.76557</v>
+        <v>0.03932</v>
       </c>
       <c r="M88" t="n">
-        <v>518772101.2826915</v>
+        <v>73267727.74824999</v>
       </c>
       <c r="N88" t="n">
-        <v>533532274.5626915</v>
+        <v>73267727.74824999</v>
       </c>
       <c r="O88" t="n">
-        <v>13.53</v>
+        <v>11.21</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>46274.55208333334</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001283923932455982</v>
+        <v>0.0001529305085384921</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="F89" t="n">
-        <v>774942361</v>
+        <v>795802898</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>46346492</v>
       </c>
       <c r="I89" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="J89" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="K89" t="n">
-        <v>0.000412</v>
+        <v>0.04194235</v>
       </c>
       <c r="L89" t="n">
-        <v>0.03695</v>
+        <v>2.81102</v>
       </c>
       <c r="M89" t="n">
-        <v>694720859.594534</v>
+        <v>518772101.2826915</v>
       </c>
       <c r="N89" t="n">
-        <v>694720859.594534</v>
+        <v>533532274.5626915</v>
       </c>
       <c r="O89" t="n">
-        <v>1.12</v>
+        <v>13.53</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>46273.57650462963</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001268736687931545</v>
+        <v>0.0001371383819930541</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>janus-henderson-anemoy-treasury-fund</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>jtrsy</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Janus Henderson Anemoy Treasury Fund</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.02847836</v>
+        <v>1.12</v>
       </c>
       <c r="F90" t="n">
-        <v>745127725</v>
+        <v>774942361</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>8316097</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.02942653</v>
+        <v>1.12</v>
       </c>
       <c r="J90" t="n">
-        <v>0.02842985</v>
+        <v>1.12</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.000771433410653052</v>
+        <v>0.000412</v>
       </c>
       <c r="L90" t="n">
-        <v>-2.63739</v>
+        <v>0.03695</v>
       </c>
       <c r="M90" t="n">
-        <v>26149385802</v>
+        <v>694720859.594534</v>
       </c>
       <c r="N90" t="n">
-        <v>100000000000</v>
+        <v>694720859.594534</v>
       </c>
       <c r="O90" t="n">
-        <v>0.04323745</v>
+        <v>1.12</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>46273.57650462963</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001079981504342541</v>
+        <v>0.0001240824990442038</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2.28</v>
+        <v>0.02858139</v>
       </c>
       <c r="F91" t="n">
-        <v>728475801</v>
+        <v>747820183</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>116065438</v>
+        <v>7198193</v>
       </c>
       <c r="I91" t="n">
-        <v>2.42</v>
+        <v>0.02896755</v>
       </c>
       <c r="J91" t="n">
-        <v>2.22</v>
+        <v>0.02823008</v>
       </c>
       <c r="K91" t="n">
-        <v>0.03228065</v>
+        <v>-0.000234992631568967</v>
       </c>
       <c r="L91" t="n">
-        <v>1.44839</v>
+        <v>-0.81548</v>
       </c>
       <c r="M91" t="n">
-        <v>320181710.9001322</v>
+        <v>26164588134</v>
       </c>
       <c r="N91" t="n">
-        <v>331857365.1830818</v>
+        <v>100000000000</v>
       </c>
       <c r="O91" t="n">
-        <v>43.96</v>
+        <v>0.04323745</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>9.745588866815323e-05</v>
+        <v>0.0001071076732625913</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1.049</v>
+        <v>2.3</v>
       </c>
       <c r="F92" t="n">
-        <v>711356516</v>
+        <v>737920504</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>72253708</v>
       </c>
       <c r="I92" t="n">
-        <v>1.049</v>
+        <v>2.32</v>
       </c>
       <c r="J92" t="n">
-        <v>1.048</v>
+        <v>2.26</v>
       </c>
       <c r="K92" t="n">
-        <v>0.00054</v>
+        <v>0.01464921</v>
       </c>
       <c r="L92" t="n">
-        <v>0.05152</v>
+        <v>0.63969</v>
       </c>
       <c r="M92" t="n">
-        <v>678322870.428591</v>
+        <v>320184235.914524</v>
       </c>
       <c r="N92" t="n">
-        <v>678322870.428591</v>
+        <v>331857365.1830818</v>
       </c>
       <c r="O92" t="n">
-        <v>1.049</v>
+        <v>43.96</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46273.57650462963</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>8.661774265460646e-05</v>
+        <v>0.0001009118092608548</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.998914</v>
+        <v>1.049</v>
       </c>
       <c r="F93" t="n">
-        <v>698237996</v>
+        <v>713208264</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>6256072</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9990019999999999</v>
+        <v>1.049</v>
       </c>
       <c r="J93" t="n">
-        <v>0.998335</v>
+        <v>1.049</v>
       </c>
       <c r="K93" t="n">
-        <v>-2.5992284555132e-05</v>
+        <v>0.00069</v>
       </c>
       <c r="L93" t="n">
-        <v>-0.00105</v>
+        <v>0.06583</v>
       </c>
       <c r="M93" t="n">
-        <v>699000000</v>
+        <v>679991365.72342</v>
       </c>
       <c r="N93" t="n">
-        <v>699000000</v>
+        <v>679991365.72342</v>
       </c>
       <c r="O93" t="n">
-        <v>1.03</v>
+        <v>1.049</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>46274.47222222222</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>7.831246382773762e-05</v>
+        <v>8.54452796674941e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6703,34 +6703,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.839761</v>
+        <v>0.846367</v>
       </c>
       <c r="F94" t="n">
-        <v>694208191</v>
+        <v>700157404</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>95240553</v>
+        <v>82587362</v>
       </c>
       <c r="I94" t="n">
         <v>0.875856</v>
       </c>
       <c r="J94" t="n">
-        <v>0.834418</v>
+        <v>0.825248</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.006253721505121712</v>
+        <v>0.00459559</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.75374</v>
+        <v>0.54594</v>
       </c>
       <c r="M94" t="n">
-        <v>827212607</v>
+        <v>827250406</v>
       </c>
       <c r="N94" t="n">
-        <v>1957077108</v>
+        <v>1957074626</v>
       </c>
       <c r="O94" t="n">
         <v>236.84</v>
@@ -6739,220 +6739,220 @@
         <v>44287.22894675926</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>7.576121154143473e-05</v>
+        <v>7.72772013221556e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00803746</v>
+        <v>0.998395</v>
       </c>
       <c r="F95" t="n">
-        <v>691179147</v>
+        <v>697878223</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>28983117</v>
+        <v>7860476</v>
       </c>
       <c r="I95" t="n">
-        <v>0.008128710000000001</v>
+        <v>0.9990019999999999</v>
       </c>
       <c r="J95" t="n">
-        <v>0.00723066</v>
+        <v>0.998297</v>
       </c>
       <c r="K95" t="n">
-        <v>0.00071256</v>
+        <v>1.54e-06</v>
       </c>
       <c r="L95" t="n">
-        <v>9.76979</v>
+        <v>0.00015</v>
       </c>
       <c r="M95" t="n">
-        <v>85985041177</v>
+        <v>699000000</v>
       </c>
       <c r="N95" t="n">
-        <v>85985041177</v>
+        <v>699000000</v>
       </c>
       <c r="O95" t="n">
-        <v>0.280991</v>
+        <v>1.03</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>7.384353675808613e-05</v>
+        <v>7.58507413822584e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6.49</v>
+        <v>0.00775709</v>
       </c>
       <c r="F96" t="n">
-        <v>648923864</v>
+        <v>666994072</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>176423220</v>
+        <v>22769195</v>
       </c>
       <c r="I96" t="n">
-        <v>6.69</v>
+        <v>0.008159120000000001</v>
       </c>
       <c r="J96" t="n">
-        <v>6.19</v>
+        <v>0.00760247</v>
       </c>
       <c r="K96" t="n">
-        <v>0.109813</v>
+        <v>1.085e-05</v>
       </c>
       <c r="L96" t="n">
-        <v>1.65802</v>
+        <v>0.14009</v>
       </c>
       <c r="M96" t="n">
-        <v>100000000</v>
+        <v>85985041177</v>
       </c>
       <c r="N96" t="n">
-        <v>100000000</v>
+        <v>85985041177</v>
       </c>
       <c r="O96" t="n">
-        <v>52.62</v>
+        <v>0.280991</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>4.709189806536384e-05</v>
+        <v>5.652142783531482e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>aerodrome-finance</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>aero</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aerodrome Finance</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.618683</v>
+        <v>6.27</v>
       </c>
       <c r="F97" t="n">
-        <v>609790353</v>
+        <v>627155056</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>106777297</v>
+        <v>123250609</v>
       </c>
       <c r="I97" t="n">
-        <v>0.672887</v>
+        <v>6.56</v>
       </c>
       <c r="J97" t="n">
-        <v>0.603402</v>
+        <v>6.2</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.02714051535917894</v>
+        <v>0.07042</v>
       </c>
       <c r="L97" t="n">
-        <v>-4.10827</v>
+        <v>1.1356</v>
       </c>
       <c r="M97" t="n">
-        <v>986551134.21137</v>
+        <v>100000000</v>
       </c>
       <c r="N97" t="n">
-        <v>1973685089.485853</v>
+        <v>100000000</v>
       </c>
       <c r="O97" t="n">
-        <v>2.32</v>
+        <v>52.62</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45633.25043981482</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>2.231663985564664e-05</v>
+        <v>3.158757643477926e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6971,28 +6971,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="F98" t="n">
-        <v>608498176</v>
+        <v>612054100</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>168476411</v>
+        <v>158108993</v>
       </c>
       <c r="I98" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="J98" t="n">
         <v>2.2</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.1024457292935086</v>
+        <v>0.01846282</v>
       </c>
       <c r="L98" t="n">
-        <v>-4.53212</v>
+        <v>0.83077</v>
       </c>
       <c r="M98" t="n">
         <v>273137120.287634</v>
@@ -7007,19 +7007,19 @@
         <v>45676.16011574074</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.149856813119397e-05</v>
+        <v>2.213641446556732e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7038,34 +7038,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.076667</v>
+        <v>0.076723</v>
       </c>
       <c r="F99" t="n">
-        <v>603662939</v>
+        <v>603855340</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>11086330</v>
+        <v>11243163</v>
       </c>
       <c r="I99" t="n">
-        <v>0.07818600000000001</v>
+        <v>0.077597</v>
       </c>
       <c r="J99" t="n">
-        <v>0.07642400000000001</v>
+        <v>0.075156</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.001411613412245452</v>
+        <v>-0.000764723909802631</v>
       </c>
       <c r="L99" t="n">
-        <v>-1.78999</v>
+        <v>-0.9869</v>
       </c>
       <c r="M99" t="n">
-        <v>7870571183.322329</v>
+        <v>7870576151.856974</v>
       </c>
       <c r="N99" t="n">
-        <v>9939511382.890877</v>
+        <v>9939516139.411463</v>
       </c>
       <c r="O99" t="n">
         <v>0.450785</v>
@@ -7074,19 +7074,19 @@
         <v>43450.66666666666</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1.843740029526485e-05</v>
+        <v>1.700509637506391e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7105,28 +7105,28 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.603808</v>
+        <v>0.619139</v>
       </c>
       <c r="F100" t="n">
-        <v>582015576</v>
+        <v>597685497</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>62513064</v>
+        <v>72496974</v>
       </c>
       <c r="I100" t="n">
-        <v>0.622841</v>
+        <v>0.639674</v>
       </c>
       <c r="J100" t="n">
-        <v>0.575167</v>
+        <v>0.589762</v>
       </c>
       <c r="K100" t="n">
-        <v>0.00337831</v>
+        <v>0.03383979</v>
       </c>
       <c r="L100" t="n">
-        <v>0.52874</v>
+        <v>5.78163</v>
       </c>
       <c r="M100" t="n">
         <v>965350000</v>
@@ -7141,77 +7141,77 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>4.73254749316186e-06</v>
+        <v>1.314360671059442e-05</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260909T013012Z-1a3f96</t>
+          <t>20260909T133820Z-e822fb</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>xdce-crowd-sale</t>
+          <t>aptos</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>xdc</t>
+          <t>apt</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>XDC Network</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.02880025</v>
+        <v>0.671587</v>
       </c>
       <c r="F101" t="n">
-        <v>574540328</v>
+        <v>576684796</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>8883651</v>
+        <v>87233923</v>
       </c>
       <c r="I101" t="n">
-        <v>0.02963929</v>
+        <v>0.667743</v>
       </c>
       <c r="J101" t="n">
-        <v>0.02824106</v>
+        <v>0.63751</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.00052301893692594</v>
+        <v>0.03328463</v>
       </c>
       <c r="L101" t="n">
-        <v>-1.79779</v>
+        <v>5.21455</v>
       </c>
       <c r="M101" t="n">
-        <v>19946688440</v>
+        <v>858689075.0815318</v>
       </c>
       <c r="N101" t="n">
-        <v>38065686425.1</v>
+        <v>1208439062.296961</v>
       </c>
       <c r="O101" t="n">
-        <v>0.192754</v>
+        <v>19.92</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>44428.86097222222</v>
+        <v>44952.26755787037</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46274.06064814814</v>
+        <v>46274.56631944444</v>
       </c>
       <c r="R101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>79593</v>
+        <v>76869</v>
       </c>
       <c r="F2" t="n">
-        <v>1598364983123</v>
+        <v>1543780270779</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>34113961073</v>
+        <v>34152452226</v>
       </c>
       <c r="I2" t="n">
-        <v>79701</v>
+        <v>79351</v>
       </c>
       <c r="J2" t="n">
-        <v>77888</v>
+        <v>76748</v>
       </c>
       <c r="K2" t="n">
-        <v>1519.73</v>
+        <v>-2710.455693790631</v>
       </c>
       <c r="L2" t="n">
-        <v>1.94656</v>
+        <v>-3.40595</v>
       </c>
       <c r="M2" t="n">
-        <v>20081850</v>
+        <v>20082225</v>
       </c>
       <c r="N2" t="n">
-        <v>20081881</v>
+        <v>20082365</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2515.98</v>
+        <v>2417.76</v>
       </c>
       <c r="F3" t="n">
-        <v>307031455725</v>
+        <v>295019194043</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>12320334940</v>
+        <v>13585995467</v>
       </c>
       <c r="I3" t="n">
-        <v>2521.51</v>
+        <v>2513.05</v>
       </c>
       <c r="J3" t="n">
-        <v>2457.39</v>
+        <v>2413.62</v>
       </c>
       <c r="K3" t="n">
-        <v>61.6</v>
+        <v>-96.6624874395302</v>
       </c>
       <c r="L3" t="n">
-        <v>2.50979</v>
+        <v>-3.84432</v>
       </c>
       <c r="M3" t="n">
-        <v>122032627.1379582</v>
+        <v>122035556.7865035</v>
       </c>
       <c r="N3" t="n">
-        <v>122032627.1379582</v>
+        <v>122035556.7865035</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1917993586821735</v>
+        <v>0.1908151463199907</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,34 +673,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999827</v>
+        <v>0.999689</v>
       </c>
       <c r="F4" t="n">
-        <v>183428486563</v>
+        <v>183399747382</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>52915294657</v>
+        <v>57650362193</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999995</v>
+        <v>0.999919</v>
       </c>
       <c r="J4" t="n">
-        <v>0.99956</v>
+        <v>0.9995579999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002526</v>
+        <v>-0.000115082843732628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02527</v>
+        <v>-0.01151</v>
       </c>
       <c r="M4" t="n">
-        <v>183460193480.142</v>
+        <v>183460843383.6048</v>
       </c>
       <c r="N4" t="n">
-        <v>188927139311.3062</v>
+        <v>188927789268.3162</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1144405688528694</v>
+        <v>0.118486846457935</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>750.04</v>
+        <v>706.52</v>
       </c>
       <c r="F5" t="n">
-        <v>99876830887</v>
+        <v>94081938222</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>923039010</v>
+        <v>1262140120</v>
       </c>
       <c r="I5" t="n">
-        <v>757.36</v>
+        <v>746.28</v>
       </c>
       <c r="J5" t="n">
-        <v>746.05</v>
+        <v>704.86</v>
       </c>
       <c r="K5" t="n">
-        <v>2.88</v>
+        <v>-43.96882713677849</v>
       </c>
       <c r="L5" t="n">
-        <v>0.38481</v>
+        <v>-5.85871</v>
       </c>
       <c r="M5" t="n">
-        <v>133161358.02</v>
+        <v>133161225.51</v>
       </c>
       <c r="N5" t="n">
-        <v>133161354.33</v>
+        <v>133161220.23</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06214850002029332</v>
+        <v>0.06060978760127664</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>90039637527</v>
+        <v>85090865143</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2699115770</v>
+        <v>2406497456</v>
       </c>
       <c r="I6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04390142</v>
+        <v>-0.07915296347920031</v>
       </c>
       <c r="L6" t="n">
-        <v>3.15584</v>
+        <v>-5.51462</v>
       </c>
       <c r="M6" t="n">
         <v>62744504852</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0559917436024999</v>
+        <v>0.0547836609791422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999918</v>
+        <v>0.999729</v>
       </c>
       <c r="F7" t="n">
-        <v>74323444836</v>
+        <v>74294024258</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>14970939745</v>
+        <v>16283054604</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99979</v>
+        <v>0.999698</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00010693</v>
+        <v>-0.000171072760730695</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0107</v>
+        <v>-0.01711</v>
       </c>
       <c r="M7" t="n">
-        <v>74329561446.62111</v>
+        <v>74315470373.78728</v>
       </c>
       <c r="N7" t="n">
-        <v>74328339343.75978</v>
+        <v>74331256693.94714</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04615552643439572</v>
+        <v>0.04778741463987383</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.41</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>61211194221</v>
+        <v>58279078429</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2888831094</v>
+        <v>3474521512</v>
       </c>
       <c r="I8" t="n">
-        <v>105.02</v>
+        <v>104.12</v>
       </c>
       <c r="J8" t="n">
-        <v>102.47</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>2.02</v>
+        <v>-5.139863338806535</v>
       </c>
       <c r="L8" t="n">
-        <v>1.97109</v>
+        <v>-4.91663</v>
       </c>
       <c r="M8" t="n">
-        <v>586250495.4491609</v>
+        <v>586335632.9426919</v>
       </c>
       <c r="N8" t="n">
-        <v>633736725.8982507</v>
+        <v>633830911.2985152</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03794902584309118</v>
+        <v>0.03740988779446246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338701</v>
+        <v>0.338163</v>
       </c>
       <c r="F9" t="n">
-        <v>32156956766</v>
+        <v>32108021382</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>332831706</v>
+        <v>386070975</v>
       </c>
       <c r="I9" t="n">
-        <v>0.339911</v>
+        <v>0.340659</v>
       </c>
       <c r="J9" t="n">
-        <v>0.337749</v>
+        <v>0.338005</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.553672881799301e-05</v>
+        <v>-0.00057910542445333</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0223</v>
+        <v>-0.17096</v>
       </c>
       <c r="M9" t="n">
-        <v>94942033418.39418</v>
+        <v>94943377255.82779</v>
       </c>
       <c r="N9" t="n">
-        <v>94942027879.98538</v>
+        <v>94943389284.71849</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01976499139658666</v>
+        <v>0.02045130111062643</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.035</v>
+        <v>1.027</v>
       </c>
       <c r="F10" t="n">
-        <v>23070630036</v>
+        <v>22977477871</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>34613377</v>
+        <v>115171089</v>
       </c>
       <c r="I10" t="n">
-        <v>1.051</v>
+        <v>1.042</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.019</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.008331250492084719</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.80491</v>
       </c>
       <c r="M10" t="n">
-        <v>22290610113.348</v>
+        <v>22379027660.478</v>
       </c>
       <c r="N10" t="n">
-        <v>22290610113.348</v>
+        <v>22379027660.478</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01407817622869863</v>
+        <v>0.01453479902499212</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1280.44</v>
+        <v>1174.12</v>
       </c>
       <c r="F11" t="n">
-        <v>21667506605</v>
+        <v>19885889479</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1394137200</v>
+        <v>1377712454</v>
       </c>
       <c r="I11" t="n">
-        <v>1275.68</v>
+        <v>1293.92</v>
       </c>
       <c r="J11" t="n">
-        <v>1144.42</v>
+        <v>1188.47</v>
       </c>
       <c r="K11" t="n">
-        <v>132.62</v>
+        <v>-90.49896540877694</v>
       </c>
       <c r="L11" t="n">
-        <v>11.55438</v>
+        <v>-7.15622</v>
       </c>
       <c r="M11" t="n">
         <v>16921867.3530448</v>
       </c>
       <c r="N11" t="n">
-        <v>16923028.2905448</v>
+        <v>16924839.2280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01320001018350405</v>
+        <v>0.01253148025791606</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>86.54000000000001</v>
+        <v>81.09</v>
       </c>
       <c r="F12" t="n">
-        <v>19250478039</v>
+        <v>18036831345</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1058509523</v>
+        <v>1321535350</v>
       </c>
       <c r="I12" t="n">
-        <v>86.98</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>82.44</v>
+        <v>80.34</v>
       </c>
       <c r="K12" t="n">
-        <v>4.04</v>
+        <v>-5.605079227248268</v>
       </c>
       <c r="L12" t="n">
-        <v>4.89902</v>
+        <v>-6.46526</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01168727625715673</v>
+        <v>0.01133330883547114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.091074</v>
+        <v>0.083634</v>
       </c>
       <c r="F13" t="n">
-        <v>14193446782</v>
+        <v>13029160774</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>811744469</v>
+        <v>945647801</v>
       </c>
       <c r="I13" t="n">
-        <v>0.091515</v>
+        <v>0.09052300000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.089</v>
+        <v>0.083463</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00247604</v>
+        <v>-0.007554012353101672</v>
       </c>
       <c r="L13" t="n">
-        <v>2.79468</v>
+        <v>-8.284000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>155844386383.7052</v>
+        <v>155856586383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155844716383.7052</v>
+        <v>171569863126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008522256672087119</v>
+        <v>0.008088387726251641</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,31 +1343,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01638259</v>
+        <v>0.0158577</v>
       </c>
       <c r="F14" t="n">
-        <v>11618735510</v>
+        <v>11244080062</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>39125793</v>
+        <v>30442537</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01675249</v>
+        <v>0.01646211</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01591912</v>
+        <v>0.01579631</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000182873056705439</v>
+        <v>-0.000524735521837818</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.10394</v>
+        <v>-3.20304</v>
       </c>
       <c r="M14" t="n">
-        <v>709212380117.7289</v>
+        <v>709212596238.4149</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1379,19 +1379,19 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006910834636579719</v>
+        <v>0.006931673041868425</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999939</v>
+        <v>0.99982</v>
       </c>
       <c r="F15" t="n">
-        <v>9847281876</v>
+        <v>9855532483</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>226871382</v>
+        <v>152958451</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999628</v>
+        <v>0.999687</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00022649</v>
+        <v>-0.000130622034676287</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02266</v>
+        <v>-0.01306</v>
       </c>
       <c r="M15" t="n">
-        <v>9847882071.139385</v>
+        <v>9857520169.204882</v>
       </c>
       <c r="N15" t="n">
-        <v>9851780066.236448</v>
+        <v>9838691287.558218</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1446,153 +1446,153 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005802143556631993</v>
+        <v>0.006031907914276781</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>82.25</v>
+        <v>502.71</v>
       </c>
       <c r="F16" t="n">
-        <v>9699044618</v>
+        <v>9437409909</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>99572519</v>
+        <v>142179940</v>
       </c>
       <c r="I16" t="n">
-        <v>82.52</v>
+        <v>518.34</v>
       </c>
       <c r="J16" t="n">
-        <v>79.16</v>
+        <v>498.54</v>
       </c>
       <c r="K16" t="n">
-        <v>2.97</v>
+        <v>3.76</v>
       </c>
       <c r="L16" t="n">
-        <v>3.74938</v>
+        <v>0.75295</v>
       </c>
       <c r="M16" t="n">
-        <v>117919967</v>
+        <v>18802821.25212499</v>
       </c>
       <c r="N16" t="n">
-        <v>293569966</v>
+        <v>18802833.85203534</v>
       </c>
       <c r="O16" t="n">
-        <v>82.52</v>
+        <v>797.73</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46274.03356481482</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005709367024124392</v>
+        <v>0.00576096861278378</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>498.98</v>
+        <v>79.34</v>
       </c>
       <c r="F17" t="n">
-        <v>9382098083</v>
+        <v>9350661300</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>115458264</v>
+        <v>108435650</v>
       </c>
       <c r="I17" t="n">
-        <v>507.62</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>491.57</v>
+        <v>79.22</v>
       </c>
       <c r="K17" t="n">
-        <v>1.62</v>
+        <v>-2.906928747854607</v>
       </c>
       <c r="L17" t="n">
-        <v>0.32548</v>
+        <v>-3.53455</v>
       </c>
       <c r="M17" t="n">
-        <v>18802391.73259455</v>
+        <v>117882016</v>
       </c>
       <c r="N17" t="n">
-        <v>18802409.73255417</v>
+        <v>293532015</v>
       </c>
       <c r="O17" t="n">
-        <v>797.73</v>
+        <v>82.52</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>46274.03356481482</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005511001236033525</v>
+        <v>0.00570475637027532</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.19</v>
+        <v>11.67</v>
       </c>
       <c r="F18" t="n">
-        <v>9120564871</v>
+        <v>8732590784</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>7088637519</v>
+        <v>4027997415</v>
       </c>
       <c r="I18" t="n">
-        <v>12.77</v>
+        <v>12.15</v>
       </c>
       <c r="J18" t="n">
-        <v>11.98</v>
+        <v>11.6</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2184760733722584</v>
+        <v>-0.5381755019183387</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.76047</v>
+        <v>-4.40724</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005347316715203172</v>
+        <v>0.005304252775656058</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.19</v>
+        <v>9.18</v>
       </c>
       <c r="F19" t="n">
-        <v>8456838824</v>
+        <v>8447958234</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>163052</v>
+        <v>103636</v>
       </c>
       <c r="I19" t="n">
-        <v>9.26</v>
+        <v>9.23</v>
       </c>
       <c r="J19" t="n">
         <v>9.17</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01153524</v>
+        <v>-0.009111009906101586</v>
       </c>
       <c r="L19" t="n">
-        <v>0.12563</v>
+        <v>-0.09911</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004931913718639129</v>
+        <v>0.005119813692299675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.220656</v>
+        <v>0.209835</v>
       </c>
       <c r="F20" t="n">
-        <v>8276912044</v>
+        <v>7871290286</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>578223441</v>
+        <v>462172278</v>
       </c>
       <c r="I20" t="n">
-        <v>0.231823</v>
+        <v>0.219716</v>
       </c>
       <c r="J20" t="n">
-        <v>0.216151</v>
+        <v>0.208156</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00384314</v>
+        <v>-0.01121438589498572</v>
       </c>
       <c r="L20" t="n">
-        <v>1.77256</v>
+        <v>-5.07325</v>
       </c>
       <c r="M20" t="n">
         <v>37510482444.2993</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004819303818949416</v>
+        <v>0.004746138553141746</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.189212</v>
+        <v>0.177265</v>
       </c>
       <c r="F21" t="n">
-        <v>6585243621</v>
+        <v>6168073836</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>168338211</v>
+        <v>177475184</v>
       </c>
       <c r="I21" t="n">
-        <v>0.19354</v>
+        <v>0.188573</v>
       </c>
       <c r="J21" t="n">
-        <v>0.186697</v>
+        <v>0.176372</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00201514</v>
+        <v>-0.01210439609112118</v>
       </c>
       <c r="L21" t="n">
-        <v>1.07648</v>
+        <v>-6.39196</v>
       </c>
       <c r="M21" t="n">
-        <v>34803513020.29381</v>
+        <v>34807089044.92414</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1848,19 +1848,19 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003760547521402802</v>
+        <v>0.003642471102614695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,34 +1879,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>259.77</v>
+        <v>230.08</v>
       </c>
       <c r="F22" t="n">
-        <v>5217902214</v>
+        <v>4620214173</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>149663820</v>
+        <v>240408727</v>
       </c>
       <c r="I22" t="n">
-        <v>261.18</v>
+        <v>259.1</v>
       </c>
       <c r="J22" t="n">
-        <v>253.89</v>
+        <v>238.03</v>
       </c>
       <c r="K22" t="n">
-        <v>6.49</v>
+        <v>-29.90268411409812</v>
       </c>
       <c r="L22" t="n">
-        <v>2.56148</v>
+        <v>-11.50199</v>
       </c>
       <c r="M22" t="n">
-        <v>20086790.52165078</v>
+        <v>20087203.02165078</v>
       </c>
       <c r="N22" t="n">
-        <v>20086793.64665078</v>
+        <v>20087540.52165078</v>
       </c>
       <c r="O22" t="n">
         <v>3785.82</v>
@@ -1915,19 +1915,19 @@
         <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002904776197735139</v>
+        <v>0.002639473316844796</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,34 +1946,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.999972</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>4586719903</v>
+        <v>4594324910</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>286655800</v>
+        <v>286425661</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.999723</v>
+        <v>0.9997</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00011842</v>
+        <v>5.839e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01184</v>
+        <v>0.00584</v>
       </c>
       <c r="M23" t="n">
-        <v>4586849364.832944</v>
+        <v>4595256677.058527</v>
       </c>
       <c r="N23" t="n">
-        <v>4586849364.832944</v>
+        <v>4586939586.962975</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -1982,19 +1982,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002509741191119498</v>
+        <v>0.002622697329922386</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.99977</v>
+        <v>0.999499</v>
       </c>
       <c r="F24" t="n">
-        <v>4455091671</v>
+        <v>4499423114</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>94194190</v>
+        <v>130660631</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9999479999999999</v>
+        <v>0.999881</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999565</v>
+        <v>0.999414</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00019246</v>
+        <v>-0.000206316856677824</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01925</v>
+        <v>-0.02064</v>
       </c>
       <c r="M24" t="n">
-        <v>4456117739.295266</v>
+        <v>4501768261.240666</v>
       </c>
       <c r="N24" t="n">
-        <v>4456117739.295266</v>
+        <v>4501768261.240666</v>
       </c>
       <c r="O24" t="n">
         <v>1.034</v>
@@ -2049,19 +2049,19 @@
         <v>46000.38208333333</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002427359669025598</v>
+        <v>0.002561201902701871</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9994729999999999</v>
+        <v>0.999355</v>
       </c>
       <c r="F25" t="n">
-        <v>4277793603</v>
+        <v>4277305044</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1033051569</v>
+        <v>1116623882</v>
       </c>
       <c r="I25" t="n">
-        <v>0.999799</v>
+        <v>0.999574</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999325</v>
+        <v>0.999229</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.5995687306056e-05</v>
+        <v>-7.4809622211958e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0036</v>
+        <v>-0.00749</v>
       </c>
       <c r="M25" t="n">
-        <v>4280049884.324213</v>
+        <v>4280219884.620713</v>
       </c>
       <c r="N25" t="n">
-        <v>4280049884.324213</v>
+        <v>4280219884.620713</v>
       </c>
       <c r="O25" t="n">
         <v>1.048</v>
@@ -2116,19 +2116,19 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002316394988544683</v>
+        <v>0.002417271585428991</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,34 +2147,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>54.42</v>
+        <v>52.07</v>
       </c>
       <c r="F26" t="n">
-        <v>4222703386</v>
+        <v>4040002355</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>306495719</v>
+        <v>291648539</v>
       </c>
       <c r="I26" t="n">
-        <v>55.2</v>
+        <v>54.52</v>
       </c>
       <c r="J26" t="n">
-        <v>53.64</v>
+        <v>51.8</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.518672100140158</v>
+        <v>-2.230848443142769</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.94401</v>
+        <v>-4.10858</v>
       </c>
       <c r="M26" t="n">
-        <v>77587829.33440471</v>
+        <v>77591379.34298518</v>
       </c>
       <c r="N26" t="n">
-        <v>77591373.09434305</v>
+        <v>77594648.10236211</v>
       </c>
       <c r="O26" t="n">
         <v>410.26</v>
@@ -2183,555 +2183,555 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002281915942066697</v>
+        <v>0.002263501784901381</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.72</v>
+        <v>0.100947</v>
       </c>
       <c r="F27" t="n">
-        <v>4185898770</v>
+        <v>3995411244</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>523424543</v>
+        <v>10736871</v>
       </c>
       <c r="I27" t="n">
-        <v>6.95</v>
+        <v>0.105557</v>
       </c>
       <c r="J27" t="n">
-        <v>6.58</v>
+        <v>0.099992</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1994994738542051</v>
+        <v>-0.003982112945947455</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.88455</v>
+        <v>-3.79506</v>
       </c>
       <c r="M27" t="n">
-        <v>623212423.7271129</v>
+        <v>39565437161.70294</v>
       </c>
       <c r="N27" t="n">
-        <v>890460420.0329479</v>
+        <v>39566001895.17695</v>
       </c>
       <c r="O27" t="n">
-        <v>44.92</v>
+        <v>0.194152</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002258881215852631</v>
+        <v>0.002234607185043836</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.105232</v>
+        <v>1.34</v>
       </c>
       <c r="F28" t="n">
-        <v>4162833873</v>
+        <v>3730580854</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>10056275</v>
+        <v>33649209</v>
       </c>
       <c r="I28" t="n">
-        <v>0.110029</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.103497</v>
+        <v>1.35</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00191148</v>
+        <v>-0.05871265632901279</v>
       </c>
       <c r="L28" t="n">
-        <v>1.85004</v>
+        <v>-4.2004</v>
       </c>
       <c r="M28" t="n">
-        <v>39558504215.70418</v>
+        <v>2785783668.754508</v>
       </c>
       <c r="N28" t="n">
-        <v>39559086607.84083</v>
+        <v>5246646343.198145</v>
       </c>
       <c r="O28" t="n">
-        <v>0.194152</v>
+        <v>8.25</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002244445700819663</v>
+        <v>0.002062999705939589</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.4</v>
+        <v>5.87</v>
       </c>
       <c r="F29" t="n">
-        <v>3890349973</v>
+        <v>3655422610</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>34199995</v>
+        <v>685422145</v>
       </c>
       <c r="I29" t="n">
-        <v>1.41</v>
+        <v>6.67</v>
       </c>
       <c r="J29" t="n">
-        <v>1.38</v>
+        <v>5.86</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01213058</v>
+        <v>-0.8323606899828881</v>
       </c>
       <c r="L29" t="n">
-        <v>0.87608</v>
+        <v>-12.41337</v>
       </c>
       <c r="M29" t="n">
-        <v>2785233859.772825</v>
+        <v>623212423.7271129</v>
       </c>
       <c r="N29" t="n">
-        <v>5246090978.585007</v>
+        <v>890460420.0329479</v>
       </c>
       <c r="O29" t="n">
-        <v>8.25</v>
+        <v>44.92</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002073907526090689</v>
+        <v>0.002014297905565614</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.07893600000000001</v>
+        <v>0.999946</v>
       </c>
       <c r="F30" t="n">
-        <v>3459896337</v>
+        <v>3311944587</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>64047127</v>
+        <v>1289827691</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08085199999999999</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.078128</v>
+        <v>0.999799</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.000481778053392432</v>
+        <v>4.556e-05</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.60664</v>
+        <v>0.00456</v>
       </c>
       <c r="M30" t="n">
-        <v>43831559703.02959</v>
+        <v>3312225593.434751</v>
       </c>
       <c r="N30" t="n">
-        <v>50000000000</v>
+        <v>3312194614.574223</v>
       </c>
       <c r="O30" t="n">
-        <v>0.569229</v>
+        <v>1.65</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001804501600129962</v>
+        <v>0.001791727536452234</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>0.075183</v>
       </c>
       <c r="F31" t="n">
-        <v>3455358179</v>
+        <v>3295094622</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>243337000</v>
+        <v>62173402</v>
       </c>
       <c r="I31" t="n">
-        <v>8.1</v>
+        <v>0.07882500000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>7.9</v>
+        <v>0.074904</v>
       </c>
       <c r="K31" t="n">
-        <v>0.109902</v>
+        <v>-0.003801348480689221</v>
       </c>
       <c r="L31" t="n">
-        <v>1.39242</v>
+        <v>-4.81282</v>
       </c>
       <c r="M31" t="n">
-        <v>431771961.1772119</v>
+        <v>43831559702.15789</v>
       </c>
       <c r="N31" t="n">
-        <v>463441061.1772119</v>
+        <v>50000000000</v>
       </c>
       <c r="O31" t="n">
-        <v>144.96</v>
+        <v>0.569229</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001801661325229493</v>
+        <v>0.001780808925424833</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.6</v>
+        <v>7.58</v>
       </c>
       <c r="F32" t="n">
-        <v>3390650895</v>
+        <v>3271991963</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>635060449</v>
+        <v>248935563</v>
       </c>
       <c r="I32" t="n">
-        <v>2.63</v>
+        <v>7.96</v>
       </c>
       <c r="J32" t="n">
-        <v>2.27</v>
+        <v>7.57</v>
       </c>
       <c r="K32" t="n">
-        <v>0.332681</v>
+        <v>-0.4223569541973546</v>
       </c>
       <c r="L32" t="n">
-        <v>14.69565</v>
+        <v>-5.27981</v>
       </c>
       <c r="M32" t="n">
-        <v>1305860723</v>
+        <v>431771961.1772119</v>
       </c>
       <c r="N32" t="n">
-        <v>1305860738</v>
+        <v>463441061.1772119</v>
       </c>
       <c r="O32" t="n">
-        <v>20.44</v>
+        <v>144.96</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R32" t="b">
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001761163291749242</v>
+        <v>0.001765838630393379</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.815164</v>
+        <v>2.4</v>
       </c>
       <c r="F33" t="n">
-        <v>3339348505</v>
+        <v>3135849191</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>589105572</v>
+        <v>564680351</v>
       </c>
       <c r="I33" t="n">
-        <v>0.833475</v>
+        <v>2.65</v>
       </c>
       <c r="J33" t="n">
-        <v>0.802561</v>
+        <v>2.38</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01404872</v>
+        <v>-0.1879549365374089</v>
       </c>
       <c r="L33" t="n">
-        <v>1.75365</v>
+        <v>-7.25159</v>
       </c>
       <c r="M33" t="n">
-        <v>4096537146.540959</v>
+        <v>1305942368</v>
       </c>
       <c r="N33" t="n">
-        <v>10000000000</v>
+        <v>1305942367</v>
       </c>
       <c r="O33" t="n">
-        <v>5.35</v>
+        <v>20.44</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001729054914153965</v>
+        <v>0.001677619457732779</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.999949</v>
+        <v>0.750186</v>
       </c>
       <c r="F34" t="n">
-        <v>3320653051</v>
+        <v>3073344321</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>1261073479</v>
+        <v>507529235</v>
       </c>
       <c r="I34" t="n">
+        <v>0.814878</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.74918</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.06634578333673313</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-8.12532</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4096537146.540959</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <v>45661.62243055556</v>
+      </c>
+      <c r="Q34" s="1" t="n">
+        <v>46275.56064814814</v>
+      </c>
+      <c r="R34" t="b">
         <v>1</v>
       </c>
-      <c r="J34" t="n">
-        <v>0.999798</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-2.142112179526e-06</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-0.00021</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3320823580.23496</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3319552997.614177</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P34" s="1" t="n">
-        <v>45686.67436342593</v>
-      </c>
-      <c r="Q34" s="1" t="n">
-        <v>46274.56631944444</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
       <c r="S34" t="n">
-        <v>0.001717354081184055</v>
+        <v>0.001637116918834434</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,31 +2750,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.44e-06</v>
+        <v>5.06e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>3208258100</v>
+        <v>2982757372</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>70982951</v>
+        <v>82600247</v>
       </c>
       <c r="I35" t="n">
-        <v>5.51e-06</v>
+        <v>5.45e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>5.36e-06</v>
+        <v>5.05e-06</v>
       </c>
       <c r="K35" t="n">
-        <v>5.8784e-08</v>
+        <v>-3.90959254583e-07</v>
       </c>
       <c r="L35" t="n">
-        <v>1.09143</v>
+        <v>-7.16822</v>
       </c>
       <c r="M35" t="n">
-        <v>589239301066730.6</v>
+        <v>589239233105565.5</v>
       </c>
       <c r="N35" t="n">
         <v>589496238721205.9</v>
@@ -2786,354 +2786,354 @@
         <v>44496.82980324074</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001647009999231718</v>
+        <v>0.001578417469886619</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.059989</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>2912083031</v>
+        <v>2798177805</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>18003909</v>
+        <v>78664296</v>
       </c>
       <c r="I36" t="n">
-        <v>0.06401</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.058574</v>
+        <v>0.9997819999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>4.7e-05</v>
+        <v>0.00015498</v>
       </c>
       <c r="L36" t="n">
-        <v>0.07840999999999999</v>
+        <v>0.0155</v>
       </c>
       <c r="M36" t="n">
-        <v>48543903603.71478</v>
+        <v>2798110720.899619</v>
       </c>
       <c r="N36" t="n">
-        <v>98910623315.97723</v>
+        <v>2798110720.899618</v>
       </c>
       <c r="O36" t="n">
-        <v>0.891544</v>
+        <v>1.021</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001461644347655651</v>
+        <v>0.001458811732089596</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.999926</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>2833707619</v>
+        <v>2797063204</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>51031125</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.999729</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.00016007</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.01601</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2833916974.830228</v>
+        <v>2797063203.770449</v>
       </c>
       <c r="N37" t="n">
-        <v>2824062986.690228</v>
+        <v>2797063203.770449</v>
       </c>
       <c r="O37" t="n">
-        <v>1.021</v>
+        <v>1</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>45222.61454861111</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001412591909305673</v>
+        <v>0.001458089481641613</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.056194</v>
       </c>
       <c r="F38" t="n">
-        <v>2817664206</v>
+        <v>2728019353</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>6873930</v>
       </c>
       <c r="I38" t="n">
+        <v>0.06001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.055997</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.003858741189189184</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-6.42555</v>
+      </c>
+      <c r="M38" t="n">
+        <v>48545965688.4151</v>
+      </c>
+      <c r="N38" t="n">
+        <v>98912619318.48181</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.891544</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>44523.66666666666</v>
+      </c>
+      <c r="Q38" s="1" t="n">
+        <v>46275.56064814814</v>
+      </c>
+      <c r="R38" t="b">
         <v>1</v>
       </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2817664205.670449</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2817664205.670449</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" s="1" t="n">
-        <v>45699.87511574074</v>
-      </c>
-      <c r="Q38" s="1" t="n">
-        <v>46274.56631944444</v>
-      </c>
-      <c r="R38" t="b">
-        <v>0</v>
-      </c>
       <c r="S38" t="n">
-        <v>0.001402550896352456</v>
+        <v>0.001413349747588586</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tether-gold</t>
+          <t>memecore</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>xaut</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tether Gold</t>
+          <t>MemeCore</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4424.73</v>
+        <v>1.18</v>
       </c>
       <c r="F39" t="n">
-        <v>2711581738</v>
+        <v>2669935508</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>183139145</v>
+        <v>1396383</v>
       </c>
       <c r="I39" t="n">
-        <v>4411.13</v>
+        <v>1.23</v>
       </c>
       <c r="J39" t="n">
-        <v>4343.14</v>
+        <v>1.16</v>
       </c>
       <c r="K39" t="n">
-        <v>30.93</v>
+        <v>-0.01088605313397406</v>
       </c>
       <c r="L39" t="n">
-        <v>0.70395</v>
+        <v>-0.91751</v>
       </c>
       <c r="M39" t="n">
-        <v>612823.6595320001</v>
+        <v>2271210359.608458</v>
       </c>
       <c r="N39" t="n">
-        <v>707747.089</v>
+        <v>5412584786.407936</v>
       </c>
       <c r="O39" t="n">
-        <v>5504.62</v>
+        <v>5.64</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>46050.66666666666</v>
+        <v>46205.17638888889</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001336157577468424</v>
+        <v>0.001375711989259069</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>memecore</t>
+          <t>tether-gold</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>xaut</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MemeCore</t>
+          <t>Tether Gold</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1.18</v>
+        <v>4348.64</v>
       </c>
       <c r="F40" t="n">
-        <v>2689559488</v>
+        <v>2664885498</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>1456779</v>
+        <v>213897427</v>
       </c>
       <c r="I40" t="n">
-        <v>1.25</v>
+        <v>4423.18</v>
       </c>
       <c r="J40" t="n">
-        <v>1.17</v>
+        <v>4329.92</v>
       </c>
       <c r="K40" t="n">
-        <v>0.01616015</v>
+        <v>-76.37241894538511</v>
       </c>
       <c r="L40" t="n">
-        <v>1.3833</v>
+        <v>-1.72593</v>
       </c>
       <c r="M40" t="n">
-        <v>2270840076.467913</v>
+        <v>612823.6595320001</v>
       </c>
       <c r="N40" t="n">
-        <v>5412229922.975138</v>
+        <v>707747.089</v>
       </c>
       <c r="O40" t="n">
-        <v>5.64</v>
+        <v>5504.62</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>46205.17638888889</v>
+        <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001322374618848024</v>
+        <v>0.001372439632617706</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3155,7 +3155,7 @@
         <v>1.14</v>
       </c>
       <c r="F41" t="n">
-        <v>2624745730</v>
+        <v>2625074051</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
@@ -3170,171 +3170,171 @@
         <v>1.14</v>
       </c>
       <c r="K41" t="n">
-        <v>9.846e-05</v>
+        <v>9.82e-05</v>
       </c>
       <c r="L41" t="n">
-        <v>0.008659999999999999</v>
+        <v>0.00864</v>
       </c>
       <c r="M41" t="n">
-        <v>2309010956.409942</v>
+        <v>2309100302.298091</v>
       </c>
       <c r="N41" t="n">
-        <v>2309010956.409942</v>
+        <v>2309100302.298091</v>
       </c>
       <c r="O41" t="n">
         <v>1.14</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46274.53819444445</v>
+        <v>46275.53819444445</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001281809947002659</v>
+        <v>0.001346642207861573</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>ripple-usd</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>rlusd</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>Ripple USD</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>267.37</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>2566084340</v>
+        <v>2421266644</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>264998125</v>
+        <v>89384433</v>
       </c>
       <c r="I42" t="n">
-        <v>269.06</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>251.25</v>
+        <v>0.9997509999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>16.36</v>
+        <v>-4.7963836192544e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>6.51859</v>
+        <v>-0.0048</v>
       </c>
       <c r="M42" t="n">
-        <v>9597491</v>
+        <v>2421307130.10722</v>
       </c>
       <c r="N42" t="n">
-        <v>21000000</v>
+        <v>2421307130.107223</v>
       </c>
       <c r="O42" t="n">
-        <v>757.6</v>
+        <v>1.073</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>45652.11518518518</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001245095827828408</v>
+        <v>0.001214577019504439</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ripple-usd</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rlusd</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ripple USD</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>242.46</v>
       </c>
       <c r="F43" t="n">
-        <v>2437862509</v>
+        <v>2327098057</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>226230371</v>
+        <v>226976572</v>
       </c>
       <c r="I43" t="n">
+        <v>264.32</v>
+      </c>
+      <c r="J43" t="n">
+        <v>242.47</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-25.06715669403047</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-9.36999</v>
+      </c>
+      <c r="M43" t="n">
+        <v>9597491</v>
+      </c>
+      <c r="N43" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="O43" t="n">
+        <v>757.6</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <v>45358.44833333333</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>46275.56064814814</v>
+      </c>
+      <c r="R43" t="b">
         <v>1</v>
       </c>
-      <c r="J43" t="n">
-        <v>0.999768</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.00011796</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2437740048.107196</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2434600130.107194</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.073</v>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>45652.11518518518</v>
-      </c>
-      <c r="Q43" s="1" t="n">
-        <v>46274.56631944444</v>
-      </c>
-      <c r="R43" t="b">
-        <v>0</v>
-      </c>
       <c r="S43" t="n">
-        <v>0.001164846253379617</v>
+        <v>0.001153556704479872</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3353,28 +3353,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>114.34</v>
+        <v>110.34</v>
       </c>
       <c r="F44" t="n">
-        <v>2401035797</v>
+        <v>2316989762</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>20248262</v>
+        <v>19348222</v>
       </c>
       <c r="I44" t="n">
-        <v>114.99</v>
+        <v>114.86</v>
       </c>
       <c r="J44" t="n">
-        <v>113.34</v>
+        <v>110.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.2677980235424968</v>
+        <v>-4.093440089202119</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.23367</v>
+        <v>-3.577</v>
       </c>
       <c r="M44" t="n">
         <v>21000000</v>
@@ -3389,19 +3389,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001141797698049377</v>
+        <v>0.001147006629078813</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,13 +3423,13 @@
         <v>1.14</v>
       </c>
       <c r="F45" t="n">
-        <v>2204440970</v>
+        <v>2215070291</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>5112891</v>
+        <v>5442811</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00221101</v>
+        <v>-0.001645623204116653</v>
       </c>
       <c r="L45" t="n">
-        <v>0.19357</v>
+        <v>-0.14364</v>
       </c>
       <c r="M45" t="n">
-        <v>1926227461.922417</v>
+        <v>1936120771.763623</v>
       </c>
       <c r="N45" t="n">
-        <v>1926227461.922417</v>
+        <v>1936120771.763623</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001018755848759425</v>
+        <v>0.001080963817715856</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,28 +3487,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.640481</v>
+        <v>0.577569</v>
       </c>
       <c r="F46" t="n">
-        <v>2115055460</v>
+        <v>1907566627</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>30688181</v>
+        <v>28213900</v>
       </c>
       <c r="I46" t="n">
-        <v>0.652427</v>
+        <v>0.642601</v>
       </c>
       <c r="J46" t="n">
-        <v>0.622271</v>
+        <v>0.57539</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01789868</v>
+        <v>-0.06314134829896989</v>
       </c>
       <c r="L46" t="n">
-        <v>2.87491</v>
+        <v>-9.854889999999999</v>
       </c>
       <c r="M46" t="n">
         <v>3302294382.53684</v>
@@ -3523,19 +3523,19 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0009628125738627485</v>
+        <v>0.0008817044782028966</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3554,28 +3554,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.751659</v>
+        <v>0.702314</v>
       </c>
       <c r="F47" t="n">
-        <v>2032539231</v>
+        <v>1898403981</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>130939381</v>
+        <v>142200533</v>
       </c>
       <c r="I47" t="n">
-        <v>0.765651</v>
+        <v>0.7511330000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>0.746359</v>
+        <v>0.701399</v>
       </c>
       <c r="K47" t="n">
-        <v>0.00017314</v>
+        <v>-0.04892281426983136</v>
       </c>
       <c r="L47" t="n">
-        <v>0.02304</v>
+        <v>-6.5123</v>
       </c>
       <c r="M47" t="n">
         <v>2704071066.799731</v>
@@ -3590,287 +3590,287 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0009111685424936363</v>
+        <v>0.0008757671740212104</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>pax-gold</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>paxg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>PAX Gold</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>130.38</v>
+        <v>4349.66</v>
       </c>
       <c r="F48" t="n">
-        <v>2011490815</v>
+        <v>1881254849</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>188654798</v>
+        <v>146309654</v>
       </c>
       <c r="I48" t="n">
-        <v>131.05</v>
+        <v>4427.77</v>
       </c>
       <c r="J48" t="n">
-        <v>127.56</v>
+        <v>4330.22</v>
       </c>
       <c r="K48" t="n">
-        <v>2.44</v>
+        <v>-77.93827460225839</v>
       </c>
       <c r="L48" t="n">
-        <v>1.90947</v>
+        <v>-1.76028</v>
       </c>
       <c r="M48" t="n">
-        <v>15427520.23413867</v>
+        <v>432503.321551</v>
       </c>
       <c r="N48" t="n">
-        <v>16000000</v>
+        <v>432503.321551</v>
       </c>
       <c r="O48" t="n">
-        <v>661.6900000000001</v>
+        <v>5619.09</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>46050.93814814815</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008979950726277979</v>
+        <v>0.0008646547057302942</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.17</v>
+        <v>121.66</v>
       </c>
       <c r="F49" t="n">
-        <v>1990773475</v>
+        <v>1876667794</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>433366537</v>
+        <v>227360877</v>
       </c>
       <c r="I49" t="n">
-        <v>1.28</v>
+        <v>130.48</v>
       </c>
       <c r="J49" t="n">
-        <v>1.073</v>
+        <v>121.65</v>
       </c>
       <c r="K49" t="n">
-        <v>0.103913</v>
+        <v>-8.660694750821918</v>
       </c>
       <c r="L49" t="n">
-        <v>9.749879999999999</v>
+        <v>-6.64545</v>
       </c>
       <c r="M49" t="n">
-        <v>1701957999.857161</v>
+        <v>15427529.56307751</v>
       </c>
       <c r="N49" t="n">
-        <v>1701965018.386449</v>
+        <v>16000000</v>
       </c>
       <c r="O49" t="n">
-        <v>54.98</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R49" t="b">
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.000885028811689667</v>
+        <v>0.0008616823393600202</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.00462038</v>
+        <v>1.092</v>
       </c>
       <c r="F50" t="n">
-        <v>1916697613</v>
+        <v>1859047595</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>242544269</v>
+        <v>194027311</v>
       </c>
       <c r="I50" t="n">
-        <v>0.00473928</v>
+        <v>1.16</v>
       </c>
       <c r="J50" t="n">
-        <v>0.00425383</v>
+        <v>1.088</v>
       </c>
       <c r="K50" t="n">
-        <v>0.00034456</v>
+        <v>-0.07838425218558731</v>
       </c>
       <c r="L50" t="n">
-        <v>8.05829</v>
+        <v>-6.69596</v>
       </c>
       <c r="M50" t="n">
-        <v>414835547764.7695</v>
+        <v>1702097434.813982</v>
       </c>
       <c r="N50" t="n">
-        <v>834972366903.9573</v>
+        <v>1702117935.326118</v>
       </c>
       <c r="O50" t="n">
-        <v>0.00881908</v>
+        <v>54.98</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R50" t="b">
         <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008386673118103884</v>
+        <v>0.0008502646243020725</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pax-gold</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>paxg</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PAX Gold</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4428.76</v>
+        <v>0.055999</v>
       </c>
       <c r="F51" t="n">
-        <v>1915451805</v>
+        <v>1777729576</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>131038731</v>
+        <v>37479304</v>
       </c>
       <c r="I51" t="n">
-        <v>4413.97</v>
+        <v>0.056977</v>
       </c>
       <c r="J51" t="n">
-        <v>4348.7</v>
+        <v>0.055019</v>
       </c>
       <c r="K51" t="n">
-        <v>30.54</v>
+        <v>8.96e-05</v>
       </c>
       <c r="L51" t="n">
-        <v>0.69446</v>
+        <v>0.16025</v>
       </c>
       <c r="M51" t="n">
-        <v>432503.312051</v>
+        <v>31777196737</v>
       </c>
       <c r="N51" t="n">
-        <v>432503.312051</v>
+        <v>100000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>5619.09</v>
+        <v>0.331336</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>46050.93814814815</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0008378876040097339</v>
+        <v>0.000797571350519025</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3889,28 +3889,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.378675</v>
+        <v>0.349506</v>
       </c>
       <c r="F52" t="n">
-        <v>1843892054</v>
+        <v>1701671484</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>104045504</v>
+        <v>117343569</v>
       </c>
       <c r="I52" t="n">
-        <v>0.385685</v>
+        <v>0.378074</v>
       </c>
       <c r="J52" t="n">
-        <v>0.369949</v>
+        <v>0.3475</v>
       </c>
       <c r="K52" t="n">
-        <v>0.00512265</v>
+        <v>-0.02968519707974521</v>
       </c>
       <c r="L52" t="n">
-        <v>1.37133</v>
+        <v>-7.82856</v>
       </c>
       <c r="M52" t="n">
         <v>4869330647</v>
@@ -3925,756 +3925,756 @@
         <v>45641.69166666667</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007931008502984142</v>
+        <v>0.0007482864575216659</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.055867</v>
+        <v>0.00387964</v>
       </c>
       <c r="F53" t="n">
-        <v>1775278070</v>
+        <v>1608873443</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>22120553</v>
+        <v>369368662</v>
       </c>
       <c r="I53" t="n">
-        <v>0.056457</v>
+        <v>0.00482089</v>
       </c>
       <c r="J53" t="n">
-        <v>0.055548</v>
+        <v>0.00384956</v>
       </c>
       <c r="K53" t="n">
-        <v>0.00026835</v>
+        <v>-0.000764813556465756</v>
       </c>
       <c r="L53" t="n">
-        <v>0.48266</v>
+        <v>-16.46724</v>
       </c>
       <c r="M53" t="n">
-        <v>31777118978</v>
+        <v>414657242500.5876</v>
       </c>
       <c r="N53" t="n">
-        <v>100000000000</v>
+        <v>834788573196.6761</v>
       </c>
       <c r="O53" t="n">
-        <v>0.331336</v>
+        <v>0.00881908</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0007501577494684458</v>
+        <v>0.0006881542427791564</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.453082</v>
+        <v>2.25</v>
       </c>
       <c r="F54" t="n">
-        <v>1666800928</v>
+        <v>1548374384</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>242159032</v>
+        <v>20872061</v>
       </c>
       <c r="I54" t="n">
-        <v>0.492671</v>
+        <v>2.39</v>
       </c>
       <c r="J54" t="n">
-        <v>0.44254</v>
+        <v>2.23</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.01373543464551086</v>
+        <v>-0.1070669937011086</v>
       </c>
       <c r="L54" t="n">
-        <v>-2.94235</v>
+        <v>-4.54654</v>
       </c>
       <c r="M54" t="n">
-        <v>3678803645.0447</v>
+        <v>688887784.3170698</v>
       </c>
       <c r="N54" t="n">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O54" t="n">
-        <v>11.74</v>
+        <v>4.17</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.000682265687601687</v>
+        <v>0.0006489514496134283</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.163574</v>
+        <v>2.74</v>
       </c>
       <c r="F55" t="n">
-        <v>1651334608</v>
+        <v>1526634131</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>453892663</v>
+        <v>55541922</v>
       </c>
       <c r="I55" t="n">
-        <v>0.168753</v>
+        <v>2.89</v>
       </c>
       <c r="J55" t="n">
-        <v>0.15868</v>
+        <v>2.72</v>
       </c>
       <c r="K55" t="n">
-        <v>0.00550579</v>
+        <v>-0.1419245793196384</v>
       </c>
       <c r="L55" t="n">
-        <v>3.48317</v>
+        <v>-4.91782</v>
       </c>
       <c r="M55" t="n">
-        <v>10095312500</v>
+        <v>556268872.9048556</v>
       </c>
       <c r="N55" t="n">
-        <v>15000000000</v>
+        <v>556269825.7674338</v>
       </c>
       <c r="O55" t="n">
-        <v>1.52</v>
+        <v>700.65</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006725858570407832</v>
+        <v>0.0006348639802243657</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.35</v>
+        <v>1.68e-06</v>
       </c>
       <c r="F56" t="n">
-        <v>1618892087</v>
+        <v>1510151983</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>32447610</v>
+        <v>45332687</v>
       </c>
       <c r="I56" t="n">
-        <v>2.44</v>
+        <v>1.69e-06</v>
       </c>
       <c r="J56" t="n">
-        <v>2.31</v>
+        <v>1.68e-06</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.06501100290062611</v>
+        <v>-7.002670966e-09</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.69175</v>
+        <v>-0.41475</v>
       </c>
       <c r="M56" t="n">
-        <v>688837052.3557253</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N56" t="n">
-        <v>1000000000</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O56" t="n">
-        <v>4.17</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006522812140327142</v>
+        <v>0.0006241837109829727</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.88</v>
+        <v>0.405233</v>
       </c>
       <c r="F57" t="n">
-        <v>1603747363</v>
+        <v>1491195699</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>63715202</v>
+        <v>206723334</v>
       </c>
       <c r="I57" t="n">
-        <v>3.07</v>
+        <v>0.44988</v>
       </c>
       <c r="J57" t="n">
-        <v>2.83</v>
+        <v>0.402342</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.1076426999183364</v>
+        <v>-0.04889978019534369</v>
       </c>
       <c r="L57" t="n">
-        <v>-3.59925</v>
+        <v>-10.76774</v>
       </c>
       <c r="M57" t="n">
-        <v>556267110.7903996</v>
+        <v>3680240835.629099</v>
       </c>
       <c r="N57" t="n">
-        <v>556267110.7903996</v>
+        <v>10000000000</v>
       </c>
       <c r="O57" t="n">
-        <v>700.65</v>
+        <v>11.74</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R57" t="b">
         <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006428026591979732</v>
+        <v>0.0006119002260308713</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.7e-06</v>
+        <v>0.999068</v>
       </c>
       <c r="F58" t="n">
-        <v>1558125094</v>
+        <v>1485914228</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>233655849</v>
+        <v>2787411</v>
       </c>
       <c r="I58" t="n">
-        <v>3.76e-06</v>
+        <v>0.9997470000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>3.59e-06</v>
+        <v>0.998008</v>
       </c>
       <c r="K58" t="n">
-        <v>1.23124e-07</v>
+        <v>-0.000648900614201087</v>
       </c>
       <c r="L58" t="n">
-        <v>3.43864</v>
+        <v>-0.06491</v>
       </c>
       <c r="M58" t="n">
-        <v>420690000000000</v>
+        <v>1487315929</v>
       </c>
       <c r="N58" t="n">
-        <v>420690000000000</v>
+        <v>1491270221</v>
       </c>
       <c r="O58" t="n">
-        <v>2.803e-05</v>
+        <v>1.24</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.000614249271338161</v>
+        <v>0.0006084778849458009</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.69e-06</v>
+        <v>0.146259</v>
       </c>
       <c r="F59" t="n">
-        <v>1516108351</v>
+        <v>1476341265</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>25301224</v>
+        <v>356558838</v>
       </c>
       <c r="I59" t="n">
-        <v>1.7e-06</v>
+        <v>0.164399</v>
       </c>
       <c r="J59" t="n">
-        <v>1.68e-06</v>
+        <v>0.145743</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.1397764713e-08</v>
+        <v>-0.01738844476775372</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.67074</v>
+        <v>-10.62556</v>
       </c>
       <c r="M59" t="n">
-        <v>898232728634017.2</v>
+        <v>10095312500</v>
       </c>
       <c r="N59" t="n">
-        <v>898232728634017.2</v>
+        <v>15000000000</v>
       </c>
       <c r="O59" t="n">
-        <v>3.75e-06</v>
+        <v>1.52</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0005879524565198308</v>
+        <v>0.0006022746993975403</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.064594</v>
+        <v>3.34e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1513277904</v>
+        <v>1405799346</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>8809154</v>
+        <v>253476976</v>
       </c>
       <c r="I60" t="n">
-        <v>0.068149</v>
+        <v>3.69e-06</v>
       </c>
       <c r="J60" t="n">
-        <v>0.064162</v>
+        <v>3.33e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.002333706369906666</v>
+        <v>-3.78331934945e-07</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.48692</v>
+        <v>-10.17511</v>
       </c>
       <c r="M60" t="n">
-        <v>23427606245.71321</v>
+        <v>420690000000000</v>
       </c>
       <c r="N60" t="n">
-        <v>23462665147.36596</v>
+        <v>420690000000000</v>
       </c>
       <c r="O60" t="n">
-        <v>0.100535</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R60" t="b">
         <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005861809784066392</v>
+        <v>0.0005565642320649734</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.999587</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>1501094917</v>
+        <v>1383051937</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>5671237</v>
+        <v>26045464</v>
       </c>
       <c r="I61" t="n">
-        <v>0.999947</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0.998458</v>
+        <v>0.999891</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.678295007543e-05</v>
+        <v>-8.2111144466213e-05</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.00468</v>
+        <v>-0.00821</v>
       </c>
       <c r="M61" t="n">
-        <v>1501715043</v>
+        <v>1382942039.16</v>
       </c>
       <c r="N61" t="n">
-        <v>1501818851</v>
+        <v>1382942039.16</v>
       </c>
       <c r="O61" t="n">
-        <v>1.24</v>
+        <v>1.002</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.000578556071519565</v>
+        <v>0.0005418241355275509</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.99</v>
+        <v>0.058619</v>
       </c>
       <c r="F62" t="n">
-        <v>1393021867</v>
+        <v>1373490617</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>11856320</v>
+        <v>14224398</v>
       </c>
       <c r="I62" t="n">
-        <v>2.02</v>
+        <v>0.064653</v>
       </c>
       <c r="J62" t="n">
-        <v>1.97</v>
+        <v>0.058177</v>
       </c>
       <c r="K62" t="n">
-        <v>0.02010862</v>
+        <v>-0.005978917726946816</v>
       </c>
       <c r="L62" t="n">
-        <v>1.02077</v>
+        <v>-9.255559999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>699992029.6481038</v>
+        <v>23426487411.36321</v>
       </c>
       <c r="N62" t="n">
-        <v>910920874.6481038</v>
+        <v>23462665147.36596</v>
       </c>
       <c r="O62" t="n">
-        <v>8.449999999999999</v>
+        <v>0.100535</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45653.15375</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005109169167497121</v>
+        <v>0.0005356284945283853</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>1.94</v>
       </c>
       <c r="F63" t="n">
-        <v>1373620824</v>
+        <v>1357386380</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>57943024</v>
+        <v>12899919</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
-        <v>0.99995</v>
+        <v>1.92</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.536233971279101e-05</v>
+        <v>-0.05123757344788293</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.008529999999999999</v>
+        <v>-2.57431</v>
       </c>
       <c r="M63" t="n">
-        <v>1373442039.16</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N63" t="n">
-        <v>1373442039.16</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O63" t="n">
-        <v>1.002</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46092.00303240741</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0004987744802202205</v>
+        <v>0.000525193107885382</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4693,28 +4693,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.996804</v>
+        <v>0.996576</v>
       </c>
       <c r="F64" t="n">
-        <v>1340178272</v>
+        <v>1339860323</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>411225</v>
+        <v>369807</v>
       </c>
       <c r="I64" t="n">
-        <v>1.001</v>
+        <v>1.01</v>
       </c>
       <c r="J64" t="n">
-        <v>0.991216</v>
+        <v>0.991111</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0001942</v>
+        <v>-0.000221950111248592</v>
       </c>
       <c r="L64" t="n">
-        <v>0.01949</v>
+        <v>-0.02227</v>
       </c>
       <c r="M64" t="n">
         <v>1344475004.618144</v>
@@ -4729,153 +4729,153 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0004778439526684686</v>
+        <v>0.0005138363959143452</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8.359999999999999</v>
+        <v>0.999521</v>
       </c>
       <c r="F65" t="n">
-        <v>1321985283</v>
+        <v>1319338368</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>119020005</v>
+        <v>6759066</v>
       </c>
       <c r="I65" t="n">
-        <v>9.02</v>
+        <v>0.999857</v>
       </c>
       <c r="J65" t="n">
-        <v>8.25</v>
+        <v>0.9994769999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>0.169357</v>
+        <v>-0.000136606878920031</v>
       </c>
       <c r="L65" t="n">
-        <v>2.06752</v>
+        <v>-0.01367</v>
       </c>
       <c r="M65" t="n">
-        <v>158119477.0392587</v>
+        <v>1320000000</v>
       </c>
       <c r="N65" t="n">
-        <v>158119854.9976587</v>
+        <v>1320000000</v>
       </c>
       <c r="O65" t="n">
-        <v>167.09</v>
+        <v>1.007</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0004664575950270656</v>
+        <v>0.0005005383716058783</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>spiko-amundi-overnight-swap-fund-eur</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>eursafo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.999678</v>
+        <v>1.17</v>
       </c>
       <c r="F66" t="n">
-        <v>1319574651</v>
+        <v>1314745897</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
       </c>
       <c r="H66" t="n">
-        <v>2012445</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0.99995</v>
+        <v>1.18</v>
       </c>
       <c r="J66" t="n">
-        <v>0.999519</v>
+        <v>1.17</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00013571</v>
+        <v>-0.004585650811628206</v>
       </c>
       <c r="L66" t="n">
-        <v>0.01358</v>
+        <v>-0.38899</v>
       </c>
       <c r="M66" t="n">
-        <v>1320000000</v>
+        <v>1119625332.18736</v>
       </c>
       <c r="N66" t="n">
-        <v>1320000000</v>
+        <v>1119625332.18736</v>
       </c>
       <c r="O66" t="n">
-        <v>1.007</v>
+        <v>1.18</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004649488644884053</v>
+        <v>0.0004975624957210549</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4894,34 +4894,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999153</v>
+        <v>0.999181</v>
       </c>
       <c r="F67" t="n">
-        <v>1287408036</v>
+        <v>1280606791</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>159253867</v>
+        <v>176865024</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999421</v>
+        <v>0.999373</v>
       </c>
       <c r="J67" t="n">
-        <v>0.998873</v>
+        <v>0.998997</v>
       </c>
       <c r="K67" t="n">
-        <v>9.974e-05</v>
+        <v>7.446e-05</v>
       </c>
       <c r="L67" t="n">
-        <v>0.009979999999999999</v>
+        <v>0.00745</v>
       </c>
       <c r="M67" t="n">
-        <v>1288500007.8</v>
+        <v>1281500007.8</v>
       </c>
       <c r="N67" t="n">
-        <v>1288500007.8</v>
+        <v>1281500007.8</v>
       </c>
       <c r="O67" t="n">
         <v>1.008</v>
@@ -4930,153 +4930,153 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004448169014281671</v>
+        <v>0.0004754406919524894</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>spiko-amundi-overnight-swap-fund-eur</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>eursafo</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Spiko Amundi Overnight Swap Fund (EUR)</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1.18</v>
+        <v>0.468503</v>
       </c>
       <c r="F68" t="n">
-        <v>1270222603</v>
+        <v>1268869271</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>10751913</v>
       </c>
       <c r="I68" t="n">
-        <v>1.18</v>
+        <v>0.471754</v>
       </c>
       <c r="J68" t="n">
-        <v>1.18</v>
+        <v>0.43293</v>
       </c>
       <c r="K68" t="n">
-        <v>0.00251157</v>
+        <v>0.01929156</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2135</v>
+        <v>4.29453</v>
       </c>
       <c r="M68" t="n">
-        <v>1077468076.07545</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N68" t="n">
-        <v>1077468076.07545</v>
+        <v>10000000000</v>
       </c>
       <c r="O68" t="n">
-        <v>1.18</v>
+        <v>0.745279</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46255.48263888889</v>
+        <v>46253.4</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004340611379656393</v>
+        <v>0.0004678348948302797</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>lighter</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>lit</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lighter</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.06</v>
+        <v>7.71</v>
       </c>
       <c r="F69" t="n">
-        <v>1265464459</v>
+        <v>1219499871</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>121774066</v>
+        <v>60458123</v>
       </c>
       <c r="I69" t="n">
-        <v>5.31</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>4.65</v>
+        <v>7.67</v>
       </c>
       <c r="K69" t="n">
-        <v>0.249492</v>
+        <v>-0.6696181749045396</v>
       </c>
       <c r="L69" t="n">
-        <v>5.18439</v>
+        <v>-7.98999</v>
       </c>
       <c r="M69" t="n">
-        <v>250000000</v>
+        <v>158130846.3427831</v>
       </c>
       <c r="N69" t="n">
-        <v>1000000000</v>
+        <v>158131277.2419831</v>
       </c>
       <c r="O69" t="n">
-        <v>7.86</v>
+        <v>167.09</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>46021.04538194444</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004310831814960731</v>
+        <v>0.0004358440108577523</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5095,34 +5095,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>26.01</v>
+        <v>24.03</v>
       </c>
       <c r="F70" t="n">
-        <v>1245840649</v>
+        <v>1152251647</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>339972518</v>
+        <v>154151810</v>
       </c>
       <c r="I70" t="n">
-        <v>29.19</v>
+        <v>26.08</v>
       </c>
       <c r="J70" t="n">
-        <v>19.47</v>
+        <v>22.23</v>
       </c>
       <c r="K70" t="n">
-        <v>7.21</v>
+        <v>-2.130860004533968</v>
       </c>
       <c r="L70" t="n">
-        <v>38.35212</v>
+        <v>-8.144360000000001</v>
       </c>
       <c r="M70" t="n">
-        <v>47901563.16795567</v>
+        <v>47914366.51301605</v>
       </c>
       <c r="N70" t="n">
-        <v>80972884.09714592</v>
+        <v>80979732.14382271</v>
       </c>
       <c r="O70" t="n">
         <v>29.19</v>
@@ -5131,421 +5131,421 @@
         <v>46274.32083333333</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.000418801322866524</v>
+        <v>0.0003922678253796517</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>lighter</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>lit</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Lighter</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.449598</v>
+        <v>4.54</v>
       </c>
       <c r="F71" t="n">
-        <v>1217576685</v>
+        <v>1135234423</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>7595620</v>
+        <v>101341183</v>
       </c>
       <c r="I71" t="n">
-        <v>0.46133</v>
+        <v>5.08</v>
       </c>
       <c r="J71" t="n">
-        <v>0.429682</v>
+        <v>4.42</v>
       </c>
       <c r="K71" t="n">
-        <v>0.005923</v>
+        <v>-0.5517406813879191</v>
       </c>
       <c r="L71" t="n">
-        <v>1.33498</v>
+        <v>-10.83157</v>
       </c>
       <c r="M71" t="n">
-        <v>2708142280.000001</v>
+        <v>250000000</v>
       </c>
       <c r="N71" t="n">
-        <v>10000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O71" t="n">
-        <v>0.745279</v>
+        <v>7.86</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>46253.4</v>
+        <v>46021.04538194444</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0004011118930280439</v>
+        <v>0.0003812408321709332</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>pi-network</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>pi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Pi Network</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.166662</v>
+        <v>0.09607</v>
       </c>
       <c r="F72" t="n">
-        <v>1112983043</v>
+        <v>1070290641</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>260935944</v>
+        <v>6550211</v>
       </c>
       <c r="I72" t="n">
-        <v>0.174571</v>
+        <v>0.097702</v>
       </c>
       <c r="J72" t="n">
-        <v>0.163302</v>
+        <v>0.093235</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.000870409281804901</v>
+        <v>-0.001789429385238753</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.51955</v>
+        <v>-1.82856</v>
       </c>
       <c r="M72" t="n">
-        <v>6678075931</v>
+        <v>11141680597.24892</v>
       </c>
       <c r="N72" t="n">
-        <v>10000000000</v>
+        <v>17141047072.69065</v>
       </c>
       <c r="O72" t="n">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>45714.36184027778</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003356503784397114</v>
+        <v>0.0003391579023662542</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>pi-network</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Pi Network</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.097941</v>
+        <v>0.03771009</v>
       </c>
       <c r="F73" t="n">
-        <v>1091222672</v>
+        <v>1045172018</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>6895684</v>
+        <v>29437666</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09958400000000001</v>
+        <v>0.03928072</v>
       </c>
       <c r="J73" t="n">
-        <v>0.095987</v>
+        <v>0.03484704</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00219393</v>
+        <v>0.00152136</v>
       </c>
       <c r="L73" t="n">
-        <v>2.29139</v>
+        <v>4.20395</v>
       </c>
       <c r="M73" t="n">
-        <v>11141680597.24892</v>
+        <v>27691695062.44326</v>
       </c>
       <c r="N73" t="n">
-        <v>17141047072.69065</v>
+        <v>27692331519.9827</v>
       </c>
       <c r="O73" t="n">
-        <v>2.99</v>
+        <v>0.207411</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45714.36184027778</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003220313207567976</v>
+        <v>0.0003228812825583841</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.097224</v>
+        <v>0.148208</v>
       </c>
       <c r="F74" t="n">
-        <v>1041386346</v>
+        <v>989717749</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>89603107</v>
+        <v>306660358</v>
       </c>
       <c r="I74" t="n">
-        <v>0.099879</v>
+        <v>0.165926</v>
       </c>
       <c r="J74" t="n">
-        <v>0.094888</v>
+        <v>0.145666</v>
       </c>
       <c r="K74" t="n">
-        <v>0.00152497</v>
+        <v>-0.01830829186910402</v>
       </c>
       <c r="L74" t="n">
-        <v>1.5935</v>
+        <v>-10.99492</v>
       </c>
       <c r="M74" t="n">
-        <v>10711198045.42806</v>
+        <v>6678075931</v>
       </c>
       <c r="N74" t="n">
-        <v>10711198045.42806</v>
+        <v>10000000000</v>
       </c>
       <c r="O74" t="n">
-        <v>1.29</v>
+        <v>2.39</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002908405015148603</v>
+        <v>0.0002869474635255353</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.96</v>
+        <v>0.091</v>
       </c>
       <c r="F75" t="n">
-        <v>1037130851</v>
+        <v>974631690</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>117474646</v>
+        <v>84450093</v>
       </c>
       <c r="I75" t="n">
-        <v>2.03</v>
+        <v>0.098193</v>
       </c>
       <c r="J75" t="n">
-        <v>1.71</v>
+        <v>0.090625</v>
       </c>
       <c r="K75" t="n">
-        <v>0.231496</v>
+        <v>-0.006450902539119729</v>
       </c>
       <c r="L75" t="n">
-        <v>13.40961</v>
+        <v>-6.61967</v>
       </c>
       <c r="M75" t="n">
-        <v>529733011.592082</v>
+        <v>10711779103.38826</v>
       </c>
       <c r="N75" t="n">
-        <v>529741698.798252</v>
+        <v>10711779103.38826</v>
       </c>
       <c r="O75" t="n">
-        <v>43.84</v>
+        <v>1.29</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002881771355329867</v>
+        <v>0.0002771718461781155</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>blockchain-capital</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>bcap</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Blockchain Capital</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.03605797</v>
+        <v>106.49</v>
       </c>
       <c r="F76" t="n">
-        <v>998336918</v>
+        <v>970348700</v>
       </c>
       <c r="G76" t="n">
         <v>75</v>
       </c>
       <c r="H76" t="n">
-        <v>18754394</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.03715227</v>
+        <v>106.49</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03506837</v>
+        <v>106.49</v>
       </c>
       <c r="K76" t="n">
-        <v>0.00088579</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>2.51845</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>27686994077.20287</v>
+        <v>9112111</v>
       </c>
       <c r="N76" t="n">
-        <v>27690422706.12956</v>
+        <v>9112111</v>
       </c>
       <c r="O76" t="n">
-        <v>0.207411</v>
+        <v>106.49</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>46273.93067129629</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.000263897365152505</v>
+        <v>0.0002743965109270188</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5564,34 +5564,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>9.359999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>997888828</v>
+        <v>956551613</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>2186375</v>
+        <v>2796794</v>
       </c>
       <c r="I77" t="n">
-        <v>9.369999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="J77" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="K77" t="n">
-        <v>0.246251</v>
+        <v>-0.4208429464590857</v>
       </c>
       <c r="L77" t="n">
-        <v>2.70223</v>
+        <v>-4.48451</v>
       </c>
       <c r="M77" t="n">
-        <v>106622060.2754268</v>
+        <v>106623165.6073925</v>
       </c>
       <c r="N77" t="n">
-        <v>118873292.382472</v>
+        <v>118874451.7093768</v>
       </c>
       <c r="O77" t="n">
         <v>25.38</v>
@@ -5600,153 +5600,153 @@
         <v>45682.66666666666</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002636169212410875</v>
+        <v>0.0002654561347147118</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>quant-network</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>qnt</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>67.75</v>
+        <v>1.79</v>
       </c>
       <c r="F78" t="n">
-        <v>985382503</v>
+        <v>947879945</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>17313401</v>
+        <v>65021941</v>
       </c>
       <c r="I78" t="n">
-        <v>69.83</v>
+        <v>1.96</v>
       </c>
       <c r="J78" t="n">
-        <v>66.81</v>
+        <v>1.78</v>
       </c>
       <c r="K78" t="n">
-        <v>0.553311</v>
+        <v>-0.1677502701765261</v>
       </c>
       <c r="L78" t="n">
-        <v>0.82341</v>
+        <v>-8.57339</v>
       </c>
       <c r="M78" t="n">
-        <v>14544176.16408117</v>
+        <v>529892426.812725</v>
       </c>
       <c r="N78" t="n">
-        <v>14612493</v>
+        <v>529922361.717385</v>
       </c>
       <c r="O78" t="n">
-        <v>427.42</v>
+        <v>43.84</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>44450.05208333334</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002557896483707736</v>
+        <v>0.0002598369794315551</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>blockchain-capital</t>
+          <t>quant-network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>bcap</t>
+          <t>qnt</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Blockchain Capital</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106.49</v>
+        <v>65.12</v>
       </c>
       <c r="F79" t="n">
-        <v>970348700</v>
+        <v>946567813</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>7039868</v>
       </c>
       <c r="I79" t="n">
-        <v>106.49</v>
+        <v>67.78</v>
       </c>
       <c r="J79" t="n">
-        <v>106.22</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>0.27</v>
+        <v>-2.68778858197895</v>
       </c>
       <c r="L79" t="n">
-        <v>0.25419</v>
+        <v>-3.96358</v>
       </c>
       <c r="M79" t="n">
-        <v>9112111</v>
+        <v>14544176.16408117</v>
       </c>
       <c r="N79" t="n">
-        <v>9112111</v>
+        <v>14612493</v>
       </c>
       <c r="O79" t="n">
-        <v>106.49</v>
+        <v>427.42</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>46273.93067129629</v>
+        <v>44450.05208333334</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002463805151234332</v>
+        <v>0.0002589867308450088</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5765,28 +5765,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7.01</v>
+        <v>6.86</v>
       </c>
       <c r="F80" t="n">
-        <v>961354266</v>
+        <v>940197876</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>2742525</v>
+        <v>2816887</v>
       </c>
       <c r="I80" t="n">
-        <v>7.05</v>
+        <v>7.06</v>
       </c>
       <c r="J80" t="n">
-        <v>6.95</v>
+        <v>6.85</v>
       </c>
       <c r="K80" t="n">
-        <v>0.02843958</v>
+        <v>-0.1494727959964726</v>
       </c>
       <c r="L80" t="n">
-        <v>0.4074</v>
+        <v>-2.13395</v>
       </c>
       <c r="M80" t="n">
         <v>137155021.2773955</v>
@@ -5801,19 +5801,19 @@
         <v>44531.29832175926</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002407512124120428</v>
+        <v>0.0002548590745340285</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5832,34 +5832,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.100637</v>
+        <v>0.097095</v>
       </c>
       <c r="F81" t="n">
-        <v>909734560</v>
+        <v>877629397</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>43569879</v>
+        <v>47216826</v>
       </c>
       <c r="I81" t="n">
-        <v>0.103137</v>
+        <v>0.101985</v>
       </c>
       <c r="J81" t="n">
-        <v>0.097334</v>
+        <v>0.09628399999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>0.00327804</v>
+        <v>-0.003935790281541229</v>
       </c>
       <c r="L81" t="n">
-        <v>3.36695</v>
+        <v>-3.89563</v>
       </c>
       <c r="M81" t="n">
-        <v>9039728572.301533</v>
+        <v>9039923262.00091</v>
       </c>
       <c r="N81" t="n">
-        <v>9039769730.371443</v>
+        <v>9039974297.342701</v>
       </c>
       <c r="O81" t="n">
         <v>3.56</v>
@@ -5868,19 +5868,19 @@
         <v>43636.28563657407</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002084442377934093</v>
+        <v>0.0002143153176314426</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5902,7 +5902,7 @@
         <v>1.23</v>
       </c>
       <c r="F82" t="n">
-        <v>881844306</v>
+        <v>865442517</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
@@ -5917,16 +5917,16 @@
         <v>1.23</v>
       </c>
       <c r="K82" t="n">
-        <v>0.00269621</v>
+        <v>-0.004782788274432015</v>
       </c>
       <c r="L82" t="n">
-        <v>0.21918</v>
+        <v>-0.38797</v>
       </c>
       <c r="M82" t="n">
-        <v>715302976.77384</v>
+        <v>704755041.68557</v>
       </c>
       <c r="N82" t="n">
-        <v>715302976.77384</v>
+        <v>704755041.68557</v>
       </c>
       <c r="O82" t="n">
         <v>1.26</v>
@@ -5935,421 +5935,421 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001909887000170949</v>
+        <v>0.0002064183396639746</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.848105</v>
+        <v>0.103766</v>
       </c>
       <c r="F83" t="n">
-        <v>848104647</v>
+        <v>849689853</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>2893581</v>
+        <v>24422970</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8501069999999999</v>
+        <v>0.105928</v>
       </c>
       <c r="J83" t="n">
-        <v>0.822473</v>
+        <v>0.102162</v>
       </c>
       <c r="K83" t="n">
-        <v>0.02610827</v>
+        <v>0.00112145</v>
       </c>
       <c r="L83" t="n">
-        <v>3.1762</v>
+        <v>1.09255</v>
       </c>
       <c r="M83" t="n">
-        <v>1000000000</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N83" t="n">
-        <v>1000000000</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O83" t="n">
-        <v>4.07</v>
+        <v>0.193254</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001698722235506395</v>
+        <v>0.0001962107688552913</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.102617</v>
+        <v>0.836378</v>
       </c>
       <c r="F84" t="n">
-        <v>840302919</v>
+        <v>837041793</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>24080947</v>
+        <v>3036475</v>
       </c>
       <c r="I84" t="n">
-        <v>0.110037</v>
+        <v>0.849623</v>
       </c>
       <c r="J84" t="n">
-        <v>0.102905</v>
+        <v>0.831659</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.004272044566157859</v>
+        <v>-0.007957469623558033</v>
       </c>
       <c r="L84" t="n">
-        <v>-3.99672</v>
+        <v>-0.94245</v>
       </c>
       <c r="M84" t="n">
-        <v>8188743036.341737</v>
+        <v>1000000000</v>
       </c>
       <c r="N84" t="n">
-        <v>8188743036.341737</v>
+        <v>1000000000</v>
       </c>
       <c r="O84" t="n">
-        <v>0.193254</v>
+        <v>4.07</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001649893939491404</v>
+        <v>0.0001880149507992168</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>64.7</v>
+        <v>11.21</v>
       </c>
       <c r="F85" t="n">
-        <v>830001957</v>
+        <v>812242372</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>191724352</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>66.34</v>
+        <v>11.21</v>
       </c>
       <c r="J85" t="n">
-        <v>61.47</v>
+        <v>11.21</v>
       </c>
       <c r="K85" t="n">
-        <v>1.94</v>
+        <v>0.001101</v>
       </c>
       <c r="L85" t="n">
-        <v>3.08551</v>
+        <v>0.00983</v>
       </c>
       <c r="M85" t="n">
-        <v>12828352.02901614</v>
+        <v>72475935.23173</v>
       </c>
       <c r="N85" t="n">
-        <v>12828387.07391258</v>
+        <v>72619184.682154</v>
       </c>
       <c r="O85" t="n">
-        <v>1493.59</v>
+        <v>11.21</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>46275.55902777778</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001585423809056815</v>
+        <v>0.0001719451707371366</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>hunter-biden-s-laptop-3</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>laptop</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Hunter Biden's Laptop</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2.37</v>
+        <v>0.02961505</v>
       </c>
       <c r="F86" t="n">
-        <v>828030832</v>
+        <v>773093892</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>3456213</v>
+        <v>9830366</v>
       </c>
       <c r="I86" t="n">
-        <v>199.51</v>
+        <v>0.02970387</v>
       </c>
       <c r="J86" t="n">
-        <v>4.15</v>
+        <v>0.02800359</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>0.0009908600000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.46161</v>
       </c>
       <c r="M86" t="n">
-        <v>350000000</v>
+        <v>26193447530</v>
       </c>
       <c r="N86" t="n">
-        <v>1000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O86" t="n">
-        <v>199.51</v>
+        <v>0.04323745</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46274.50636574074</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001573087224779262</v>
+        <v>0.0001465773420541708</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>janus-henderson-anemoy-treasury-fund</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>jtrsy</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Janus Henderson Anemoy Treasury Fund</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.249268</v>
+        <v>1.12</v>
       </c>
       <c r="F87" t="n">
-        <v>827648744</v>
+        <v>750052639</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>85872214</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.253844</v>
+        <v>1.12</v>
       </c>
       <c r="J87" t="n">
-        <v>0.237355</v>
+        <v>1.12</v>
       </c>
       <c r="K87" t="n">
-        <v>0.00948354</v>
+        <v>0.000164</v>
       </c>
       <c r="L87" t="n">
-        <v>3.95502</v>
+        <v>0.0147</v>
       </c>
       <c r="M87" t="n">
-        <v>3320312968.08</v>
+        <v>672308859.001803</v>
       </c>
       <c r="N87" t="n">
-        <v>6862431106.912057</v>
+        <v>672308859.001803</v>
       </c>
       <c r="O87" t="n">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>46275.55902777778</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001570695869176019</v>
+        <v>0.0001316468375046998</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>11.21</v>
+        <v>0.224658</v>
       </c>
       <c r="F88" t="n">
-        <v>821035373</v>
+        <v>745795089</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>79189933</v>
       </c>
       <c r="I88" t="n">
-        <v>11.2</v>
+        <v>0.252296</v>
       </c>
       <c r="J88" t="n">
-        <v>11.2</v>
+        <v>0.223238</v>
       </c>
       <c r="K88" t="n">
-        <v>0.004404</v>
+        <v>-0.02533083322216281</v>
       </c>
       <c r="L88" t="n">
-        <v>0.03932</v>
+        <v>-10.13279</v>
       </c>
       <c r="M88" t="n">
-        <v>73267727.74824999</v>
+        <v>3320312968.08</v>
       </c>
       <c r="N88" t="n">
-        <v>73267727.74824999</v>
+        <v>6861487305.722849</v>
       </c>
       <c r="O88" t="n">
-        <v>11.21</v>
+        <v>2</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46274.55208333334</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001529305085384921</v>
+        <v>0.0001288879871225353</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6368,28 +6368,28 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="F89" t="n">
-        <v>795802898</v>
+        <v>726596100</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>46346492</v>
+        <v>57077786</v>
       </c>
       <c r="I89" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="J89" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="K89" t="n">
-        <v>0.04194235</v>
+        <v>-0.1370691628276224</v>
       </c>
       <c r="L89" t="n">
-        <v>2.81102</v>
+        <v>-8.91394</v>
       </c>
       <c r="M89" t="n">
         <v>518772101.2826915</v>
@@ -6404,814 +6404,814 @@
         <v>45368.35444444444</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001371383819930541</v>
+        <v>0.0001164472317256937</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.12</v>
+        <v>56.41</v>
       </c>
       <c r="F90" t="n">
-        <v>774942361</v>
+        <v>723287048</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>175518035</v>
       </c>
       <c r="I90" t="n">
-        <v>1.12</v>
+        <v>65.06</v>
       </c>
       <c r="J90" t="n">
-        <v>1.12</v>
+        <v>56.07</v>
       </c>
       <c r="K90" t="n">
-        <v>0.000412</v>
+        <v>-7.975759511683925</v>
       </c>
       <c r="L90" t="n">
-        <v>0.03695</v>
+        <v>-12.38724</v>
       </c>
       <c r="M90" t="n">
-        <v>694720859.594534</v>
+        <v>12824703.59132163</v>
       </c>
       <c r="N90" t="n">
-        <v>694720859.594534</v>
+        <v>12824688.23224829</v>
       </c>
       <c r="O90" t="n">
-        <v>1.12</v>
+        <v>1493.59</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46273.57650462963</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001240824990442038</v>
+        <v>0.0001143029986867858</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.02858139</v>
+        <v>1.049</v>
       </c>
       <c r="F91" t="n">
-        <v>747820183</v>
+        <v>713208265</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>7198193</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.02896755</v>
+        <v>1.049</v>
       </c>
       <c r="J91" t="n">
-        <v>0.02823008</v>
+        <v>1.049</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.000234992631568967</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>-0.81548</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>26164588134</v>
+        <v>679991366.72342</v>
       </c>
       <c r="N91" t="n">
-        <v>100000000000</v>
+        <v>679991366.72342</v>
       </c>
       <c r="O91" t="n">
-        <v>0.04323745</v>
+        <v>1.049</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>46274.47222222222</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001071076732625913</v>
+        <v>0.0001077720467704716</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2.3</v>
+        <v>0.998486</v>
       </c>
       <c r="F92" t="n">
-        <v>737920504</v>
+        <v>697954217</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>72253708</v>
+        <v>5301136</v>
       </c>
       <c r="I92" t="n">
-        <v>2.32</v>
+        <v>0.998636</v>
       </c>
       <c r="J92" t="n">
-        <v>2.26</v>
+        <v>0.998163</v>
       </c>
       <c r="K92" t="n">
-        <v>0.01464921</v>
+        <v>0.00017849</v>
       </c>
       <c r="L92" t="n">
-        <v>0.63969</v>
+        <v>0.01788</v>
       </c>
       <c r="M92" t="n">
-        <v>320184235.914524</v>
+        <v>699000000</v>
       </c>
       <c r="N92" t="n">
-        <v>331857365.1830818</v>
+        <v>699000000</v>
       </c>
       <c r="O92" t="n">
-        <v>43.96</v>
+        <v>1.03</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0001009118092608548</v>
+        <v>9.788757420893823e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.049</v>
+        <v>0.00787007</v>
       </c>
       <c r="F93" t="n">
-        <v>713208264</v>
+        <v>676572141</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>22647904</v>
       </c>
       <c r="I93" t="n">
-        <v>1.049</v>
+        <v>0.00807445</v>
       </c>
       <c r="J93" t="n">
-        <v>1.049</v>
+        <v>0.00740968</v>
       </c>
       <c r="K93" t="n">
-        <v>0.00069</v>
+        <v>9.907e-05</v>
       </c>
       <c r="L93" t="n">
-        <v>0.06583</v>
+        <v>1.27482</v>
       </c>
       <c r="M93" t="n">
-        <v>679991365.72342</v>
+        <v>85985041177</v>
       </c>
       <c r="N93" t="n">
-        <v>679991365.72342</v>
+        <v>85985041177</v>
       </c>
       <c r="O93" t="n">
-        <v>1.049</v>
+        <v>0.280991</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46274.47222222222</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>8.54452796674941e-05</v>
+        <v>8.403219998102046e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.846367</v>
+        <v>2.1</v>
       </c>
       <c r="F94" t="n">
-        <v>700157404</v>
+        <v>671657521</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>82587362</v>
+        <v>76196526</v>
       </c>
       <c r="I94" t="n">
-        <v>0.875856</v>
+        <v>2.29</v>
       </c>
       <c r="J94" t="n">
-        <v>0.825248</v>
+        <v>2.11</v>
       </c>
       <c r="K94" t="n">
-        <v>0.00459559</v>
+        <v>-0.2103581739932632</v>
       </c>
       <c r="L94" t="n">
-        <v>0.54594</v>
+        <v>-9.11121</v>
       </c>
       <c r="M94" t="n">
-        <v>827250406</v>
+        <v>320187582.0028005</v>
       </c>
       <c r="N94" t="n">
-        <v>1957074626</v>
+        <v>331857365.0223532</v>
       </c>
       <c r="O94" t="n">
-        <v>236.84</v>
+        <v>43.96</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>7.72772013221556e-05</v>
+        <v>8.084757472349123e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.998395</v>
+        <v>0.801834</v>
       </c>
       <c r="F95" t="n">
-        <v>697878223</v>
+        <v>663358743</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>7860476</v>
+        <v>71198473</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9990019999999999</v>
+        <v>0.853332</v>
       </c>
       <c r="J95" t="n">
-        <v>0.998297</v>
+        <v>0.79472</v>
       </c>
       <c r="K95" t="n">
-        <v>1.54e-06</v>
+        <v>-0.04792108817033724</v>
       </c>
       <c r="L95" t="n">
-        <v>0.00015</v>
+        <v>-5.6394</v>
       </c>
       <c r="M95" t="n">
-        <v>699000000</v>
+        <v>827388008</v>
       </c>
       <c r="N95" t="n">
-        <v>699000000</v>
+        <v>1957070603</v>
       </c>
       <c r="O95" t="n">
-        <v>1.03</v>
+        <v>236.84</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>7.58507413822584e-05</v>
+        <v>7.547004848027654e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.00775709</v>
+        <v>0.62739</v>
       </c>
       <c r="F96" t="n">
-        <v>666994072</v>
+        <v>605365589</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>22769195</v>
+        <v>57168157</v>
       </c>
       <c r="I96" t="n">
-        <v>0.008159120000000001</v>
+        <v>0.647862</v>
       </c>
       <c r="J96" t="n">
-        <v>0.00760247</v>
+        <v>0.600308</v>
       </c>
       <c r="K96" t="n">
-        <v>1.085e-05</v>
+        <v>0.008542660000000001</v>
       </c>
       <c r="L96" t="n">
-        <v>0.14009</v>
+        <v>1.38041</v>
       </c>
       <c r="M96" t="n">
-        <v>85985041177</v>
+        <v>965350000</v>
       </c>
       <c r="N96" t="n">
-        <v>85985041177</v>
+        <v>965350000</v>
       </c>
       <c r="O96" t="n">
-        <v>0.280991</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>5.652142783531482e-05</v>
+        <v>3.78910570237282e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>injective-protocol</t>
+          <t>beldex</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>inj</t>
+          <t>bdx</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6.27</v>
+        <v>0.076862</v>
       </c>
       <c r="F97" t="n">
-        <v>627155056</v>
+        <v>604714731</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>123250609</v>
+        <v>11695818</v>
       </c>
       <c r="I97" t="n">
-        <v>6.56</v>
+        <v>0.07706300000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>6.2</v>
+        <v>0.076083</v>
       </c>
       <c r="K97" t="n">
-        <v>0.07042</v>
+        <v>0.00037129</v>
       </c>
       <c r="L97" t="n">
-        <v>1.1356</v>
+        <v>0.4854</v>
       </c>
       <c r="M97" t="n">
-        <v>100000000</v>
+        <v>7870595048.404165</v>
       </c>
       <c r="N97" t="n">
-        <v>100000000</v>
+        <v>9939534911.670143</v>
       </c>
       <c r="O97" t="n">
-        <v>52.62</v>
+        <v>0.450785</v>
       </c>
       <c r="P97" s="1" t="n">
-        <v>45365.29608796296</v>
+        <v>43450.66666666666</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.158757643477926e-05</v>
+        <v>3.746930746305719e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>official-trump</t>
+          <t>injective-protocol</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>trump</t>
+          <t>inj</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Official Trump</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2.24</v>
+        <v>5.93</v>
       </c>
       <c r="F98" t="n">
-        <v>612054100</v>
+        <v>593229023</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>158108993</v>
+        <v>83496740</v>
       </c>
       <c r="I98" t="n">
-        <v>2.28</v>
+        <v>6.25</v>
       </c>
       <c r="J98" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="K98" t="n">
-        <v>0.01846282</v>
+        <v>-0.3291334657151408</v>
       </c>
       <c r="L98" t="n">
-        <v>0.83077</v>
+        <v>-5.25602</v>
       </c>
       <c r="M98" t="n">
-        <v>273137120.287634</v>
+        <v>100000000</v>
       </c>
       <c r="N98" t="n">
-        <v>1000000000</v>
+        <v>100000000</v>
       </c>
       <c r="O98" t="n">
-        <v>73.43000000000001</v>
+        <v>52.62</v>
       </c>
       <c r="P98" s="1" t="n">
-        <v>45676.16011574074</v>
+        <v>45365.29608796296</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" t="n">
-        <v>2.213641446556732e-05</v>
+        <v>3.002668203171044e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>beldex</t>
+          <t>xdce-crowd-sale</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>bdx</t>
+          <t>xdc</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Beldex</t>
+          <t>XDC Network</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.076723</v>
+        <v>0.02811165</v>
       </c>
       <c r="F99" t="n">
-        <v>603855340</v>
+        <v>560726767</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>11243163</v>
+        <v>5787636</v>
       </c>
       <c r="I99" t="n">
-        <v>0.077597</v>
+        <v>0.02885457</v>
       </c>
       <c r="J99" t="n">
-        <v>0.075156</v>
+        <v>0.02806083</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.000764723909802631</v>
+        <v>-0.000759056230095898</v>
       </c>
       <c r="L99" t="n">
-        <v>-0.9869</v>
+        <v>-2.62916</v>
       </c>
       <c r="M99" t="n">
-        <v>7870576151.856974</v>
+        <v>19946688440</v>
       </c>
       <c r="N99" t="n">
-        <v>9939516139.411463</v>
+        <v>38065686425.1</v>
       </c>
       <c r="O99" t="n">
-        <v>0.450785</v>
+        <v>0.192754</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>43450.66666666666</v>
+        <v>44428.86097222222</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1.700509637506391e-05</v>
+        <v>8.965540909043664e-06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.619139</v>
+        <v>0.00634582</v>
       </c>
       <c r="F100" t="n">
-        <v>597685497</v>
+        <v>551497765</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>72496974</v>
+        <v>3149003</v>
       </c>
       <c r="I100" t="n">
-        <v>0.639674</v>
+        <v>0.00646956</v>
       </c>
       <c r="J100" t="n">
-        <v>0.589762</v>
+        <v>0.00634072</v>
       </c>
       <c r="K100" t="n">
-        <v>0.03383979</v>
+        <v>-0.00012076737794174</v>
       </c>
       <c r="L100" t="n">
-        <v>5.78163</v>
+        <v>-1.86756</v>
       </c>
       <c r="M100" t="n">
-        <v>965350000</v>
+        <v>86902599207.89294</v>
       </c>
       <c r="N100" t="n">
-        <v>965350000</v>
+        <v>106517929730.2676</v>
       </c>
       <c r="O100" t="n">
-        <v>8.529999999999999</v>
+        <v>0.150073</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>1.314360671059442e-05</v>
+        <v>2.985238694225902e-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260909T133820Z-e822fb</t>
+          <t>20260910T132952Z-c388cc</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>aptos</t>
+          <t>usual-usd</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>apt</t>
+          <t>usd0</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Aptos</t>
+          <t>Usual USD</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.671587</v>
+        <v>0.997173</v>
       </c>
       <c r="F101" t="n">
-        <v>576684796</v>
+        <v>546890845</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>87233923</v>
+        <v>200442</v>
       </c>
       <c r="I101" t="n">
-        <v>0.667743</v>
+        <v>0.999036</v>
       </c>
       <c r="J101" t="n">
-        <v>0.63751</v>
+        <v>0.998624</v>
       </c>
       <c r="K101" t="n">
-        <v>0.03328463</v>
+        <v>-0.001528778750158555</v>
       </c>
       <c r="L101" t="n">
-        <v>5.21455</v>
+        <v>-0.15308</v>
       </c>
       <c r="M101" t="n">
-        <v>858689075.0815318</v>
+        <v>548453143.6102545</v>
       </c>
       <c r="N101" t="n">
-        <v>1208439062.296961</v>
+        <v>548453143.6102545</v>
       </c>
       <c r="O101" t="n">
-        <v>19.92</v>
+        <v>1.33</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>44952.26755787037</v>
+        <v>45485.02012731481</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46274.56631944444</v>
+        <v>46275.56064814814</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76869</v>
+        <v>77677</v>
       </c>
       <c r="F2" t="n">
-        <v>1543780270779</v>
+        <v>1560125511429</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>34152452226</v>
+        <v>29594094775</v>
       </c>
       <c r="I2" t="n">
-        <v>79351</v>
+        <v>78035</v>
       </c>
       <c r="J2" t="n">
-        <v>76748</v>
+        <v>76393</v>
       </c>
       <c r="K2" t="n">
-        <v>-2710.455693790631</v>
+        <v>800.51</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.40595</v>
+        <v>1.0413</v>
       </c>
       <c r="M2" t="n">
-        <v>20082225</v>
+        <v>20082787</v>
       </c>
       <c r="N2" t="n">
-        <v>20082365</v>
+        <v>20082809</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2417.76</v>
+        <v>2506.31</v>
       </c>
       <c r="F3" t="n">
-        <v>295019194043</v>
+        <v>305935492370</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>13585995467</v>
+        <v>16878541137</v>
       </c>
       <c r="I3" t="n">
-        <v>2513.05</v>
+        <v>2512.29</v>
       </c>
       <c r="J3" t="n">
-        <v>2413.62</v>
+        <v>2428.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-96.6624874395302</v>
+        <v>88.77</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.84432</v>
+        <v>3.67177</v>
       </c>
       <c r="M3" t="n">
-        <v>122035556.7865035</v>
+        <v>122038476.3012703</v>
       </c>
       <c r="N3" t="n">
-        <v>122035556.7865035</v>
+        <v>122038476.3012702</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1908151463199907</v>
+        <v>0.1958137278964211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,28 +673,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999689</v>
+        <v>0.99961</v>
       </c>
       <c r="F4" t="n">
-        <v>183399747382</v>
+        <v>183389557643</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>57650362193</v>
+        <v>58668007467</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999919</v>
+        <v>0.999861</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9995579999999999</v>
+        <v>0.999515</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000115082843732628</v>
+        <v>-7.4913892993966e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01151</v>
+        <v>-0.00749</v>
       </c>
       <c r="M4" t="n">
         <v>183460843383.6048</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.118486846457935</v>
+        <v>0.1172373105179005</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>706.52</v>
+        <v>720.65</v>
       </c>
       <c r="F5" t="n">
-        <v>94081938222</v>
+        <v>95991544747</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1262140120</v>
+        <v>886998934</v>
       </c>
       <c r="I5" t="n">
-        <v>746.28</v>
+        <v>723.4</v>
       </c>
       <c r="J5" t="n">
-        <v>704.86</v>
+        <v>704.72</v>
       </c>
       <c r="K5" t="n">
-        <v>-43.96882713677849</v>
+        <v>14.1</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.85871</v>
+        <v>1.99581</v>
       </c>
       <c r="M5" t="n">
-        <v>133161225.51</v>
+        <v>133161118.37</v>
       </c>
       <c r="N5" t="n">
-        <v>133161220.23</v>
+        <v>133161113.02</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06060978760127664</v>
+        <v>0.06119773030115795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -810,31 +810,31 @@
         <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>85090865143</v>
+        <v>85628071806</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2406497456</v>
+        <v>2239415372</v>
       </c>
       <c r="I6" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07915296347920031</v>
+        <v>0.00524616</v>
       </c>
       <c r="L6" t="n">
-        <v>-5.51462</v>
+        <v>0.38688</v>
       </c>
       <c r="M6" t="n">
-        <v>62744504852</v>
+        <v>62879209849</v>
       </c>
       <c r="N6" t="n">
-        <v>99985627691</v>
+        <v>99985622230</v>
       </c>
       <c r="O6" t="n">
         <v>3.65</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0547836609791422</v>
+        <v>0.05455267449316954</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999729</v>
+        <v>0.999807</v>
       </c>
       <c r="F7" t="n">
-        <v>74294024258</v>
+        <v>74180090683</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16283054604</v>
+        <v>16624710113</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999698</v>
+        <v>0.999741</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000171072760730695</v>
+        <v>8.262000000000001e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01711</v>
+        <v>0.00826</v>
       </c>
       <c r="M7" t="n">
-        <v>74315470373.78728</v>
+        <v>74193437886.21786</v>
       </c>
       <c r="N7" t="n">
-        <v>74331256693.94714</v>
+        <v>74212582140.11983</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04778741463987383</v>
+        <v>0.0472122323571965</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>99.40000000000001</v>
+        <v>101.29</v>
       </c>
       <c r="F8" t="n">
-        <v>58279078429</v>
+        <v>59439992570</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3474521512</v>
+        <v>3174746581</v>
       </c>
       <c r="I8" t="n">
-        <v>104.12</v>
+        <v>101.74</v>
       </c>
       <c r="J8" t="n">
-        <v>98.90000000000001</v>
+        <v>98.56</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.139863338806535</v>
+        <v>1.9</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.91663</v>
+        <v>1.90687</v>
       </c>
       <c r="M8" t="n">
-        <v>586335632.9426919</v>
+        <v>586537449.1371635</v>
       </c>
       <c r="N8" t="n">
-        <v>633830911.2985152</v>
+        <v>633830009.5093167</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03740988779446246</v>
+        <v>0.03776088577350404</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338163</v>
+        <v>0.336103</v>
       </c>
       <c r="F9" t="n">
-        <v>32108021382</v>
+        <v>31912142968</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>386070975</v>
+        <v>358032118</v>
       </c>
       <c r="I9" t="n">
-        <v>0.340659</v>
+        <v>0.340962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.338005</v>
+        <v>0.335436</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.00057910542445333</v>
+        <v>-0.002159410412531093</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.17096</v>
+        <v>-0.6383799999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>94943377255.82779</v>
+        <v>94944701333.48628</v>
       </c>
       <c r="N9" t="n">
-        <v>94943389284.71849</v>
+        <v>94944700423.18279</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02045130111062643</v>
+        <v>0.02011003668839505</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.027</v>
+        <v>1.035</v>
       </c>
       <c r="F10" t="n">
-        <v>22977477871</v>
+        <v>23223868031</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>115171089</v>
+        <v>93264084</v>
       </c>
       <c r="I10" t="n">
-        <v>1.042</v>
+        <v>1.036</v>
       </c>
       <c r="J10" t="n">
-        <v>1.019</v>
+        <v>1.015</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.008331250492084719</v>
+        <v>0.007932140000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.80491</v>
+        <v>0.77257</v>
       </c>
       <c r="M10" t="n">
-        <v>22379027660.478</v>
+        <v>22446057111.938</v>
       </c>
       <c r="N10" t="n">
-        <v>22379027660.478</v>
+        <v>22446057111.938</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01453479902499212</v>
+        <v>0.01453911734888443</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1174.12</v>
+        <v>1158.21</v>
       </c>
       <c r="F11" t="n">
-        <v>19885889479</v>
+        <v>19616404230</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1377712454</v>
+        <v>1671260451</v>
       </c>
       <c r="I11" t="n">
-        <v>1293.92</v>
+        <v>1183.37</v>
       </c>
       <c r="J11" t="n">
-        <v>1188.47</v>
+        <v>1055.58</v>
       </c>
       <c r="K11" t="n">
-        <v>-90.49896540877694</v>
+        <v>-17.24410873122633</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.15622</v>
+        <v>-1.46702</v>
       </c>
       <c r="M11" t="n">
-        <v>16921867.3530448</v>
+        <v>16925695.4780448</v>
       </c>
       <c r="N11" t="n">
-        <v>16924839.2280448</v>
+        <v>16926651.7280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01253148025791606</v>
+        <v>0.01222601261850918</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>81.09</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>18036831345</v>
+        <v>18098825995</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1321535350</v>
+        <v>1095111848</v>
       </c>
       <c r="I12" t="n">
-        <v>86.98999999999999</v>
+        <v>82.09</v>
       </c>
       <c r="J12" t="n">
-        <v>80.34</v>
+        <v>78.27</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.605079227248268</v>
+        <v>0.123405</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.46526</v>
+        <v>0.15219</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01133330883547114</v>
+        <v>0.01125294189965125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.083634</v>
+        <v>0.0848</v>
       </c>
       <c r="F13" t="n">
-        <v>13029160774</v>
+        <v>13224091428</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>945647801</v>
+        <v>678267919</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09052300000000001</v>
+        <v>0.085089</v>
       </c>
       <c r="J13" t="n">
-        <v>0.083463</v>
+        <v>0.082747</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.007554012353101672</v>
+        <v>0.00124017</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.284000000000001</v>
+        <v>1.48417</v>
       </c>
       <c r="M13" t="n">
-        <v>155856586383.7052</v>
+        <v>155871456383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171569863126.5791</v>
+        <v>155871546383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008088387726251641</v>
+        <v>0.008127263526073179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,31 +1343,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0158577</v>
+        <v>0.01582451</v>
       </c>
       <c r="F14" t="n">
-        <v>11244080062</v>
+        <v>11227376908</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>30442537</v>
+        <v>39502813</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01646211</v>
+        <v>0.0160076</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01579631</v>
+        <v>0.01551577</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000524735521837818</v>
+        <v>-3.0215214789967e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.20304</v>
+        <v>-0.19058</v>
       </c>
       <c r="M14" t="n">
-        <v>709212596238.4149</v>
+        <v>709212992829.0042</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1379,19 +1379,19 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006931673041868425</v>
+        <v>0.006846970761904443</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.99982</v>
+        <v>0.999744</v>
       </c>
       <c r="F15" t="n">
-        <v>9855532483</v>
+        <v>9744724175</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>152958451</v>
+        <v>197400586</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.999936</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999687</v>
+        <v>0.999592</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000130622034676287</v>
+        <v>-7.2646757613426e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.01306</v>
+        <v>-0.00727</v>
       </c>
       <c r="M15" t="n">
-        <v>9857520169.204882</v>
+        <v>9747194186.835777</v>
       </c>
       <c r="N15" t="n">
-        <v>9838691287.558218</v>
+        <v>9748798031.413788</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1446,19 +1446,19 @@
         <v>45593.90336805556</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.006031907914276781</v>
+        <v>0.005896294264677938</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,34 +1477,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>502.71</v>
+        <v>512.91</v>
       </c>
       <c r="F16" t="n">
-        <v>9437409909</v>
+        <v>9645572026</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>142179940</v>
+        <v>102137061</v>
       </c>
       <c r="I16" t="n">
-        <v>518.34</v>
+        <v>518.6799999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>498.54</v>
+        <v>500.26</v>
       </c>
       <c r="K16" t="n">
-        <v>3.76</v>
+        <v>11.01</v>
       </c>
       <c r="L16" t="n">
-        <v>0.75295</v>
+        <v>2.1934</v>
       </c>
       <c r="M16" t="n">
-        <v>18802821.25212499</v>
+        <v>18803154.24465362</v>
       </c>
       <c r="N16" t="n">
-        <v>18802833.85203534</v>
+        <v>18803235.84437571</v>
       </c>
       <c r="O16" t="n">
         <v>797.73</v>
@@ -1513,19 +1513,19 @@
         <v>46036.48202546296</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.00576096861278378</v>
+        <v>0.005832717935841265</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,28 +1544,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>79.34</v>
+        <v>80.55</v>
       </c>
       <c r="F17" t="n">
-        <v>9350661300</v>
+        <v>9497240871</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>108435650</v>
+        <v>101915128</v>
       </c>
       <c r="I17" t="n">
-        <v>81.98999999999999</v>
+        <v>80.97</v>
       </c>
       <c r="J17" t="n">
-        <v>79.22</v>
+        <v>79</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.906928747854607</v>
+        <v>1.23</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.53455</v>
+        <v>1.54504</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1580,19 +1580,19 @@
         <v>46274.03356481482</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.00570475637027532</v>
+        <v>0.005737608042791911</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.67</v>
+        <v>11.69</v>
       </c>
       <c r="F18" t="n">
-        <v>8732590784</v>
+        <v>8749576424</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>4027997415</v>
+        <v>371507695</v>
       </c>
       <c r="I18" t="n">
-        <v>12.15</v>
+        <v>11.72</v>
       </c>
       <c r="J18" t="n">
-        <v>11.6</v>
+        <v>11.31</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5381755019183387</v>
+        <v>0.02035372</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.40724</v>
+        <v>0.17437</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005304252775656058</v>
+        <v>0.005258205818822348</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.18</v>
+        <v>9.15</v>
       </c>
       <c r="F19" t="n">
-        <v>8447958234</v>
+        <v>8418079995</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>103636</v>
+        <v>189958</v>
       </c>
       <c r="I19" t="n">
         <v>9.23</v>
       </c>
       <c r="J19" t="n">
-        <v>9.17</v>
+        <v>9.02</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.009111009906101586</v>
+        <v>-0.03241308782886954</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.09911</v>
+        <v>-0.35293</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.005119813692299675</v>
+        <v>0.005045650405844996</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.209835</v>
+        <v>0.207783</v>
       </c>
       <c r="F20" t="n">
-        <v>7871290286</v>
+        <v>7799990505</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>462172278</v>
+        <v>475922020</v>
       </c>
       <c r="I20" t="n">
-        <v>0.219716</v>
+        <v>0.211947</v>
       </c>
       <c r="J20" t="n">
-        <v>0.208156</v>
+        <v>0.200878</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01121438589498572</v>
+        <v>-0.002025983797910053</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.07325</v>
+        <v>-0.96563</v>
       </c>
       <c r="M20" t="n">
         <v>37510482444.2993</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004746138553141746</v>
+        <v>0.004649331606272314</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.177265</v>
+        <v>0.1788</v>
       </c>
       <c r="F21" t="n">
-        <v>6168073836</v>
+        <v>6226118444</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>177475184</v>
+        <v>144935960</v>
       </c>
       <c r="I21" t="n">
-        <v>0.188573</v>
+        <v>0.179365</v>
       </c>
       <c r="J21" t="n">
-        <v>0.176372</v>
+        <v>0.173418</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.01210439609112118</v>
+        <v>0.00162509</v>
       </c>
       <c r="L21" t="n">
-        <v>-6.39196</v>
+        <v>0.91722</v>
       </c>
       <c r="M21" t="n">
-        <v>34807089044.92414</v>
+        <v>34811503371.5922</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1848,220 +1848,220 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003642471102614695</v>
+        <v>0.003640165302705976</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bitcoin-cash</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bch</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230.08</v>
+        <v>0.999513</v>
       </c>
       <c r="F22" t="n">
-        <v>4620214173</v>
+        <v>4599511936</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>240408727</v>
+        <v>69743386</v>
       </c>
       <c r="I22" t="n">
-        <v>259.1</v>
+        <v>0.999649</v>
       </c>
       <c r="J22" t="n">
-        <v>238.03</v>
+        <v>0.999302</v>
       </c>
       <c r="K22" t="n">
-        <v>-29.90268411409812</v>
+        <v>1.915e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>-11.50199</v>
+        <v>0.00192</v>
       </c>
       <c r="M22" t="n">
-        <v>20087203.02165078</v>
+        <v>4601732684.783278</v>
       </c>
       <c r="N22" t="n">
-        <v>20087540.52165078</v>
+        <v>4601551140.243678</v>
       </c>
       <c r="O22" t="n">
-        <v>3785.82</v>
+        <v>1.034</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002639473316844796</v>
+        <v>0.002597185687201314</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>bitcoin-cash</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dai</t>
+          <t>bch</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>228.66</v>
       </c>
       <c r="F23" t="n">
-        <v>4594324910</v>
+        <v>4594108661</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>286425661</v>
+        <v>290215500</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>229.44</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9997</v>
+        <v>221.45</v>
       </c>
       <c r="K23" t="n">
-        <v>5.839e-05</v>
+        <v>-1.328170852425927</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00584</v>
+        <v>-0.5775</v>
       </c>
       <c r="M23" t="n">
-        <v>4595256677.058527</v>
+        <v>20087609.27165078</v>
       </c>
       <c r="N23" t="n">
-        <v>4586939586.962975</v>
+        <v>20087999.89665078</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>3785.82</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>43902.79363425926</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002622697329922386</v>
+        <v>0.002593721108857228</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>dai</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.999499</v>
+        <v>0.999938</v>
       </c>
       <c r="F24" t="n">
-        <v>4499423114</v>
+        <v>4579726989</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>130660631</v>
+        <v>295208672</v>
       </c>
       <c r="I24" t="n">
-        <v>0.999881</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999414</v>
+        <v>0.999683</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.000206316856677824</v>
+        <v>0.00012281</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.02064</v>
+        <v>0.01228</v>
       </c>
       <c r="M24" t="n">
-        <v>4501768261.240666</v>
+        <v>4580443616.059474</v>
       </c>
       <c r="N24" t="n">
-        <v>4501768261.240666</v>
+        <v>4586837991.908969</v>
       </c>
       <c r="O24" t="n">
-        <v>1.034</v>
+        <v>1.22</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>43902.79363425926</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002561201902701871</v>
+        <v>0.002584499584991989</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999355</v>
+        <v>0.999592</v>
       </c>
       <c r="F25" t="n">
-        <v>4277305044</v>
+        <v>4278520207</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1116623882</v>
+        <v>1331717650</v>
       </c>
       <c r="I25" t="n">
-        <v>0.999574</v>
+        <v>0.999637</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999229</v>
+        <v>0.999073</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.4809622211958e-05</v>
+        <v>0.00025078</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.00749</v>
+        <v>0.02509</v>
       </c>
       <c r="M25" t="n">
-        <v>4280219884.620713</v>
+        <v>4280220129.914264</v>
       </c>
       <c r="N25" t="n">
-        <v>4280219884.620713</v>
+        <v>4280220129.914264</v>
       </c>
       <c r="O25" t="n">
         <v>1.048</v>
@@ -2116,19 +2116,19 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002417271585428991</v>
+        <v>0.002391365884780729</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,34 +2147,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>52.07</v>
+        <v>53.5</v>
       </c>
       <c r="F26" t="n">
-        <v>4040002355</v>
+        <v>4151707448</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>291648539</v>
+        <v>246229119</v>
       </c>
       <c r="I26" t="n">
-        <v>54.52</v>
+        <v>53.32</v>
       </c>
       <c r="J26" t="n">
-        <v>51.8</v>
+        <v>51.68</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.230848443142769</v>
+        <v>1.43</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.10858</v>
+        <v>2.75287</v>
       </c>
       <c r="M26" t="n">
-        <v>77591379.34298518</v>
+        <v>77595273.10667892</v>
       </c>
       <c r="N26" t="n">
-        <v>77594648.10236211</v>
+        <v>77598279.36456157</v>
       </c>
       <c r="O26" t="n">
         <v>410.26</v>
@@ -2183,19 +2183,19 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002263501784901381</v>
+        <v>0.002310053580930716</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,34 +2214,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.100947</v>
+        <v>0.09754599999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>3995411244</v>
+        <v>3860730361</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>10736871</v>
+        <v>10816765</v>
       </c>
       <c r="I27" t="n">
-        <v>0.105557</v>
+        <v>0.102022</v>
       </c>
       <c r="J27" t="n">
-        <v>0.099992</v>
+        <v>0.09499199999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.003982112945947455</v>
+        <v>-0.003497612882979284</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.79506</v>
+        <v>-3.46147</v>
       </c>
       <c r="M27" t="n">
-        <v>39565437161.70294</v>
+        <v>39571131039.5762</v>
       </c>
       <c r="N27" t="n">
-        <v>39566001895.17695</v>
+        <v>39571821711.34754</v>
       </c>
       <c r="O27" t="n">
         <v>0.194152</v>
@@ -2250,555 +2250,555 @@
         <v>46056.00148148148</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002234607185043836</v>
+        <v>0.00212347915815094</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>the-open-network</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gram</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gram (prev. Toncoin)</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.34</v>
+        <v>6.18</v>
       </c>
       <c r="F28" t="n">
-        <v>3730580854</v>
+        <v>3854268305</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>33649209</v>
+        <v>534492504</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>6.22</v>
       </c>
       <c r="J28" t="n">
-        <v>1.35</v>
+        <v>5.88</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.05871265632901279</v>
+        <v>0.304086</v>
       </c>
       <c r="L28" t="n">
-        <v>-4.2004</v>
+        <v>5.17582</v>
       </c>
       <c r="M28" t="n">
-        <v>2785783668.754508</v>
+        <v>623212423.7271129</v>
       </c>
       <c r="N28" t="n">
-        <v>5246646343.198145</v>
+        <v>890460420.0329479</v>
       </c>
       <c r="O28" t="n">
-        <v>8.25</v>
+        <v>44.92</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>45457.69225694444</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R28" t="b">
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002062999705939589</v>
+        <v>0.002119335689740417</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>the-open-network</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>gram</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Gram (prev. Toncoin)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.87</v>
+        <v>1.36</v>
       </c>
       <c r="F29" t="n">
-        <v>3655422610</v>
+        <v>3794903391</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>685422145</v>
+        <v>30916826</v>
       </c>
       <c r="I29" t="n">
-        <v>6.67</v>
+        <v>1.37</v>
       </c>
       <c r="J29" t="n">
-        <v>5.86</v>
+        <v>1.34</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.8323606899828881</v>
+        <v>0.02288055</v>
       </c>
       <c r="L29" t="n">
-        <v>-12.41337</v>
+        <v>1.70863</v>
       </c>
       <c r="M29" t="n">
-        <v>623212423.7271129</v>
+        <v>2786609237.436568</v>
       </c>
       <c r="N29" t="n">
-        <v>890460420.0329479</v>
+        <v>5247225223.221386</v>
       </c>
       <c r="O29" t="n">
-        <v>44.92</v>
+        <v>8.25</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>45457.69225694444</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002014297905565614</v>
+        <v>0.002081270924307801</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.999946</v>
+        <v>2.61</v>
       </c>
       <c r="F30" t="n">
-        <v>3311944587</v>
+        <v>3414897594</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>1289827691</v>
+        <v>530732610</v>
       </c>
       <c r="I30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.210456</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.765319999999999</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1306023672</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1306023669</v>
+      </c>
+      <c r="O30" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>44577.59010416667</v>
+      </c>
+      <c r="Q30" s="1" t="n">
+        <v>46276.55914351852</v>
+      </c>
+      <c r="R30" t="b">
         <v>1</v>
       </c>
-      <c r="J30" t="n">
-        <v>0.999799</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.556e-05</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.00456</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3312225593.434751</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3312194614.574223</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P30" s="1" t="n">
-        <v>45686.67436342593</v>
-      </c>
-      <c r="Q30" s="1" t="n">
-        <v>46275.56064814814</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
       <c r="S30" t="n">
-        <v>0.001791727536452234</v>
+        <v>0.001837611318806823</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hedera-hashgraph</t>
+          <t>avalanche-2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>hbar</t>
+          <t>avax</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.075183</v>
+        <v>7.54</v>
       </c>
       <c r="F31" t="n">
-        <v>3295094622</v>
+        <v>3337034688</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>62173402</v>
+        <v>258337087</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07882500000000001</v>
+        <v>7.66</v>
       </c>
       <c r="J31" t="n">
-        <v>0.074904</v>
+        <v>7.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.003801348480689221</v>
+        <v>-0.03910654255478985</v>
       </c>
       <c r="L31" t="n">
-        <v>-4.81282</v>
+        <v>-0.5159899999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>43831559702.15789</v>
+        <v>442490100.8059288</v>
       </c>
       <c r="N31" t="n">
-        <v>50000000000</v>
+        <v>469158789.1601316</v>
       </c>
       <c r="O31" t="n">
-        <v>0.569229</v>
+        <v>144.96</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>44454.11143518519</v>
+        <v>44521.26314814815</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001780808925424833</v>
+        <v>0.001787685646333148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>avalanche-2</t>
+          <t>hedera-hashgraph</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>avax</t>
+          <t>hbar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7.58</v>
+        <v>0.075407</v>
       </c>
       <c r="F32" t="n">
-        <v>3271991963</v>
+        <v>3305627660</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>248935563</v>
+        <v>55662699</v>
       </c>
       <c r="I32" t="n">
-        <v>7.96</v>
+        <v>0.07587099999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>7.57</v>
+        <v>0.073326</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.4223569541973546</v>
+        <v>0.00024528</v>
       </c>
       <c r="L32" t="n">
-        <v>-5.27981</v>
+        <v>0.32634</v>
       </c>
       <c r="M32" t="n">
-        <v>431771961.1772119</v>
+        <v>43831559676.41492</v>
       </c>
       <c r="N32" t="n">
-        <v>463441061.1772119</v>
+        <v>50000000000</v>
       </c>
       <c r="O32" t="n">
-        <v>144.96</v>
+        <v>0.569229</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>44521.26314814815</v>
+        <v>44454.11143518519</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001765838630393379</v>
+        <v>0.001767547469197819</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>3135849191</v>
+        <v>3306148548</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>564680351</v>
+        <v>1740405168</v>
       </c>
       <c r="I33" t="n">
-        <v>2.65</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>2.38</v>
+        <v>0.9997470000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.1879549365374089</v>
+        <v>5.111e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>-7.25159</v>
+        <v>0.00511</v>
       </c>
       <c r="M33" t="n">
-        <v>1305942368</v>
+        <v>3306126794.671768</v>
       </c>
       <c r="N33" t="n">
-        <v>1305942367</v>
+        <v>3305944150.525681</v>
       </c>
       <c r="O33" t="n">
-        <v>20.44</v>
+        <v>1.65</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001677619457732779</v>
+        <v>0.001767881462430533</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sui</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.750186</v>
+        <v>5.14e-06</v>
       </c>
       <c r="F34" t="n">
-        <v>3073344321</v>
+        <v>3032067683</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>507529235</v>
+        <v>66559557</v>
       </c>
       <c r="I34" t="n">
-        <v>0.814878</v>
+        <v>5.15e-06</v>
       </c>
       <c r="J34" t="n">
-        <v>0.74918</v>
+        <v>5e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.06634578333673313</v>
+        <v>8.213900000000001e-08</v>
       </c>
       <c r="L34" t="n">
-        <v>-8.12532</v>
+        <v>1.6227</v>
       </c>
       <c r="M34" t="n">
-        <v>4096537146.540959</v>
+        <v>589239233105565.5</v>
       </c>
       <c r="N34" t="n">
-        <v>10000000000</v>
+        <v>589496238721205.9</v>
       </c>
       <c r="O34" t="n">
-        <v>5.35</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>45661.62243055556</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001637116918834434</v>
+        <v>0.001592140892237951</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>sui</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Sui</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.06e-06</v>
+        <v>0.733199</v>
       </c>
       <c r="F35" t="n">
-        <v>2982757372</v>
+        <v>3006788096</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>82600247</v>
+        <v>512139661</v>
       </c>
       <c r="I35" t="n">
-        <v>5.45e-06</v>
+        <v>0.753451</v>
       </c>
       <c r="J35" t="n">
-        <v>5.05e-06</v>
+        <v>0.712406</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.90959254583e-07</v>
+        <v>-0.01700455324618688</v>
       </c>
       <c r="L35" t="n">
-        <v>-7.16822</v>
+        <v>-2.26666</v>
       </c>
       <c r="M35" t="n">
-        <v>589239233105565.5</v>
+        <v>4096537146.540959</v>
       </c>
       <c r="N35" t="n">
-        <v>589496238721205.9</v>
+        <v>10000000000</v>
       </c>
       <c r="O35" t="n">
-        <v>8.616e-05</v>
+        <v>5.35</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>45661.62243055556</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001578417469886619</v>
+        <v>0.001575931628473357</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,34 +2817,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0.999802</v>
       </c>
       <c r="F36" t="n">
-        <v>2798177805</v>
+        <v>2774645441</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>78664296</v>
+        <v>97144192</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9997819999999999</v>
+        <v>0.99966</v>
       </c>
       <c r="K36" t="n">
-        <v>0.00015498</v>
+        <v>-0.00024035531706379</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0155</v>
+        <v>-0.02403</v>
       </c>
       <c r="M36" t="n">
-        <v>2798110720.899619</v>
+        <v>2775204047.281764</v>
       </c>
       <c r="N36" t="n">
-        <v>2798110720.899618</v>
+        <v>2775404030.790055</v>
       </c>
       <c r="O36" t="n">
         <v>1.021</v>
@@ -2853,19 +2853,19 @@
         <v>45222.61454861111</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001458811732089596</v>
+        <v>0.0014270818262235</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2887,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>2797063204</v>
+        <v>2772571255</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
@@ -2908,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2797063203.770449</v>
+        <v>2772571254.640448</v>
       </c>
       <c r="N37" t="n">
-        <v>2797063203.770449</v>
+        <v>2772571254.640448</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -2920,19 +2920,19 @@
         <v>45699.87511574074</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001458089481641613</v>
+        <v>0.001425751858769093</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2951,34 +2951,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.056194</v>
+        <v>0.056899</v>
       </c>
       <c r="F38" t="n">
-        <v>2728019353</v>
+        <v>2762146802</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>6873930</v>
+        <v>5384142</v>
       </c>
       <c r="I38" t="n">
-        <v>0.06001</v>
+        <v>0.05704</v>
       </c>
       <c r="J38" t="n">
-        <v>0.055997</v>
+        <v>0.055842</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.003858741189189184</v>
+        <v>0.00070577</v>
       </c>
       <c r="L38" t="n">
-        <v>-6.42555</v>
+        <v>1.25596</v>
       </c>
       <c r="M38" t="n">
-        <v>48545965688.4151</v>
+        <v>48548017567.46945</v>
       </c>
       <c r="N38" t="n">
-        <v>98912619318.48181</v>
+        <v>98914688510.54858</v>
       </c>
       <c r="O38" t="n">
         <v>0.891544</v>
@@ -2987,19 +2987,19 @@
         <v>44523.66666666666</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001413349747588586</v>
+        <v>0.001419067702565172</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,34 +3018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="F39" t="n">
-        <v>2669935508</v>
+        <v>2713315324</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>1396383</v>
+        <v>1446907</v>
       </c>
       <c r="I39" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.01088605313397406</v>
+        <v>0.01825308</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.91751</v>
+        <v>1.55263</v>
       </c>
       <c r="M39" t="n">
-        <v>2271210359.608458</v>
+        <v>2271580642.297657</v>
       </c>
       <c r="N39" t="n">
-        <v>5412584786.407936</v>
+        <v>5412955068.886312</v>
       </c>
       <c r="O39" t="n">
         <v>5.64</v>
@@ -3054,19 +3054,19 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001375711989259069</v>
+        <v>0.001387756973204089</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4348.64</v>
+        <v>4382.93</v>
       </c>
       <c r="F40" t="n">
-        <v>2664885498</v>
+        <v>2684888372</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>213897427</v>
+        <v>250788877</v>
       </c>
       <c r="I40" t="n">
-        <v>4423.18</v>
+        <v>4389.16</v>
       </c>
       <c r="J40" t="n">
-        <v>4329.92</v>
+        <v>4302.81</v>
       </c>
       <c r="K40" t="n">
-        <v>-76.37241894538511</v>
+        <v>34.92</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.72593</v>
+        <v>0.80321</v>
       </c>
       <c r="M40" t="n">
         <v>612823.6595320001</v>
@@ -3121,19 +3121,19 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001372439632617706</v>
+        <v>0.001369529619925278</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3155,7 +3155,7 @@
         <v>1.14</v>
       </c>
       <c r="F41" t="n">
-        <v>2625074051</v>
+        <v>2605358571</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
@@ -3170,37 +3170,37 @@
         <v>1.14</v>
       </c>
       <c r="K41" t="n">
-        <v>9.82e-05</v>
+        <v>0.00031524</v>
       </c>
       <c r="L41" t="n">
-        <v>0.00864</v>
+        <v>0.02773</v>
       </c>
       <c r="M41" t="n">
-        <v>2309100302.298091</v>
+        <v>2291122606.297392</v>
       </c>
       <c r="N41" t="n">
-        <v>2309100302.298091</v>
+        <v>2291122606.297392</v>
       </c>
       <c r="O41" t="n">
         <v>1.14</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>46275.53819444445</v>
+        <v>46276.53819444445</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001346642207861573</v>
+        <v>0.001318535134866854</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3219,34 +3219,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.999924</v>
       </c>
       <c r="F42" t="n">
-        <v>2421266644</v>
+        <v>2405187563</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>89384433</v>
+        <v>257216446</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0.9997509999999999</v>
+        <v>0.999785</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.7963836192544e-05</v>
+        <v>-8.0108728248263e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.0048</v>
+        <v>-0.00801</v>
       </c>
       <c r="M42" t="n">
-        <v>2421307130.10722</v>
+        <v>2405335190.107209</v>
       </c>
       <c r="N42" t="n">
-        <v>2421307130.107223</v>
+        <v>2405335190.107207</v>
       </c>
       <c r="O42" t="n">
         <v>1.073</v>
@@ -3255,153 +3255,153 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001214577019504439</v>
+        <v>0.001190185543289404</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bittensor</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>tao</t>
+          <t>okb</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bittensor</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>242.46</v>
+        <v>113.15</v>
       </c>
       <c r="F43" t="n">
-        <v>2327098057</v>
+        <v>2378543687</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>226976572</v>
+        <v>34387010</v>
       </c>
       <c r="I43" t="n">
-        <v>264.32</v>
+        <v>114.36</v>
       </c>
       <c r="J43" t="n">
-        <v>242.47</v>
+        <v>108.12</v>
       </c>
       <c r="K43" t="n">
-        <v>-25.06715669403047</v>
+        <v>2.83</v>
       </c>
       <c r="L43" t="n">
-        <v>-9.36999</v>
+        <v>2.56088</v>
       </c>
       <c r="M43" t="n">
-        <v>9597491</v>
+        <v>21000000</v>
       </c>
       <c r="N43" t="n">
         <v>21000000</v>
       </c>
       <c r="O43" t="n">
-        <v>757.6</v>
+        <v>228.74</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>45358.44833333333</v>
+        <v>45934.66666666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001153556704479872</v>
+        <v>0.001173101497818443</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>bittensor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>okb</t>
+          <t>tao</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>110.34</v>
+        <v>239.8</v>
       </c>
       <c r="F44" t="n">
-        <v>2316989762</v>
+        <v>2301541936</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>19348222</v>
+        <v>225240727</v>
       </c>
       <c r="I44" t="n">
-        <v>114.86</v>
+        <v>244.36</v>
       </c>
       <c r="J44" t="n">
-        <v>110.34</v>
+        <v>230.01</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.093440089202119</v>
+        <v>-2.785491097572077</v>
       </c>
       <c r="L44" t="n">
-        <v>-3.577</v>
+        <v>-1.14823</v>
       </c>
       <c r="M44" t="n">
-        <v>21000000</v>
+        <v>9597491</v>
       </c>
       <c r="N44" t="n">
         <v>21000000</v>
       </c>
       <c r="O44" t="n">
-        <v>228.74</v>
+        <v>757.6</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>45934.66666666666</v>
+        <v>45358.44833333333</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001147006629078813</v>
+        <v>0.001123727997678011</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3420,16 +3420,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2215070291</v>
+        <v>2221246321</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>5442811</v>
+        <v>3198815</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.001645623204116653</v>
+        <v>0.00108932</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.14364</v>
+        <v>0.09521</v>
       </c>
       <c r="M45" t="n">
-        <v>1936120771.763623</v>
+        <v>1939633516.713295</v>
       </c>
       <c r="N45" t="n">
-        <v>1936120771.763623</v>
+        <v>1939633516.713294</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,19 +3456,19 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.001080963817715856</v>
+        <v>0.00107224247290756</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3487,28 +3487,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.577569</v>
+        <v>0.586103</v>
       </c>
       <c r="F46" t="n">
-        <v>1907566627</v>
+        <v>1936039659</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>28213900</v>
+        <v>27034282</v>
       </c>
       <c r="I46" t="n">
-        <v>0.642601</v>
+        <v>0.587968</v>
       </c>
       <c r="J46" t="n">
-        <v>0.57539</v>
+        <v>0.567507</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.06314134829896989</v>
+        <v>0.008711989999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>-9.854889999999999</v>
+        <v>1.50885</v>
       </c>
       <c r="M46" t="n">
         <v>3302294382.53684</v>
@@ -3523,86 +3523,86 @@
         <v>45938.71164351852</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0008817044782028966</v>
+        <v>0.0008893680449441083</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>aster-2</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>aster</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.702314</v>
+        <v>124.99</v>
       </c>
       <c r="F47" t="n">
-        <v>1898403981</v>
+        <v>1928768550</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>142200533</v>
+        <v>176763274</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7511330000000001</v>
+        <v>125.34</v>
       </c>
       <c r="J47" t="n">
-        <v>0.701399</v>
+        <v>120.57</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.04892281426983136</v>
+        <v>3.31</v>
       </c>
       <c r="L47" t="n">
-        <v>-6.5123</v>
+        <v>2.72166</v>
       </c>
       <c r="M47" t="n">
-        <v>2704071066.799731</v>
+        <v>15427562.51867931</v>
       </c>
       <c r="N47" t="n">
-        <v>7803968119.651995</v>
+        <v>16000000</v>
       </c>
       <c r="O47" t="n">
-        <v>2.41</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>45924.13766203704</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0008757671740212104</v>
+        <v>0.00088470581198745</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3621,34 +3621,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4349.66</v>
+        <v>4387.11</v>
       </c>
       <c r="F48" t="n">
-        <v>1881254849</v>
+        <v>1896775860</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>146309654</v>
+        <v>179797302</v>
       </c>
       <c r="I48" t="n">
-        <v>4427.77</v>
+        <v>4392.22</v>
       </c>
       <c r="J48" t="n">
-        <v>4330.22</v>
+        <v>4309.71</v>
       </c>
       <c r="K48" t="n">
-        <v>-77.93827460225839</v>
+        <v>37.85</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.76028</v>
+        <v>0.87035</v>
       </c>
       <c r="M48" t="n">
-        <v>432503.321551</v>
+        <v>432503.320539</v>
       </c>
       <c r="N48" t="n">
-        <v>432503.321551</v>
+        <v>432503.320539</v>
       </c>
       <c r="O48" t="n">
         <v>5619.09</v>
@@ -3657,86 +3657,86 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008646547057302942</v>
+        <v>0.0008641921085496178</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>aster-2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>aster</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>121.66</v>
+        <v>0.697635</v>
       </c>
       <c r="F49" t="n">
-        <v>1876667794</v>
+        <v>1887254347</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>227360877</v>
+        <v>127539997</v>
       </c>
       <c r="I49" t="n">
-        <v>130.48</v>
+        <v>0.711375</v>
       </c>
       <c r="J49" t="n">
-        <v>121.65</v>
+        <v>0.678593</v>
       </c>
       <c r="K49" t="n">
-        <v>-8.660694750821918</v>
+        <v>-0.004338511102796705</v>
       </c>
       <c r="L49" t="n">
-        <v>-6.64545</v>
+        <v>-0.61805</v>
       </c>
       <c r="M49" t="n">
-        <v>15427529.56307751</v>
+        <v>2704071066.799731</v>
       </c>
       <c r="N49" t="n">
-        <v>16000000</v>
+        <v>7803968119.651995</v>
       </c>
       <c r="O49" t="n">
-        <v>661.6900000000001</v>
+        <v>2.41</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45924.13766203704</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008616823393600202</v>
+        <v>0.0008580869172086751</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3755,34 +3755,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.092</v>
+        <v>1.088</v>
       </c>
       <c r="F50" t="n">
-        <v>1859047595</v>
+        <v>1851932098</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>194027311</v>
+        <v>214878707</v>
       </c>
       <c r="I50" t="n">
         <v>1.16</v>
       </c>
       <c r="J50" t="n">
-        <v>1.088</v>
+        <v>1.073</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.07838425218558731</v>
+        <v>-0.004645409720101634</v>
       </c>
       <c r="L50" t="n">
-        <v>-6.69596</v>
+        <v>-0.42533</v>
       </c>
       <c r="M50" t="n">
-        <v>1702097434.813982</v>
+        <v>1702250904.807482</v>
       </c>
       <c r="N50" t="n">
-        <v>1702117935.326118</v>
+        <v>1702270902.550952</v>
       </c>
       <c r="O50" t="n">
         <v>54.98</v>
@@ -3791,354 +3791,354 @@
         <v>44504.25704861111</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008502646243020725</v>
+        <v>0.0008354383015173011</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.055999</v>
+        <v>0.354835</v>
       </c>
       <c r="F51" t="n">
-        <v>1777729576</v>
+        <v>1729446777</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>37479304</v>
+        <v>93283877</v>
       </c>
       <c r="I51" t="n">
-        <v>0.056977</v>
+        <v>0.358455</v>
       </c>
       <c r="J51" t="n">
-        <v>0.055019</v>
+        <v>0.342359</v>
       </c>
       <c r="K51" t="n">
-        <v>8.96e-05</v>
+        <v>0.00538958</v>
       </c>
       <c r="L51" t="n">
-        <v>0.16025</v>
+        <v>1.54232</v>
       </c>
       <c r="M51" t="n">
-        <v>31777196737</v>
+        <v>4869330647</v>
       </c>
       <c r="N51" t="n">
-        <v>100000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O51" t="n">
-        <v>0.331336</v>
+        <v>2.14</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.000797571350519025</v>
+        <v>0.0007569007496427422</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.349506</v>
+        <v>0.05234</v>
       </c>
       <c r="F52" t="n">
-        <v>1701671484</v>
+        <v>1664166533</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>117343569</v>
+        <v>87281436</v>
       </c>
       <c r="I52" t="n">
-        <v>0.378074</v>
+        <v>0.056965</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3475</v>
+        <v>0.04828182</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.02968519707974521</v>
+        <v>-0.003616400874016316</v>
       </c>
       <c r="L52" t="n">
-        <v>-7.82856</v>
+        <v>-6.46287</v>
       </c>
       <c r="M52" t="n">
-        <v>4869330647</v>
+        <v>31777204151</v>
       </c>
       <c r="N52" t="n">
-        <v>10000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="O52" t="n">
-        <v>2.14</v>
+        <v>0.331336</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R52" t="b">
         <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0007482864575216659</v>
+        <v>0.000715043076350333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>morpho</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>Morpho</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.00387964</v>
+        <v>2.37</v>
       </c>
       <c r="F53" t="n">
-        <v>1608873443</v>
+        <v>1637472718</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>369368662</v>
+        <v>24546993</v>
       </c>
       <c r="I53" t="n">
-        <v>0.00482089</v>
+        <v>2.38</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00384956</v>
+        <v>2.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.000764813556465756</v>
+        <v>0.1261</v>
       </c>
       <c r="L53" t="n">
-        <v>-16.46724</v>
+        <v>5.61006</v>
       </c>
       <c r="M53" t="n">
-        <v>414657242500.5876</v>
+        <v>688937204.4827486</v>
       </c>
       <c r="N53" t="n">
-        <v>834788573196.6761</v>
+        <v>1000000000</v>
       </c>
       <c r="O53" t="n">
-        <v>0.00881908</v>
+        <v>4.17</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45674.19883101852</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R53" t="b">
         <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0006881542427791564</v>
+        <v>0.0006979270100072292</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>internet-computer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>morpho</t>
+          <t>icp</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Morpho</t>
+          <t>Internet Computer</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="F54" t="n">
-        <v>1548374384</v>
+        <v>1556817159</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>20872061</v>
+        <v>46260797</v>
       </c>
       <c r="I54" t="n">
-        <v>2.39</v>
+        <v>2.83</v>
       </c>
       <c r="J54" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.1070669937011086</v>
+        <v>0.052938</v>
       </c>
       <c r="L54" t="n">
-        <v>-4.54654</v>
+        <v>1.92892</v>
       </c>
       <c r="M54" t="n">
-        <v>688887784.3170698</v>
+        <v>556272745.1443182</v>
       </c>
       <c r="N54" t="n">
-        <v>1000000000</v>
+        <v>556273142.5125661</v>
       </c>
       <c r="O54" t="n">
-        <v>4.17</v>
+        <v>700.65</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>45674.19883101852</v>
+        <v>44326.33741898148</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0006489514496134283</v>
+        <v>0.0006462106892496255</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>internet-computer</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>icp</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.74</v>
+        <v>0.00369072</v>
       </c>
       <c r="F55" t="n">
-        <v>1526634131</v>
+        <v>1531678178</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>55541922</v>
+        <v>216800001</v>
       </c>
       <c r="I55" t="n">
-        <v>2.89</v>
+        <v>0.00392038</v>
       </c>
       <c r="J55" t="n">
-        <v>2.72</v>
+        <v>0.00356584</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.1419245793196384</v>
+        <v>-0.000189200679835274</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.91782</v>
+        <v>-4.87641</v>
       </c>
       <c r="M55" t="n">
-        <v>556268872.9048556</v>
+        <v>414503015998.9233</v>
       </c>
       <c r="N55" t="n">
-        <v>556269825.7674338</v>
+        <v>834631199451.8402</v>
       </c>
       <c r="O55" t="n">
-        <v>700.65</v>
+        <v>0.00881908</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>44326.33741898148</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R55" t="b">
         <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006348639802243657</v>
+        <v>0.0006300915820109626</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4160,25 +4160,25 @@
         <v>1.68e-06</v>
       </c>
       <c r="F56" t="n">
-        <v>1510151983</v>
+        <v>1509536401</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>45332687</v>
+        <v>63687124</v>
       </c>
       <c r="I56" t="n">
-        <v>1.69e-06</v>
+        <v>1.7e-06</v>
       </c>
       <c r="J56" t="n">
         <v>1.68e-06</v>
       </c>
       <c r="K56" t="n">
-        <v>-7.002670966e-09</v>
+        <v>1.133e-09</v>
       </c>
       <c r="L56" t="n">
-        <v>-0.41475</v>
+        <v>0.06737</v>
       </c>
       <c r="M56" t="n">
         <v>898232728634017.2</v>
@@ -4193,220 +4193,220 @@
         <v>45629.67800925926</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0006241837109829727</v>
+        <v>0.000615894281097391</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.405233</v>
+        <v>0.998903</v>
       </c>
       <c r="F57" t="n">
-        <v>1491195699</v>
+        <v>1493031049</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>206723334</v>
+        <v>7558824</v>
       </c>
       <c r="I57" t="n">
-        <v>0.44988</v>
+        <v>0.999358</v>
       </c>
       <c r="J57" t="n">
-        <v>0.402342</v>
+        <v>0.99427</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.04889978019534369</v>
+        <v>-0.000164509772873078</v>
       </c>
       <c r="L57" t="n">
-        <v>-10.76774</v>
+        <v>-0.01647</v>
       </c>
       <c r="M57" t="n">
-        <v>3680240835.629099</v>
+        <v>1494666477</v>
       </c>
       <c r="N57" t="n">
-        <v>10000000000</v>
+        <v>1497163797</v>
       </c>
       <c r="O57" t="n">
-        <v>11.74</v>
+        <v>1.24</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006119002260308713</v>
+        <v>0.0006053110542394735</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.999068</v>
+        <v>0.147305</v>
       </c>
       <c r="F58" t="n">
-        <v>1485914228</v>
+        <v>1488701361</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>2787411</v>
+        <v>317283224</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9997470000000001</v>
+        <v>0.150054</v>
       </c>
       <c r="J58" t="n">
-        <v>0.998008</v>
+        <v>0.141387</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.000648900614201087</v>
+        <v>0.00106833</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.06491</v>
+        <v>0.73055</v>
       </c>
       <c r="M58" t="n">
-        <v>1487315929</v>
+        <v>10095312500</v>
       </c>
       <c r="N58" t="n">
-        <v>1491270221</v>
+        <v>15000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45393.21892361111</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006084778849458009</v>
+        <v>0.0006025348595646793</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.146259</v>
+        <v>0.408621</v>
       </c>
       <c r="F59" t="n">
-        <v>1476341265</v>
+        <v>1489134201</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>356558838</v>
+        <v>141293490</v>
       </c>
       <c r="I59" t="n">
-        <v>0.164399</v>
+        <v>0.410786</v>
       </c>
       <c r="J59" t="n">
-        <v>0.145743</v>
+        <v>0.391882</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.01738844476775372</v>
+        <v>0.00333089</v>
       </c>
       <c r="L59" t="n">
-        <v>-10.62556</v>
+        <v>0.82185</v>
       </c>
       <c r="M59" t="n">
-        <v>10095312500</v>
+        <v>3642314682.371945</v>
       </c>
       <c r="N59" t="n">
-        <v>15000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O59" t="n">
-        <v>1.52</v>
+        <v>11.74</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006022746993975403</v>
+        <v>0.0006028123964456365</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4425,28 +4425,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3.34e-06</v>
+        <v>3.35e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1405799346</v>
+        <v>1411275814</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>253476976</v>
+        <v>220807133</v>
       </c>
       <c r="I60" t="n">
-        <v>3.69e-06</v>
+        <v>3.36e-06</v>
       </c>
       <c r="J60" t="n">
-        <v>3.33e-06</v>
+        <v>3.22e-06</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.78331934945e-07</v>
+        <v>1.121e-08</v>
       </c>
       <c r="L60" t="n">
-        <v>-10.17511</v>
+        <v>0.33555</v>
       </c>
       <c r="M60" t="n">
         <v>420690000000000</v>
@@ -4461,19 +4461,19 @@
         <v>45635.35457175926</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005565642320649734</v>
+        <v>0.0005528896215534354</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4495,31 +4495,31 @@
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>1383051937</v>
+        <v>1383270977</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>26045464</v>
+        <v>28018522</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0.999891</v>
+        <v>0.999893</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.2111144466213e-05</v>
+        <v>0.00012525</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.00821</v>
+        <v>0.01252</v>
       </c>
       <c r="M61" t="n">
-        <v>1382942039.16</v>
+        <v>1382942040.16</v>
       </c>
       <c r="N61" t="n">
-        <v>1382942039.16</v>
+        <v>1382942045.16</v>
       </c>
       <c r="O61" t="n">
         <v>1.002</v>
@@ -4528,287 +4528,287 @@
         <v>46092.00303240741</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0005418241355275509</v>
+        <v>0.0005349329282887293</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.058619</v>
+        <v>1.96</v>
       </c>
       <c r="F62" t="n">
-        <v>1373490617</v>
+        <v>1374457843</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>14224398</v>
+        <v>9190660</v>
       </c>
       <c r="I62" t="n">
-        <v>0.064653</v>
+        <v>1.97</v>
       </c>
       <c r="J62" t="n">
-        <v>0.058177</v>
+        <v>1.93</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.005978917726946816</v>
+        <v>0.02435951</v>
       </c>
       <c r="L62" t="n">
-        <v>-9.255559999999999</v>
+        <v>1.25617</v>
       </c>
       <c r="M62" t="n">
-        <v>23426487411.36321</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N62" t="n">
-        <v>23462665147.36596</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O62" t="n">
-        <v>0.100535</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005356284945283853</v>
+        <v>0.0005292819493546704</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.94</v>
+        <v>0.058158</v>
       </c>
       <c r="F63" t="n">
-        <v>1357386380</v>
+        <v>1365122165</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>12899919</v>
+        <v>14829654</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0.061385</v>
       </c>
       <c r="J63" t="n">
-        <v>1.92</v>
+        <v>0.058078</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.05123757344788293</v>
+        <v>-0.000474670622074118</v>
       </c>
       <c r="L63" t="n">
-        <v>-2.57431</v>
+        <v>-0.80957</v>
       </c>
       <c r="M63" t="n">
-        <v>699992029.6481038</v>
+        <v>23425278090.46795</v>
       </c>
       <c r="N63" t="n">
-        <v>910920874.6481038</v>
+        <v>23462665147.36596</v>
       </c>
       <c r="O63" t="n">
-        <v>8.449999999999999</v>
+        <v>0.100535</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>45653.15375</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.000525193107885382</v>
+        <v>0.0005232959153611833</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>falcon-finance</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>usdf</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Falcon USD</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.996576</v>
+        <v>0.499741</v>
       </c>
       <c r="F64" t="n">
-        <v>1339860323</v>
+        <v>1352987499</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>369807</v>
+        <v>14777585</v>
       </c>
       <c r="I64" t="n">
-        <v>1.01</v>
+        <v>0.516378</v>
       </c>
       <c r="J64" t="n">
-        <v>0.991111</v>
+        <v>0.451093</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.000221950111248592</v>
+        <v>0.03125239</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.02227</v>
+        <v>6.6709</v>
       </c>
       <c r="M64" t="n">
-        <v>1344475004.618144</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N64" t="n">
-        <v>1344475004.618144</v>
+        <v>10000000000</v>
       </c>
       <c r="O64" t="n">
-        <v>1.075</v>
+        <v>0.745279</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>45785.55951388889</v>
+        <v>46253.4</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005138363959143452</v>
+        <v>0.0005155151710836267</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>falcon-finance</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bfusd</t>
+          <t>usdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BFUSD</t>
+          <t>Falcon USD</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.999521</v>
+        <v>0.996268</v>
       </c>
       <c r="F65" t="n">
-        <v>1319338368</v>
+        <v>1339475574</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>6759066</v>
+        <v>410919</v>
       </c>
       <c r="I65" t="n">
-        <v>0.999857</v>
+        <v>1.002</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9994769999999999</v>
+        <v>0.992092</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.000136606878920031</v>
+        <v>-0.000302944713080122</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.01367</v>
+        <v>-0.0304</v>
       </c>
       <c r="M65" t="n">
-        <v>1320000000</v>
+        <v>1344489118.116781</v>
       </c>
       <c r="N65" t="n">
-        <v>1320000000</v>
+        <v>1344489118.116781</v>
       </c>
       <c r="O65" t="n">
-        <v>1.007</v>
+        <v>1.075</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>45940.56990740741</v>
+        <v>45785.55951388889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005005383716058783</v>
+        <v>0.0005068513287395089</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4830,7 +4830,7 @@
         <v>1.17</v>
       </c>
       <c r="F66" t="n">
-        <v>1314745897</v>
+        <v>1332238102</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
@@ -4845,16 +4845,16 @@
         <v>1.17</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.004585650811628206</v>
+        <v>-4.7045165355586e-05</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.38899</v>
+        <v>-0.00401</v>
       </c>
       <c r="M66" t="n">
-        <v>1119625332.18736</v>
+        <v>1134566984.99023</v>
       </c>
       <c r="N66" t="n">
-        <v>1119625332.18736</v>
+        <v>1134566984.99023</v>
       </c>
       <c r="O66" t="n">
         <v>1.18</v>
@@ -4863,287 +4863,287 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0004975624957210549</v>
+        <v>0.0005022106638173779</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>united-stables</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>bfusd</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>United Stables</t>
+          <t>BFUSD</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999181</v>
+        <v>0.999538</v>
       </c>
       <c r="F67" t="n">
-        <v>1280606791</v>
+        <v>1319394082</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>176865024</v>
+        <v>4259383</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999373</v>
+        <v>0.999725</v>
       </c>
       <c r="J67" t="n">
-        <v>0.998997</v>
+        <v>0.999358</v>
       </c>
       <c r="K67" t="n">
-        <v>7.446e-05</v>
+        <v>2.154e-05</v>
       </c>
       <c r="L67" t="n">
-        <v>0.00745</v>
+        <v>0.00216</v>
       </c>
       <c r="M67" t="n">
-        <v>1281500007.8</v>
+        <v>1320000000</v>
       </c>
       <c r="N67" t="n">
-        <v>1281500007.8</v>
+        <v>1320000000</v>
       </c>
       <c r="O67" t="n">
-        <v>1.008</v>
+        <v>1.007</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46058.54591435185</v>
+        <v>45940.56990740741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004754406919524894</v>
+        <v>0.0004939750819632235</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>united-stables</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>u</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>United Stables</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.468503</v>
+        <v>0.999318</v>
       </c>
       <c r="F68" t="n">
-        <v>1268869271</v>
+        <v>1283500273</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>10751913</v>
+        <v>162320060</v>
       </c>
       <c r="I68" t="n">
-        <v>0.471754</v>
+        <v>0.999425</v>
       </c>
       <c r="J68" t="n">
-        <v>0.43293</v>
+        <v>0.99893</v>
       </c>
       <c r="K68" t="n">
-        <v>0.01929156</v>
+        <v>4.72e-05</v>
       </c>
       <c r="L68" t="n">
-        <v>4.29453</v>
+        <v>0.00472</v>
       </c>
       <c r="M68" t="n">
-        <v>2708142280.000001</v>
+        <v>1284500007.8</v>
       </c>
       <c r="N68" t="n">
-        <v>10000000000</v>
+        <v>1286000007.8</v>
       </c>
       <c r="O68" t="n">
-        <v>0.745279</v>
+        <v>1.008</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46253.4</v>
+        <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004678348948302797</v>
+        <v>0.0004709599821676079</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.71</v>
+        <v>26.08</v>
       </c>
       <c r="F69" t="n">
-        <v>1219499871</v>
+        <v>1249707775</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>60458123</v>
+        <v>102651981</v>
       </c>
       <c r="I69" t="n">
-        <v>8.369999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="J69" t="n">
-        <v>7.67</v>
+        <v>22.72</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.6696181749045396</v>
+        <v>2.02</v>
       </c>
       <c r="L69" t="n">
-        <v>-7.98999</v>
+        <v>8.415760000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>158130846.3427831</v>
+        <v>47928096.04257578</v>
       </c>
       <c r="N69" t="n">
-        <v>158131277.2419831</v>
+        <v>80986596.52104242</v>
       </c>
       <c r="O69" t="n">
-        <v>167.09</v>
+        <v>29.19</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>46274.32083333333</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
       </c>
       <c r="S69" t="n">
-        <v>0.0004358440108577523</v>
+        <v>0.000449292242368437</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>24.03</v>
+        <v>7.71</v>
       </c>
       <c r="F70" t="n">
-        <v>1152251647</v>
+        <v>1218614410</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>154151810</v>
+        <v>52635522</v>
       </c>
       <c r="I70" t="n">
-        <v>26.08</v>
+        <v>7.78</v>
       </c>
       <c r="J70" t="n">
-        <v>22.23</v>
+        <v>7.43</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.130860004533968</v>
+        <v>-0.003077005696481727</v>
       </c>
       <c r="L70" t="n">
-        <v>-8.144360000000001</v>
+        <v>-0.03991</v>
       </c>
       <c r="M70" t="n">
-        <v>47914366.51301605</v>
+        <v>158140942.4707831</v>
       </c>
       <c r="N70" t="n">
-        <v>80979732.14382271</v>
+        <v>158141763.9747831</v>
       </c>
       <c r="O70" t="n">
-        <v>29.19</v>
+        <v>167.09</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46274.32083333333</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0003922678253796517</v>
+        <v>0.0004293551858566441</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5162,28 +5162,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.54</v>
+        <v>4.66</v>
       </c>
       <c r="F71" t="n">
-        <v>1135234423</v>
+        <v>1163955696</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>101341183</v>
+        <v>96426083</v>
       </c>
       <c r="I71" t="n">
-        <v>5.08</v>
+        <v>4.67</v>
       </c>
       <c r="J71" t="n">
-        <v>4.42</v>
+        <v>4.29</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.5517406813879191</v>
+        <v>0.121124</v>
       </c>
       <c r="L71" t="n">
-        <v>-10.83157</v>
+        <v>2.66667</v>
       </c>
       <c r="M71" t="n">
         <v>250000000</v>
@@ -5198,19 +5198,19 @@
         <v>46021.04538194444</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003812408321709332</v>
+        <v>0.0003943080344827119</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5229,34 +5229,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.09607</v>
+        <v>0.09493699999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>1070290641</v>
+        <v>1060010138</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>6550211</v>
+        <v>5562293</v>
       </c>
       <c r="I72" t="n">
-        <v>0.097702</v>
+        <v>0.09700499999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>0.093235</v>
+        <v>0.093487</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.001789429385238753</v>
+        <v>-0.001126560587777992</v>
       </c>
       <c r="L72" t="n">
-        <v>-1.82856</v>
+        <v>-1.17272</v>
       </c>
       <c r="M72" t="n">
-        <v>11141680597.24892</v>
+        <v>11162267022.98023</v>
       </c>
       <c r="N72" t="n">
-        <v>17141047072.69065</v>
+        <v>17172718496.89267</v>
       </c>
       <c r="O72" t="n">
         <v>2.99</v>
@@ -5265,220 +5265,220 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0003391579023662542</v>
+        <v>0.000327658173202151</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>polygon-ecosystem-token</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>pol</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>POL (ex-MATIC)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.03771009</v>
+        <v>0.09686599999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>1045172018</v>
+        <v>1038022867</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>29437666</v>
+        <v>79635826</v>
       </c>
       <c r="I73" t="n">
-        <v>0.03928072</v>
+        <v>0.09592199999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>0.03484704</v>
+        <v>0.091382</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00152136</v>
+        <v>0.00588087</v>
       </c>
       <c r="L73" t="n">
-        <v>4.20395</v>
+        <v>6.46357</v>
       </c>
       <c r="M73" t="n">
-        <v>27691695062.44326</v>
+        <v>10712360273.58979</v>
       </c>
       <c r="N73" t="n">
-        <v>27692331519.9827</v>
+        <v>10712360273.58979</v>
       </c>
       <c r="O73" t="n">
-        <v>0.207411</v>
+        <v>1.29</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003228812825583841</v>
+        <v>0.0003135599414904304</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.148208</v>
+        <v>0.03595403</v>
       </c>
       <c r="F74" t="n">
-        <v>989717749</v>
+        <v>994734819</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>306660358</v>
+        <v>21428726</v>
       </c>
       <c r="I74" t="n">
-        <v>0.165926</v>
+        <v>0.03822965</v>
       </c>
       <c r="J74" t="n">
-        <v>0.145666</v>
+        <v>0.03396212</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.01830829186910402</v>
+        <v>-0.001802680228815516</v>
       </c>
       <c r="L74" t="n">
-        <v>-10.99492</v>
+        <v>-4.77446</v>
       </c>
       <c r="M74" t="n">
-        <v>6678075931</v>
+        <v>27693237714.84791</v>
       </c>
       <c r="N74" t="n">
-        <v>10000000000</v>
+        <v>27694208549.70138</v>
       </c>
       <c r="O74" t="n">
-        <v>2.39</v>
+        <v>0.207411</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002869474635255353</v>
+        <v>0.0002858036578182964</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>polygon-ecosystem-token</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>pol</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>POL (ex-MATIC)</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.091</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>974631690</v>
+        <v>981524179</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>84450093</v>
+        <v>5271661</v>
       </c>
       <c r="I75" t="n">
-        <v>0.098193</v>
+        <v>9.51</v>
       </c>
       <c r="J75" t="n">
-        <v>0.090625</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.006450902539119729</v>
+        <v>0.241067</v>
       </c>
       <c r="L75" t="n">
-        <v>-6.61967</v>
+        <v>2.68682</v>
       </c>
       <c r="M75" t="n">
-        <v>10711779103.38826</v>
+        <v>106624324.9792634</v>
       </c>
       <c r="N75" t="n">
-        <v>10711779103.38826</v>
+        <v>118875580.2820878</v>
       </c>
       <c r="O75" t="n">
-        <v>1.29</v>
+        <v>25.38</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45364.45493055556</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002771718461781155</v>
+        <v>0.0002773329993277486</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5533,153 +5533,153 @@
         <v>46273.93067129629</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002743965109270188</v>
+        <v>0.0002701672854730611</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>8.960000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="F77" t="n">
-        <v>956551613</v>
+        <v>961459699</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>2796794</v>
+        <v>2770787</v>
       </c>
       <c r="I77" t="n">
-        <v>9.35</v>
+        <v>7.05</v>
       </c>
       <c r="J77" t="n">
-        <v>9</v>
+        <v>6.83</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.4208429464590857</v>
+        <v>0.155616</v>
       </c>
       <c r="L77" t="n">
-        <v>-4.48451</v>
+        <v>2.27035</v>
       </c>
       <c r="M77" t="n">
-        <v>106623165.6073925</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N77" t="n">
-        <v>118874451.7093768</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O77" t="n">
-        <v>25.38</v>
+        <v>28.83</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002654561347147118</v>
+        <v>0.0002644676606408699</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1.79</v>
+        <v>0.143521</v>
       </c>
       <c r="F78" t="n">
-        <v>947879945</v>
+        <v>958743093</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>65021941</v>
+        <v>202835706</v>
       </c>
       <c r="I78" t="n">
-        <v>1.96</v>
+        <v>0.153242</v>
       </c>
       <c r="J78" t="n">
-        <v>1.78</v>
+        <v>0.138315</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.1677502701765261</v>
+        <v>-0.00476547542386474</v>
       </c>
       <c r="L78" t="n">
-        <v>-8.57339</v>
+        <v>-3.2137</v>
       </c>
       <c r="M78" t="n">
-        <v>529892426.812725</v>
+        <v>6678075931</v>
       </c>
       <c r="N78" t="n">
-        <v>529922361.717385</v>
+        <v>10000000000</v>
       </c>
       <c r="O78" t="n">
-        <v>43.84</v>
+        <v>2.39</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002598369794315551</v>
+        <v>0.0002627257736710204</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5698,28 +5698,28 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>65.12</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>946567813</v>
+        <v>942825988</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>7039868</v>
+        <v>9224706</v>
       </c>
       <c r="I79" t="n">
-        <v>67.78</v>
+        <v>66.38</v>
       </c>
       <c r="J79" t="n">
-        <v>64.81999999999999</v>
+        <v>63.82</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.68778858197895</v>
+        <v>-0.27550565831352</v>
       </c>
       <c r="L79" t="n">
-        <v>-3.96358</v>
+        <v>-0.42321</v>
       </c>
       <c r="M79" t="n">
         <v>14544176.16408117</v>
@@ -5734,756 +5734,756 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002589867308450088</v>
+        <v>0.0002525197306168465</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6.86</v>
+        <v>1.73</v>
       </c>
       <c r="F80" t="n">
-        <v>940197876</v>
+        <v>916337794</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>2816887</v>
+        <v>54228029</v>
       </c>
       <c r="I80" t="n">
-        <v>7.06</v>
+        <v>1.82</v>
       </c>
       <c r="J80" t="n">
-        <v>6.85</v>
+        <v>1.7</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.1494727959964726</v>
+        <v>-0.0601896227796066</v>
       </c>
       <c r="L80" t="n">
-        <v>-2.13395</v>
+        <v>-3.3649</v>
       </c>
       <c r="M80" t="n">
-        <v>137155021.2773955</v>
+        <v>530093191.963316</v>
       </c>
       <c r="N80" t="n">
-        <v>142155021.2773955</v>
+        <v>530111563.170892</v>
       </c>
       <c r="O80" t="n">
-        <v>28.83</v>
+        <v>43.84</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002548590745340285</v>
+        <v>0.0002355355083985909</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>eutbl</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>Spiko EU T-Bills Money Market Fund</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.097095</v>
+        <v>1.23</v>
       </c>
       <c r="F81" t="n">
-        <v>877629397</v>
+        <v>880185352</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
       </c>
       <c r="H81" t="n">
-        <v>47216826</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.101985</v>
+        <v>1.23</v>
       </c>
       <c r="J81" t="n">
-        <v>0.09628399999999999</v>
+        <v>1.23</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.003935790281541229</v>
+        <v>-8.1966592208715e-05</v>
       </c>
       <c r="L81" t="n">
-        <v>-3.89563</v>
+        <v>-0.00667</v>
       </c>
       <c r="M81" t="n">
-        <v>9039923262.00091</v>
+        <v>716808406.83022</v>
       </c>
       <c r="N81" t="n">
-        <v>9039974297.342701</v>
+        <v>716808406.83022</v>
       </c>
       <c r="O81" t="n">
-        <v>3.56</v>
+        <v>1.26</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>46049.54175925926</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002143153176314426</v>
+        <v>0.0002123545731992866</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>eutbl</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Spiko EU T-Bills Money Market Fund</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1.23</v>
+        <v>0.102603</v>
       </c>
       <c r="F82" t="n">
-        <v>865442517</v>
+        <v>840199045</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>19464978</v>
       </c>
       <c r="I82" t="n">
-        <v>1.23</v>
+        <v>0.104605</v>
       </c>
       <c r="J82" t="n">
-        <v>1.23</v>
+        <v>0.102366</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.004782788274432015</v>
+        <v>-0.001171828866008306</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.38797</v>
+        <v>-1.1292</v>
       </c>
       <c r="M82" t="n">
-        <v>704755041.68557</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N82" t="n">
-        <v>704755041.68557</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O82" t="n">
-        <v>1.26</v>
+        <v>0.193254</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46049.54175925926</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0002064183396639746</v>
+        <v>0.0001867153648872593</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.103766</v>
+        <v>0.832133</v>
       </c>
       <c r="F83" t="n">
-        <v>849689853</v>
+        <v>832126414</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>24422970</v>
+        <v>3345268</v>
       </c>
       <c r="I83" t="n">
-        <v>0.105928</v>
+        <v>0.846696</v>
       </c>
       <c r="J83" t="n">
-        <v>0.102162</v>
+        <v>0.820491</v>
       </c>
       <c r="K83" t="n">
-        <v>0.00112145</v>
+        <v>-0.004223176933168871</v>
       </c>
       <c r="L83" t="n">
-        <v>1.09255</v>
+        <v>-0.50495</v>
       </c>
       <c r="M83" t="n">
-        <v>8188743036.341737</v>
+        <v>1000000000</v>
       </c>
       <c r="N83" t="n">
-        <v>8188743036.341737</v>
+        <v>1000000000</v>
       </c>
       <c r="O83" t="n">
-        <v>0.193254</v>
+        <v>4.07</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001962107688552913</v>
+        <v>0.0001815391962594555</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.836378</v>
+        <v>0.09136900000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>837041793</v>
+        <v>826564762</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>3036475</v>
+        <v>44325049</v>
       </c>
       <c r="I84" t="n">
-        <v>0.849623</v>
+        <v>0.098091</v>
       </c>
       <c r="J84" t="n">
-        <v>0.831659</v>
+        <v>0.08820699999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.007957469623558033</v>
+        <v>-0.005872704953126001</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.94245</v>
+        <v>-6.03931</v>
       </c>
       <c r="M84" t="n">
-        <v>1000000000</v>
+        <v>9040075710.158276</v>
       </c>
       <c r="N84" t="n">
-        <v>1000000000</v>
+        <v>9040214132.26104</v>
       </c>
       <c r="O84" t="n">
-        <v>4.07</v>
+        <v>3.56</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001880149507992168</v>
+        <v>0.0001779730666294548</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
+          <t>jupiter-exchange-solana</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ustb</t>
+          <t>jup</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Invesco Short Duration US Government Securities Fund</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11.21</v>
+        <v>0.242788</v>
       </c>
       <c r="F85" t="n">
-        <v>812242372</v>
+        <v>805923333</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>92695382</v>
       </c>
       <c r="I85" t="n">
-        <v>11.21</v>
+        <v>0.2431</v>
       </c>
       <c r="J85" t="n">
-        <v>11.21</v>
+        <v>0.22017</v>
       </c>
       <c r="K85" t="n">
-        <v>0.001101</v>
+        <v>0.01816376</v>
       </c>
       <c r="L85" t="n">
-        <v>0.00983</v>
+        <v>8.0863</v>
       </c>
       <c r="M85" t="n">
-        <v>72475935.23173</v>
+        <v>3319369204.37</v>
       </c>
       <c r="N85" t="n">
-        <v>72619184.682154</v>
+        <v>6861487243.558427</v>
       </c>
       <c r="O85" t="n">
-        <v>11.21</v>
+        <v>2</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46275.55902777778</v>
+        <v>45322.29359953704</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001719451707371366</v>
+        <v>0.0001647377884131164</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>superstate-short-duration-us-government-securities-fund-ustb</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>ustb</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Invesco Short Duration US Government Securities Fund</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.02961505</v>
+        <v>11.21</v>
       </c>
       <c r="F86" t="n">
-        <v>773093892</v>
+        <v>806196290</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
       </c>
       <c r="H86" t="n">
-        <v>9830366</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0.02970387</v>
+        <v>11.21</v>
       </c>
       <c r="J86" t="n">
-        <v>0.02800359</v>
+        <v>11.21</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0009908600000000001</v>
+        <v>0.001097</v>
       </c>
       <c r="L86" t="n">
-        <v>3.46161</v>
+        <v>0.00979</v>
       </c>
       <c r="M86" t="n">
-        <v>26193447530</v>
+        <v>71929405.877505</v>
       </c>
       <c r="N86" t="n">
-        <v>100000000000</v>
+        <v>71806917.885897</v>
       </c>
       <c r="O86" t="n">
-        <v>0.04323745</v>
+        <v>11.21</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>46276.55543981482</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001465773420541708</v>
+        <v>0.0001649128083614008</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.12</v>
+        <v>0.02873046</v>
       </c>
       <c r="F87" t="n">
-        <v>750052639</v>
+        <v>754085357</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>10760536</v>
       </c>
       <c r="I87" t="n">
-        <v>1.12</v>
+        <v>0.03046497</v>
       </c>
       <c r="J87" t="n">
-        <v>1.12</v>
+        <v>0.02650292</v>
       </c>
       <c r="K87" t="n">
-        <v>0.000164</v>
+        <v>-0.000759855443758024</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0147</v>
+        <v>-2.57663</v>
       </c>
       <c r="M87" t="n">
-        <v>672308859.001803</v>
+        <v>26223510631</v>
       </c>
       <c r="N87" t="n">
-        <v>672308859.001803</v>
+        <v>100000000000</v>
       </c>
       <c r="O87" t="n">
-        <v>1.12</v>
+        <v>0.04323745</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46275.55902777778</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001316468375046998</v>
+        <v>0.0001314992934168699</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jupiter-exchange-solana</t>
+          <t>janus-henderson-anemoy-treasury-fund</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jup</t>
+          <t>jtrsy</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Janus Henderson Anemoy Treasury Fund</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.224658</v>
+        <v>1.12</v>
       </c>
       <c r="F88" t="n">
-        <v>745795089</v>
+        <v>750073481</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>79189933</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.252296</v>
+        <v>1.12</v>
       </c>
       <c r="J88" t="n">
-        <v>0.223238</v>
+        <v>1.12</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.02533083322216281</v>
+        <v>3.1e-05</v>
       </c>
       <c r="L88" t="n">
-        <v>-10.13279</v>
+        <v>0.00278</v>
       </c>
       <c r="M88" t="n">
-        <v>3320312968.08</v>
+        <v>672308860.001803</v>
       </c>
       <c r="N88" t="n">
-        <v>6861487305.722849</v>
+        <v>672308860.001803</v>
       </c>
       <c r="O88" t="n">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>45322.29359953704</v>
+        <v>46276.55543981482</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001288879871225353</v>
+        <v>0.0001289268797031948</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.4</v>
+        <v>57.03</v>
       </c>
       <c r="F89" t="n">
-        <v>726596100</v>
+        <v>731971802</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>57077786</v>
+        <v>133468774</v>
       </c>
       <c r="I89" t="n">
-        <v>1.57</v>
+        <v>57.28</v>
       </c>
       <c r="J89" t="n">
-        <v>1.39</v>
+        <v>53.95</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.1370691628276224</v>
+        <v>0.618684</v>
       </c>
       <c r="L89" t="n">
-        <v>-8.91394</v>
+        <v>1.09679</v>
       </c>
       <c r="M89" t="n">
-        <v>518772101.2826915</v>
+        <v>12824705.2497973</v>
       </c>
       <c r="N89" t="n">
-        <v>533532274.5626915</v>
+        <v>12825258.12914009</v>
       </c>
       <c r="O89" t="n">
-        <v>13.53</v>
+        <v>1493.59</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001164472317256937</v>
+        <v>0.0001173200884414149</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>56.41</v>
+        <v>1.41</v>
       </c>
       <c r="F90" t="n">
-        <v>723287048</v>
+        <v>731771096</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>175518035</v>
+        <v>45758488</v>
       </c>
       <c r="I90" t="n">
-        <v>65.06</v>
+        <v>1.43</v>
       </c>
       <c r="J90" t="n">
-        <v>56.07</v>
+        <v>1.36</v>
       </c>
       <c r="K90" t="n">
-        <v>-7.975759511683925</v>
+        <v>0.00881273</v>
       </c>
       <c r="L90" t="n">
-        <v>-12.38724</v>
+        <v>0.62924</v>
       </c>
       <c r="M90" t="n">
-        <v>12824703.59132163</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N90" t="n">
-        <v>12824688.23224829</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O90" t="n">
-        <v>1493.59</v>
+        <v>13.53</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001143029986867858</v>
+        <v>0.0001171913958131241</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6505,7 +6505,7 @@
         <v>1.049</v>
       </c>
       <c r="F91" t="n">
-        <v>713208265</v>
+        <v>713088227</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
@@ -6520,37 +6520,37 @@
         <v>1.049</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>0.000132</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>0.01259</v>
       </c>
       <c r="M91" t="n">
-        <v>679991366.72342</v>
+        <v>679791365.723425</v>
       </c>
       <c r="N91" t="n">
-        <v>679991366.72342</v>
+        <v>679791365.723425</v>
       </c>
       <c r="O91" t="n">
         <v>1.049</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>46274.47222222222</v>
+        <v>46275.59733796296</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.0001077720467704716</v>
+        <v>0.000105211945693929</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6569,28 +6569,28 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.998486</v>
+        <v>0.99869</v>
       </c>
       <c r="F92" t="n">
-        <v>697954217</v>
+        <v>698086092</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>5301136</v>
+        <v>3715987</v>
       </c>
       <c r="I92" t="n">
-        <v>0.998636</v>
+        <v>0.9987239999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>0.998163</v>
+        <v>0.998057</v>
       </c>
       <c r="K92" t="n">
-        <v>0.00017849</v>
+        <v>0.00016817</v>
       </c>
       <c r="L92" t="n">
-        <v>0.01788</v>
+        <v>0.01684</v>
       </c>
       <c r="M92" t="n">
         <v>699000000</v>
@@ -6605,220 +6605,220 @@
         <v>45350.38608796296</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>9.788757420893823e-05</v>
+        <v>9.559258113520257e-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>vechain</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>vet</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VeChain</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.00787007</v>
+        <v>2.17</v>
       </c>
       <c r="F93" t="n">
-        <v>676572141</v>
+        <v>696423755</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>22647904</v>
+        <v>63350640</v>
       </c>
       <c r="I93" t="n">
-        <v>0.00807445</v>
+        <v>2.18</v>
       </c>
       <c r="J93" t="n">
-        <v>0.00740968</v>
+        <v>2.07</v>
       </c>
       <c r="K93" t="n">
-        <v>9.907e-05</v>
+        <v>0.077262</v>
       </c>
       <c r="L93" t="n">
-        <v>1.27482</v>
+        <v>3.68482</v>
       </c>
       <c r="M93" t="n">
-        <v>85985041177</v>
+        <v>320188212.4569827</v>
       </c>
       <c r="N93" t="n">
-        <v>85985041177</v>
+        <v>331857365.0223532</v>
       </c>
       <c r="O93" t="n">
-        <v>0.280991</v>
+        <v>43.96</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>44304.71413194444</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>8.403219998102046e-05</v>
+        <v>9.452669113871476e-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2.1</v>
+        <v>0.793442</v>
       </c>
       <c r="F94" t="n">
-        <v>671657521</v>
+        <v>656647980</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>76196526</v>
+        <v>76206740</v>
       </c>
       <c r="I94" t="n">
-        <v>2.29</v>
+        <v>0.806818</v>
       </c>
       <c r="J94" t="n">
-        <v>2.11</v>
+        <v>0.773916</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.2103581739932632</v>
+        <v>-0.008356446045602484</v>
       </c>
       <c r="L94" t="n">
-        <v>-9.11121</v>
+        <v>-1.04221</v>
       </c>
       <c r="M94" t="n">
-        <v>320187582.0028005</v>
+        <v>827606294</v>
       </c>
       <c r="N94" t="n">
-        <v>331857365.0223532</v>
+        <v>1957066751</v>
       </c>
       <c r="O94" t="n">
-        <v>43.96</v>
+        <v>236.84</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>8.084757472349123e-05</v>
+        <v>6.902247588329421e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>vechain</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>VeChain</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.801834</v>
+        <v>0.00734403</v>
       </c>
       <c r="F95" t="n">
-        <v>663358743</v>
+        <v>631506549</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>71198473</v>
+        <v>23069119</v>
       </c>
       <c r="I95" t="n">
-        <v>0.853332</v>
+        <v>0.00841606</v>
       </c>
       <c r="J95" t="n">
-        <v>0.79472</v>
+        <v>0.00719802</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.04792108817033724</v>
+        <v>-0.000528154914175558</v>
       </c>
       <c r="L95" t="n">
-        <v>-5.6394</v>
+        <v>-6.70913</v>
       </c>
       <c r="M95" t="n">
-        <v>827388008</v>
+        <v>85985041177</v>
       </c>
       <c r="N95" t="n">
-        <v>1957070603</v>
+        <v>85985041177</v>
       </c>
       <c r="O95" t="n">
-        <v>236.84</v>
+        <v>0.280991</v>
       </c>
       <c r="P95" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>44304.71413194444</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>7.547004848027654e-05</v>
+        <v>5.29017977053504e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6837,28 +6837,28 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.62739</v>
+        <v>0.642814</v>
       </c>
       <c r="F96" t="n">
-        <v>605365589</v>
+        <v>620793377</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>57168157</v>
+        <v>168575735</v>
       </c>
       <c r="I96" t="n">
-        <v>0.647862</v>
+        <v>0.720922</v>
       </c>
       <c r="J96" t="n">
-        <v>0.600308</v>
+        <v>0.613161</v>
       </c>
       <c r="K96" t="n">
-        <v>0.008542660000000001</v>
+        <v>0.01528787</v>
       </c>
       <c r="L96" t="n">
-        <v>1.38041</v>
+        <v>2.43621</v>
       </c>
       <c r="M96" t="n">
         <v>965350000</v>
@@ -6873,19 +6873,19 @@
         <v>45378.63525462963</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>3.78910570237282e-05</v>
+        <v>4.603251496337129e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6904,34 +6904,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.076862</v>
+        <v>0.077068</v>
       </c>
       <c r="F97" t="n">
-        <v>604714731</v>
+        <v>606389450</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>11695818</v>
+        <v>10575322</v>
       </c>
       <c r="I97" t="n">
-        <v>0.07706300000000001</v>
+        <v>0.077185</v>
       </c>
       <c r="J97" t="n">
-        <v>0.076083</v>
+        <v>0.07657</v>
       </c>
       <c r="K97" t="n">
-        <v>0.00037129</v>
+        <v>0.00024138</v>
       </c>
       <c r="L97" t="n">
-        <v>0.4854</v>
+        <v>0.31419</v>
       </c>
       <c r="M97" t="n">
-        <v>7870595048.404165</v>
+        <v>7870613218.707415</v>
       </c>
       <c r="N97" t="n">
-        <v>9939534911.670143</v>
+        <v>9939553386.621778</v>
       </c>
       <c r="O97" t="n">
         <v>0.450785</v>
@@ -6940,19 +6940,19 @@
         <v>43450.66666666666</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.746930746305719e-05</v>
+        <v>3.679672119866491e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6974,25 +6974,25 @@
         <v>5.93</v>
       </c>
       <c r="F98" t="n">
-        <v>593229023</v>
+        <v>594252980</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>83496740</v>
+        <v>87829225</v>
       </c>
       <c r="I98" t="n">
-        <v>6.25</v>
+        <v>6.04</v>
       </c>
       <c r="J98" t="n">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.3291334657151408</v>
+        <v>0.0017728</v>
       </c>
       <c r="L98" t="n">
-        <v>-5.25602</v>
+        <v>0.02989</v>
       </c>
       <c r="M98" t="n">
         <v>100000000</v>
@@ -7007,208 +7007,208 @@
         <v>45365.29608796296</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.002668203171044e-05</v>
+        <v>2.90148201968377e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>xdce-crowd-sale</t>
+          <t>aerodrome-finance</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>xdc</t>
+          <t>aero</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>XDC Network</t>
+          <t>Aerodrome Finance</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.02811165</v>
+        <v>0.578779</v>
       </c>
       <c r="F99" t="n">
-        <v>560726767</v>
+        <v>573351093</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>5787636</v>
+        <v>34408838</v>
       </c>
       <c r="I99" t="n">
-        <v>0.02885457</v>
+        <v>0.57278</v>
       </c>
       <c r="J99" t="n">
-        <v>0.02806083</v>
+        <v>0.539678</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.000759056230095898</v>
+        <v>0.03371139</v>
       </c>
       <c r="L99" t="n">
-        <v>-2.62916</v>
+        <v>6.18481</v>
       </c>
       <c r="M99" t="n">
-        <v>19946688440</v>
+        <v>988997908.4629087</v>
       </c>
       <c r="N99" t="n">
-        <v>38065686425.1</v>
+        <v>1978450301.483024</v>
       </c>
       <c r="O99" t="n">
-        <v>0.192754</v>
+        <v>2.32</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>44428.86097222222</v>
+        <v>45633.25043981482</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" t="n">
-        <v>8.965540909043664e-06</v>
+        <v>1.561253638734621e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>flare-networks</t>
+          <t>xdce-crowd-sale</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>flr</t>
+          <t>xdc</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>XDC Network</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.00634582</v>
+        <v>0.02806316</v>
       </c>
       <c r="F100" t="n">
-        <v>551497765</v>
+        <v>560440294</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>3149003</v>
+        <v>6560353</v>
       </c>
       <c r="I100" t="n">
-        <v>0.00646956</v>
+        <v>0.02856101</v>
       </c>
       <c r="J100" t="n">
-        <v>0.00634072</v>
+        <v>0.02772397</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.00012076737794174</v>
+        <v>-5.306641111116e-05</v>
       </c>
       <c r="L100" t="n">
-        <v>-1.86756</v>
+        <v>-0.18874</v>
       </c>
       <c r="M100" t="n">
-        <v>86902599207.89294</v>
+        <v>19946688440</v>
       </c>
       <c r="N100" t="n">
-        <v>106517929730.2676</v>
+        <v>38065686425.1</v>
       </c>
       <c r="O100" t="n">
-        <v>0.150073</v>
+        <v>0.192754</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>44935.80144675926</v>
+        <v>44428.86097222222</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>2.985238694225902e-06</v>
+        <v>7.334135857992144e-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260910T132952Z-c388cc</t>
+          <t>20260911T132734Z-a714b0</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>usual-usd</t>
+          <t>official-trump</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>usd0</t>
+          <t>trump</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Usual USD</t>
+          <t>Official Trump</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.997173</v>
+        <v>2.01</v>
       </c>
       <c r="F101" t="n">
-        <v>546890845</v>
+        <v>549002148</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>200442</v>
+        <v>177214327</v>
       </c>
       <c r="I101" t="n">
-        <v>0.999036</v>
+        <v>2.02</v>
       </c>
       <c r="J101" t="n">
-        <v>0.998624</v>
+        <v>1.91</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.001528778750158555</v>
+        <v>0.04460472</v>
       </c>
       <c r="L101" t="n">
-        <v>-0.15308</v>
+        <v>2.27177</v>
       </c>
       <c r="M101" t="n">
-        <v>548453143.6102545</v>
+        <v>273137120.287634</v>
       </c>
       <c r="N101" t="n">
-        <v>548453143.6102545</v>
+        <v>1000000000</v>
       </c>
       <c r="O101" t="n">
-        <v>1.33</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45485.02012731481</v>
+        <v>45676.16011574074</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46275.56064814814</v>
+        <v>46276.55914351852</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>

--- a/src/xlsx/cleaned_data.xlsx
+++ b/src/xlsx/cleaned_data.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,34 +539,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77677</v>
+        <v>77314</v>
       </c>
       <c r="F2" t="n">
-        <v>1560125511429</v>
+        <v>1552722866590</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29594094775</v>
+        <v>28639817629</v>
       </c>
       <c r="I2" t="n">
-        <v>78035</v>
+        <v>79607</v>
       </c>
       <c r="J2" t="n">
-        <v>76393</v>
+        <v>76952</v>
       </c>
       <c r="K2" t="n">
-        <v>800.51</v>
+        <v>-262.4575759976724</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0413</v>
+        <v>-0.40435</v>
       </c>
       <c r="M2" t="n">
-        <v>20082787</v>
+        <v>20083262</v>
       </c>
       <c r="N2" t="n">
-        <v>20082809</v>
+        <v>20083312</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -575,7 +575,7 @@
         <v>45936.45673611111</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,34 +606,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2506.31</v>
+        <v>2534.68</v>
       </c>
       <c r="F3" t="n">
-        <v>305935492370</v>
+        <v>309335837072</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16878541137</v>
+        <v>21125178458</v>
       </c>
       <c r="I3" t="n">
-        <v>2512.29</v>
+        <v>2647.68</v>
       </c>
       <c r="J3" t="n">
-        <v>2428.8</v>
+        <v>2492.31</v>
       </c>
       <c r="K3" t="n">
-        <v>88.77</v>
+        <v>40.13</v>
       </c>
       <c r="L3" t="n">
-        <v>3.67177</v>
+        <v>1.54763</v>
       </c>
       <c r="M3" t="n">
-        <v>122038476.3012703</v>
+        <v>122041373.1030534</v>
       </c>
       <c r="N3" t="n">
-        <v>122038476.3012702</v>
+        <v>122041373.1030533</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -642,19 +642,19 @@
         <v>45893.47295138889</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1958137278964211</v>
+        <v>0.19893376061168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,34 +673,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99961</v>
+        <v>0.99981</v>
       </c>
       <c r="F4" t="n">
-        <v>183389557643</v>
+        <v>183482230974</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>58668007467</v>
+        <v>59719219122</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999861</v>
+        <v>0.99993</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999515</v>
+        <v>0.999562</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.4913892993966e-05</v>
+        <v>0.00025862</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00749</v>
+        <v>0.02306</v>
       </c>
       <c r="M4" t="n">
-        <v>183460843383.6048</v>
+        <v>183517171052.1943</v>
       </c>
       <c r="N4" t="n">
-        <v>188927789268.3162</v>
+        <v>188984116915.3062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -709,19 +709,19 @@
         <v>43304.66666666666</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1172373105179005</v>
+        <v>0.1178511430863342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,34 +740,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>720.65</v>
+        <v>736.4299999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>95991544747</v>
+        <v>98062399038</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>886998934</v>
+        <v>1194854270</v>
       </c>
       <c r="I5" t="n">
-        <v>723.4</v>
+        <v>740.12</v>
       </c>
       <c r="J5" t="n">
-        <v>704.72</v>
+        <v>717.4400000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1</v>
+        <v>14.67</v>
       </c>
       <c r="L5" t="n">
-        <v>1.99581</v>
+        <v>1.99022</v>
       </c>
       <c r="M5" t="n">
-        <v>133161118.37</v>
+        <v>133161036.91</v>
       </c>
       <c r="N5" t="n">
-        <v>133161113.02</v>
+        <v>133161033.96</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -776,19 +776,19 @@
         <v>45943.02875</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06119773030115795</v>
+        <v>0.06281844456712928</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="F6" t="n">
-        <v>85628071806</v>
+        <v>86186130739</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2239415372</v>
+        <v>2258448691</v>
       </c>
       <c r="I6" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00524616</v>
+        <v>0.0121198</v>
       </c>
       <c r="L6" t="n">
-        <v>0.38688</v>
+        <v>0.73402</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -843,19 +843,19 @@
         <v>45855.82005787037</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05455267449316954</v>
+        <v>0.05516702360294676</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999807</v>
+        <v>0.999865</v>
       </c>
       <c r="F7" t="n">
-        <v>74180090683</v>
+        <v>74337600627</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16624710113</v>
+        <v>15757949678</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999952</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999741</v>
+        <v>0.999771</v>
       </c>
       <c r="K7" t="n">
-        <v>8.262000000000001e-05</v>
+        <v>7.379e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00826</v>
+        <v>0.00401</v>
       </c>
       <c r="M7" t="n">
-        <v>74193437886.21786</v>
+        <v>74347671861.2077</v>
       </c>
       <c r="N7" t="n">
-        <v>74212582140.11983</v>
+        <v>74349866797.12619</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -910,19 +910,19 @@
         <v>43418.66666666666</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0472122323571965</v>
+        <v>0.04753347328130759</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,34 +941,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.29</v>
+        <v>102.26</v>
       </c>
       <c r="F8" t="n">
-        <v>59439992570</v>
+        <v>59986196956</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3174746581</v>
+        <v>4038038163</v>
       </c>
       <c r="I8" t="n">
-        <v>101.74</v>
+        <v>105.42</v>
       </c>
       <c r="J8" t="n">
-        <v>98.56</v>
+        <v>100.64</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="L8" t="n">
-        <v>1.90687</v>
+        <v>1.16766</v>
       </c>
       <c r="M8" t="n">
-        <v>586537449.1371635</v>
+        <v>586632914.9787524</v>
       </c>
       <c r="N8" t="n">
-        <v>633830009.5093167</v>
+        <v>633924207.4848769</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -977,19 +977,19 @@
         <v>45676.13572916666</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03776088577350404</v>
+        <v>0.03828741819488104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,34 +1008,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.336103</v>
+        <v>0.341025</v>
       </c>
       <c r="F9" t="n">
-        <v>31912142968</v>
+        <v>32378541531</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>358032118</v>
+        <v>521177154</v>
       </c>
       <c r="I9" t="n">
-        <v>0.340962</v>
+        <v>0.344079</v>
       </c>
       <c r="J9" t="n">
-        <v>0.335436</v>
+        <v>0.335532</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002159410412531093</v>
+        <v>0.00460594</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6383799999999999</v>
+        <v>1.36849</v>
       </c>
       <c r="M9" t="n">
-        <v>94944701333.48628</v>
+        <v>94944652948.92628</v>
       </c>
       <c r="N9" t="n">
-        <v>94944700423.18279</v>
+        <v>94946361438.41998</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1044,19 +1044,19 @@
         <v>45629.67407407407</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02011003668839505</v>
+        <v>0.0205008721037525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,34 +1075,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.035</v>
+        <v>1.016</v>
       </c>
       <c r="F10" t="n">
-        <v>23223868031</v>
+        <v>22870501626</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>93264084</v>
+        <v>60215308</v>
       </c>
       <c r="I10" t="n">
         <v>1.036</v>
       </c>
       <c r="J10" t="n">
-        <v>1.015</v>
+        <v>1.016</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007932140000000001</v>
+        <v>-0.0185665039219145</v>
       </c>
       <c r="L10" t="n">
-        <v>0.77257</v>
+        <v>-1.79099</v>
       </c>
       <c r="M10" t="n">
-        <v>22446057111.938</v>
+        <v>22502232981.668</v>
       </c>
       <c r="N10" t="n">
-        <v>22446057111.938</v>
+        <v>22502232981.668</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1111,19 +1111,19 @@
         <v>46237.59675925926</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01453911734888443</v>
+        <v>0.01437520922499061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1158.21</v>
+        <v>1158.26</v>
       </c>
       <c r="F11" t="n">
-        <v>19616404230</v>
+        <v>19604336005</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1671260451</v>
+        <v>1665786195</v>
       </c>
       <c r="I11" t="n">
-        <v>1183.37</v>
+        <v>1215.61</v>
       </c>
       <c r="J11" t="n">
-        <v>1055.58</v>
+        <v>1121.91</v>
       </c>
       <c r="K11" t="n">
-        <v>-17.24410873122633</v>
+        <v>-0.629609895717067</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.46702</v>
+        <v>0.1411</v>
       </c>
       <c r="M11" t="n">
         <v>16925695.4780448</v>
       </c>
       <c r="N11" t="n">
-        <v>16926651.7280448</v>
+        <v>16928367.3530448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1178,19 +1178,19 @@
         <v>42671.66666666666</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01222601261850918</v>
+        <v>0.01227094486552713</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>81.20999999999999</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>18098825995</v>
+        <v>17867396242</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1095111848</v>
+        <v>1071366521</v>
       </c>
       <c r="I12" t="n">
-        <v>82.09</v>
+        <v>83.63</v>
       </c>
       <c r="J12" t="n">
-        <v>78.27</v>
+        <v>78.41</v>
       </c>
       <c r="K12" t="n">
-        <v>0.123405</v>
+        <v>-1.044752684165488</v>
       </c>
       <c r="L12" t="n">
-        <v>0.15219</v>
+        <v>-1.36165</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1245,19 +1245,19 @@
         <v>46271.5199074074</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01125294189965125</v>
+        <v>0.01115190166259954</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,34 +1276,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0848</v>
+        <v>0.085033</v>
       </c>
       <c r="F13" t="n">
-        <v>13224091428</v>
+        <v>13255413715</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>678267919</v>
+        <v>651168802</v>
       </c>
       <c r="I13" t="n">
-        <v>0.085089</v>
+        <v>0.087898</v>
       </c>
       <c r="J13" t="n">
-        <v>0.082747</v>
+        <v>0.08368</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00124017</v>
+        <v>0.00046809</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48417</v>
+        <v>0.50806</v>
       </c>
       <c r="M13" t="n">
-        <v>155871456383.7052</v>
+        <v>155884756383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155871546383.7052</v>
+        <v>155884476383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1312,19 +1312,19 @@
         <v>44323.88082175926</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.008127263526073179</v>
+        <v>0.00818057945051188</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,31 +1343,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01582451</v>
+        <v>0.01512165</v>
       </c>
       <c r="F14" t="n">
-        <v>11227376908</v>
+        <v>10724534145</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>39502813</v>
+        <v>38289961</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0160076</v>
+        <v>0.01626765</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01551577</v>
+        <v>0.01509086</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.0215214789967e-05</v>
+        <v>-0.000651524093373202</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.19058</v>
+        <v>-4.09935</v>
       </c>
       <c r="M14" t="n">
-        <v>709212992829.0042</v>
+        <v>709217602168.6873</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1379,153 +1379,153 @@
         <v>46259.82847222222</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.006846970761904443</v>
+        <v>0.00655003149452222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999744</v>
+        <v>529.46</v>
       </c>
       <c r="F15" t="n">
-        <v>9744724175</v>
+        <v>9955702220</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>197400586</v>
+        <v>123793672</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999936</v>
+        <v>546.62</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999592</v>
+        <v>509.38</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.2646757613426e-05</v>
+        <v>16.48</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00727</v>
+        <v>3.27851</v>
       </c>
       <c r="M15" t="n">
-        <v>9747194186.835777</v>
+        <v>18803665.4396461</v>
       </c>
       <c r="N15" t="n">
-        <v>9748798031.413788</v>
+        <v>18803679.83773144</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>45593.90336805556</v>
+        <v>46036.48202546296</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005896294264677938</v>
+        <v>0.006054702780083096</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>512.91</v>
+        <v>0.999871</v>
       </c>
       <c r="F16" t="n">
-        <v>9645572026</v>
+        <v>9804836648</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>102137061</v>
+        <v>169068394</v>
       </c>
       <c r="I16" t="n">
-        <v>518.6799999999999</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>500.26</v>
+        <v>0.999626</v>
       </c>
       <c r="K16" t="n">
-        <v>11.01</v>
+        <v>0.00020096</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1934</v>
+        <v>0.00217</v>
       </c>
       <c r="M16" t="n">
-        <v>18803154.24465362</v>
+        <v>9806099950.497782</v>
       </c>
       <c r="N16" t="n">
-        <v>18803235.84437571</v>
+        <v>9806099950.497782</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>46036.48202546296</v>
+        <v>45593.90336805556</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.005832717935841265</v>
+        <v>0.005957505918972154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,28 +1544,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.55</v>
+        <v>80.37</v>
       </c>
       <c r="F17" t="n">
-        <v>9497240871</v>
+        <v>9474296952</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>101915128</v>
+        <v>120604559</v>
       </c>
       <c r="I17" t="n">
-        <v>80.97</v>
+        <v>83.22</v>
       </c>
       <c r="J17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K17" t="n">
-        <v>1.23</v>
+        <v>0.054638</v>
       </c>
       <c r="L17" t="n">
-        <v>1.54504</v>
+        <v>-0.18838</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1574,25 +1574,25 @@
         <v>293532015</v>
       </c>
       <c r="O17" t="n">
-        <v>82.52</v>
+        <v>83.22</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>46274.03356481482</v>
+        <v>46276.58553240741</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005737608042791911</v>
+        <v>0.005744551959378476</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.69</v>
+        <v>11.57</v>
       </c>
       <c r="F18" t="n">
-        <v>8749576424</v>
+        <v>8653159423</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>371507695</v>
+        <v>449714905</v>
       </c>
       <c r="I18" t="n">
-        <v>11.72</v>
+        <v>12.17</v>
       </c>
       <c r="J18" t="n">
-        <v>11.31</v>
+        <v>11.46</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02035372</v>
+        <v>0.02458788</v>
       </c>
       <c r="L18" t="n">
-        <v>0.17437</v>
+        <v>0.05704</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1647,19 +1647,19 @@
         <v>44325.67635416667</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005258205818822348</v>
+        <v>0.005215524764498022</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,28 +1678,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.15</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>8418079995</v>
+        <v>8383078709</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>189958</v>
+        <v>119813</v>
       </c>
       <c r="I19" t="n">
-        <v>9.23</v>
+        <v>9.16</v>
       </c>
       <c r="J19" t="n">
-        <v>9.02</v>
+        <v>9.1</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03241308782886954</v>
+        <v>-0.03313417990051093</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.35293</v>
+        <v>-0.36101</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1714,19 +1714,19 @@
         <v>46146.39930555555</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.005045650405844996</v>
+        <v>0.00504152219188058</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.207783</v>
+        <v>0.208994</v>
       </c>
       <c r="F20" t="n">
-        <v>7799990505</v>
+        <v>7840773190</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>475922020</v>
+        <v>484036030</v>
       </c>
       <c r="I20" t="n">
-        <v>0.211947</v>
+        <v>0.215743</v>
       </c>
       <c r="J20" t="n">
-        <v>0.200878</v>
+        <v>0.203215</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.002025983797910053</v>
+        <v>0.00173125</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.96563</v>
+        <v>0.54303</v>
       </c>
       <c r="M20" t="n">
-        <v>37510482444.2993</v>
+        <v>37516725700.17653</v>
       </c>
       <c r="N20" t="n">
         <v>45000000000</v>
@@ -1781,19 +1781,19 @@
         <v>44440.91678240741</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004649331606272314</v>
+        <v>0.004692135691626298</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.1788</v>
+        <v>0.181899</v>
       </c>
       <c r="F21" t="n">
-        <v>6226118444</v>
+        <v>6336215728</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>144935960</v>
+        <v>152590419</v>
       </c>
       <c r="I21" t="n">
-        <v>0.179365</v>
+        <v>0.184869</v>
       </c>
       <c r="J21" t="n">
-        <v>0.173418</v>
+        <v>0.177114</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00162509</v>
+        <v>0.00402238</v>
       </c>
       <c r="L21" t="n">
-        <v>0.91722</v>
+        <v>2.13215</v>
       </c>
       <c r="M21" t="n">
-        <v>34811503371.5922</v>
+        <v>34833772973.98598</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1848,153 +1848,153 @@
         <v>43102.66666666666</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.003640165302705976</v>
+        <v>0.003722807429857964</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ethena-usde</t>
+          <t>bitcoin-cash</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>usde</t>
+          <t>bch</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ethena USDe</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.999513</v>
+        <v>231.06</v>
       </c>
       <c r="F22" t="n">
-        <v>4599511936</v>
+        <v>4641577287</v>
       </c>
       <c r="G22" t="n">
         <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>69743386</v>
+        <v>183606425</v>
       </c>
       <c r="I22" t="n">
-        <v>0.999649</v>
+        <v>237.75</v>
       </c>
       <c r="J22" t="n">
-        <v>0.999302</v>
+        <v>225.57</v>
       </c>
       <c r="K22" t="n">
-        <v>1.915e-05</v>
+        <v>3.84</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00192</v>
+        <v>1.55399</v>
       </c>
       <c r="M22" t="n">
-        <v>4601732684.783278</v>
+        <v>20088074.89665078</v>
       </c>
       <c r="N22" t="n">
-        <v>4601551140.243678</v>
+        <v>20088099.89665078</v>
       </c>
       <c r="O22" t="n">
-        <v>1.034</v>
+        <v>3785.82</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>46000.38208333333</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002597185687201314</v>
+        <v>0.002631017334877644</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bitcoin-cash</t>
+          <t>ethena-usde</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bch</t>
+          <t>usde</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Ethena USDe</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228.66</v>
+        <v>0.9997549999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>4594108661</v>
+        <v>4599690699</v>
       </c>
       <c r="G23" t="n">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>290215500</v>
+        <v>57253693</v>
       </c>
       <c r="I23" t="n">
-        <v>229.44</v>
+        <v>0.9999440000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>221.45</v>
+        <v>0.999438</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.328170852425927</v>
+        <v>0.0003092</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5775</v>
+        <v>0.02766</v>
       </c>
       <c r="M23" t="n">
-        <v>20087609.27165078</v>
+        <v>4600819094.053699</v>
       </c>
       <c r="N23" t="n">
-        <v>20087999.89665078</v>
+        <v>4600819094.053699</v>
       </c>
       <c r="O23" t="n">
-        <v>3785.82</v>
+        <v>1.034</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>46000.38208333333</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.002593721108857228</v>
+        <v>0.002604031424028167</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,34 +2013,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.999938</v>
+        <v>0.99977</v>
       </c>
       <c r="F24" t="n">
-        <v>4579726989</v>
+        <v>4575781871</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>295208672</v>
+        <v>212008770</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999683</v>
+        <v>0.999699</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00012281</v>
+        <v>-0.000199777112947164</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01228</v>
+        <v>-0.0039</v>
       </c>
       <c r="M24" t="n">
-        <v>4580443616.059474</v>
+        <v>4576834066.613646</v>
       </c>
       <c r="N24" t="n">
-        <v>4586837991.908969</v>
+        <v>4575568673.433953</v>
       </c>
       <c r="O24" t="n">
         <v>1.22</v>
@@ -2049,19 +2049,19 @@
         <v>43902.79363425926</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.002584499584991989</v>
+        <v>0.002588627889585986</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,34 +2080,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.999592</v>
+        <v>0.999718</v>
       </c>
       <c r="F25" t="n">
-        <v>4278520207</v>
+        <v>4301404459</v>
       </c>
       <c r="G25" t="n">
         <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>1331717650</v>
+        <v>1112443789</v>
       </c>
       <c r="I25" t="n">
-        <v>0.999637</v>
+        <v>0.999893</v>
       </c>
       <c r="J25" t="n">
-        <v>0.999073</v>
+        <v>0.999515</v>
       </c>
       <c r="K25" t="n">
-        <v>0.00025078</v>
+        <v>0.00016961</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02509</v>
+        <v>0.01252</v>
       </c>
       <c r="M25" t="n">
-        <v>4280220129.914264</v>
+        <v>4302618142.639469</v>
       </c>
       <c r="N25" t="n">
-        <v>4280220129.914264</v>
+        <v>4302618142.639469</v>
       </c>
       <c r="O25" t="n">
         <v>1.048</v>
@@ -2116,19 +2116,19 @@
         <v>46212.42696759259</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002391365884780729</v>
+        <v>0.002411857120399867</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,34 +2147,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53.5</v>
+        <v>53.98</v>
       </c>
       <c r="F26" t="n">
-        <v>4151707448</v>
+        <v>4188496530</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>246229119</v>
+        <v>221042595</v>
       </c>
       <c r="I26" t="n">
-        <v>53.32</v>
+        <v>54.24</v>
       </c>
       <c r="J26" t="n">
-        <v>51.68</v>
+        <v>52.9</v>
       </c>
       <c r="K26" t="n">
-        <v>1.43</v>
+        <v>0.958371</v>
       </c>
       <c r="L26" t="n">
-        <v>2.75287</v>
+        <v>1.68775</v>
       </c>
       <c r="M26" t="n">
-        <v>77595273.10667892</v>
+        <v>77599073.1147867</v>
       </c>
       <c r="N26" t="n">
-        <v>77598279.36456157</v>
+        <v>77601641.87155811</v>
       </c>
       <c r="O26" t="n">
         <v>410.26</v>
@@ -2183,153 +2183,153 @@
         <v>44325.80077546297</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002310053580930716</v>
+        <v>0.002339114902623786</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>canton-network</t>
+          <t>uniswap</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>uni</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.09754599999999999</v>
+        <v>6.45</v>
       </c>
       <c r="F27" t="n">
-        <v>3860730361</v>
+        <v>4020690137</v>
       </c>
       <c r="G27" t="n">
         <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>10816765</v>
+        <v>653762748</v>
       </c>
       <c r="I27" t="n">
-        <v>0.102022</v>
+        <v>6.51</v>
       </c>
       <c r="J27" t="n">
-        <v>0.09499199999999999</v>
+        <v>5.94</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.003497612882979284</v>
+        <v>0.340794</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.46147</v>
+        <v>5.28911</v>
       </c>
       <c r="M27" t="n">
-        <v>39571131039.5762</v>
+        <v>623212423.7271129</v>
       </c>
       <c r="N27" t="n">
-        <v>39571821711.34754</v>
+        <v>890460420.0329479</v>
       </c>
       <c r="O27" t="n">
-        <v>0.194152</v>
+        <v>44.92</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>46056.00148148148</v>
+        <v>44318.89240740741</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.00212347915815094</v>
+        <v>0.002231003724853227</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>uniswap</t>
+          <t>canton-network</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>uni</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Uniswap</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.18</v>
+        <v>0.098431</v>
       </c>
       <c r="F28" t="n">
-        <v>3854268305</v>
+        <v>3895610450</v>
       </c>
       <c r="G28" t="n">
         <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>534492504</v>
+        <v>8865517</v>
       </c>
       <c r="I28" t="n">
-        <v>6.22</v>
+        <v>0.101898</v>
       </c>
       <c r="J28" t="n">
-        <v>5.88</v>
+        <v>0.096594</v>
       </c>
       <c r="K28" t="n">
-        <v>0.304086</v>
+        <v>0.00051503</v>
       </c>
       <c r="L28" t="n">
-        <v>5.17582</v>
+        <v>0.46758</v>
       </c>
       <c r="M28" t="n">
-        <v>623212423.7271129</v>
+        <v>39576931489.55997</v>
       </c>
       <c r="N28" t="n">
-        <v>890460420.0329479</v>
+        <v>39576931489.55997</v>
       </c>
       <c r="O28" t="n">
-        <v>44.92</v>
+        <v>0.194152</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>44318.89240740741</v>
+        <v>46056.00148148148</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.002119335689740417</v>
+        <v>0.0021504197135114</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="F29" t="n">
-        <v>3794903391</v>
+        <v>3839636947</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>30916826</v>
+        <v>27386361</v>
       </c>
       <c r="I29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="J29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02288055</v>
+        <v>0.01469045</v>
       </c>
       <c r="L29" t="n">
-        <v>1.70863</v>
+        <v>0.9879</v>
       </c>
       <c r="M29" t="n">
-        <v>2786609237.436568</v>
+        <v>2787175826.164195</v>
       </c>
       <c r="N29" t="n">
-        <v>5247225223.221386</v>
+        <v>5247793479.85942</v>
       </c>
       <c r="O29" t="n">
         <v>8.25</v>
@@ -2384,86 +2384,86 @@
         <v>45457.69225694444</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002081270924307801</v>
+        <v>0.002114358147410793</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>global-dollar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>usdg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Global Dollar</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.61</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>3414897594</v>
+        <v>3306050702</v>
       </c>
       <c r="G30" t="n">
         <v>29</v>
       </c>
       <c r="H30" t="n">
-        <v>530732610</v>
+        <v>1707855037</v>
       </c>
       <c r="I30" t="n">
-        <v>2.58</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>2.38</v>
+        <v>0.999818</v>
       </c>
       <c r="K30" t="n">
-        <v>0.210456</v>
+        <v>-0.000103654832734001</v>
       </c>
       <c r="L30" t="n">
-        <v>8.765319999999999</v>
+        <v>-0.00161</v>
       </c>
       <c r="M30" t="n">
-        <v>1306023672</v>
+        <v>3306051192.175045</v>
       </c>
       <c r="N30" t="n">
-        <v>1306023669</v>
+        <v>3306126794.725507</v>
       </c>
       <c r="O30" t="n">
-        <v>20.44</v>
+        <v>1.65</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>44577.59010416667</v>
+        <v>45686.67436342593</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001837611318806823</v>
+        <v>0.001770589138627437</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,34 +2482,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.54</v>
+        <v>7.45</v>
       </c>
       <c r="F31" t="n">
-        <v>3337034688</v>
+        <v>3298662556</v>
       </c>
       <c r="G31" t="n">
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>258337087</v>
+        <v>279708963</v>
       </c>
       <c r="I31" t="n">
-        <v>7.66</v>
+        <v>7.81</v>
       </c>
       <c r="J31" t="n">
-        <v>7.3</v>
+        <v>7.41</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.03910654255478985</v>
+        <v>-0.09093661311304313</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5159899999999999</v>
+        <v>-1.3548</v>
       </c>
       <c r="M31" t="n">
-        <v>442490100.8059288</v>
+        <v>442494917.9713389</v>
       </c>
       <c r="N31" t="n">
-        <v>469158789.1601316</v>
+        <v>469163526.3103041</v>
       </c>
       <c r="O31" t="n">
         <v>144.96</v>
@@ -2518,19 +2518,19 @@
         <v>44521.26314814815</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001787685646333148</v>
+        <v>0.001765829241514334</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.075407</v>
+        <v>0.07473399999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>3305627660</v>
+        <v>3275725089</v>
       </c>
       <c r="G32" t="n">
         <v>31</v>
       </c>
       <c r="H32" t="n">
-        <v>55662699</v>
+        <v>52016055</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07587099999999999</v>
+        <v>0.07695299999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>0.073326</v>
+        <v>0.073904</v>
       </c>
       <c r="K32" t="n">
-        <v>0.00024528</v>
+        <v>-0.00031668373285558</v>
       </c>
       <c r="L32" t="n">
-        <v>0.32634</v>
+        <v>-0.60851</v>
       </c>
       <c r="M32" t="n">
-        <v>43831559676.41492</v>
+        <v>43831559674.09415</v>
       </c>
       <c r="N32" t="n">
         <v>50000000000</v>
@@ -2585,153 +2585,153 @@
         <v>44454.11143518519</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001767547469197819</v>
+        <v>0.00175105151744727</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>global-dollar</t>
+          <t>shiba-inu</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>usdg</t>
+          <t>shib</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Global Dollar</t>
+          <t>Shiba Inu</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>5.35e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>3306148548</v>
+        <v>3155339989</v>
       </c>
       <c r="G33" t="n">
         <v>32</v>
       </c>
       <c r="H33" t="n">
-        <v>1740405168</v>
+        <v>86440248</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>5.39e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9997470000000001</v>
+        <v>5.11e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>5.111e-05</v>
+        <v>2.234e-07</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00511</v>
+        <v>4.11151</v>
       </c>
       <c r="M33" t="n">
-        <v>3306126794.671768</v>
+        <v>589239233105565.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3305944150.525681</v>
+        <v>589496238721205.9</v>
       </c>
       <c r="O33" t="n">
-        <v>1.65</v>
+        <v>8.616e-05</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>45686.67436342593</v>
+        <v>44496.82980324074</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001767881462430533</v>
+        <v>0.001673492047189027</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>shiba-inu</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shib</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.14e-06</v>
+        <v>2.37</v>
       </c>
       <c r="F34" t="n">
-        <v>3032067683</v>
+        <v>3098020615</v>
       </c>
       <c r="G34" t="n">
         <v>33</v>
       </c>
       <c r="H34" t="n">
-        <v>66559557</v>
+        <v>508937832</v>
       </c>
       <c r="I34" t="n">
-        <v>5.15e-06</v>
+        <v>2.72</v>
       </c>
       <c r="J34" t="n">
-        <v>5e-06</v>
+        <v>2.33</v>
       </c>
       <c r="K34" t="n">
-        <v>8.213900000000001e-08</v>
+        <v>-0.1722313415777665</v>
       </c>
       <c r="L34" t="n">
-        <v>1.6227</v>
+        <v>-6.9323</v>
       </c>
       <c r="M34" t="n">
-        <v>589239233105565.5</v>
+        <v>1306106318</v>
       </c>
       <c r="N34" t="n">
-        <v>589496238721205.9</v>
+        <v>1306106333</v>
       </c>
       <c r="O34" t="n">
-        <v>8.616e-05</v>
+        <v>20.44</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>44496.82980324074</v>
+        <v>44577.59010416667</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.001592140892237951</v>
+        <v>0.00163656338838512</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.733199</v>
+        <v>0.729106</v>
       </c>
       <c r="F35" t="n">
-        <v>3006788096</v>
+        <v>2986810464</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>512139661</v>
+        <v>499464398</v>
       </c>
       <c r="I35" t="n">
-        <v>0.753451</v>
+        <v>0.763093</v>
       </c>
       <c r="J35" t="n">
-        <v>0.712406</v>
+        <v>0.719113</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.01700455324618688</v>
+        <v>-0.00523676014790786</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.26666</v>
+        <v>-0.8893799999999999</v>
       </c>
       <c r="M35" t="n">
         <v>4096537146.540959</v>
@@ -2786,220 +2786,220 @@
         <v>45661.62243055556</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001575931628473357</v>
+        <v>0.001564914983400623</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>paypal-usd</t>
+          <t>crypto-com-chain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pyusd</t>
+          <t>cro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PayPal USD</t>
+          <t>Cronos</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.999802</v>
+        <v>0.058225</v>
       </c>
       <c r="F36" t="n">
-        <v>2774645441</v>
+        <v>2826808968</v>
       </c>
       <c r="G36" t="n">
         <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>97144192</v>
+        <v>5783379</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.058403</v>
       </c>
       <c r="J36" t="n">
-        <v>0.99966</v>
+        <v>0.055969</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.00024035531706379</v>
+        <v>0.00145309</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.02403</v>
+        <v>2.68879</v>
       </c>
       <c r="M36" t="n">
-        <v>2775204047.281764</v>
+        <v>48550035909.05608</v>
       </c>
       <c r="N36" t="n">
-        <v>2775404030.790055</v>
+        <v>98916656597.64023</v>
       </c>
       <c r="O36" t="n">
-        <v>1.021</v>
+        <v>0.891544</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>45222.61454861111</v>
+        <v>44523.66666666666</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0014270818262235</v>
+        <v>0.00146183219931616</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
+          <t>paypal-usd</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>buidl</t>
+          <t>pyusd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
+          <t>PayPal USD</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.999861</v>
       </c>
       <c r="F37" t="n">
-        <v>2772571255</v>
+        <v>2792156571</v>
       </c>
       <c r="G37" t="n">
         <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>144383699</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0.999739</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.00015109</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.00487</v>
       </c>
       <c r="M37" t="n">
-        <v>2772571254.640448</v>
+        <v>2792543783.480257</v>
       </c>
       <c r="N37" t="n">
-        <v>2772571254.640448</v>
+        <v>2792543783.480256</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>1.021</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>45699.87511574074</v>
+        <v>45222.61454861111</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001425751858769093</v>
+        <v>0.001439506998319539</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>crypto-com-chain</t>
+          <t>blackrock-usd-institutional-digital-liquidity-fund</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cro</t>
+          <t>buidl</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cronos</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.056899</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>2762146802</v>
+        <v>2750834099</v>
       </c>
       <c r="G38" t="n">
         <v>37</v>
       </c>
       <c r="H38" t="n">
-        <v>5384142</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.05704</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0.055842</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00070577</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1.25596</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>48548017567.46945</v>
+        <v>2750834099.470449</v>
       </c>
       <c r="N38" t="n">
-        <v>98914688510.54858</v>
+        <v>2750834099.470449</v>
       </c>
       <c r="O38" t="n">
-        <v>0.891544</v>
+        <v>1</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>44523.66666666666</v>
+        <v>45699.87511574074</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.001419067702565172</v>
+        <v>0.001412884525620832</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,34 +3018,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="F39" t="n">
-        <v>2713315324</v>
+        <v>2671365632</v>
       </c>
       <c r="G39" t="n">
         <v>38</v>
       </c>
       <c r="H39" t="n">
-        <v>1446907</v>
+        <v>1356005</v>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="J39" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01825308</v>
+        <v>-0.01885958591067305</v>
       </c>
       <c r="L39" t="n">
-        <v>1.55263</v>
+        <v>-1.64046</v>
       </c>
       <c r="M39" t="n">
-        <v>2271580642.297657</v>
+        <v>2271935475.487713</v>
       </c>
       <c r="N39" t="n">
-        <v>5412955068.886312</v>
+        <v>5413309902.267487</v>
       </c>
       <c r="O39" t="n">
         <v>5.64</v>
@@ -3054,19 +3054,19 @@
         <v>46205.17638888889</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001387756973204089</v>
+        <v>0.001361686061668444</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4382.93</v>
+        <v>4347.44</v>
       </c>
       <c r="F40" t="n">
-        <v>2684888372</v>
+        <v>2664214314</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
       </c>
       <c r="H40" t="n">
-        <v>250788877</v>
+        <v>130346848</v>
       </c>
       <c r="I40" t="n">
-        <v>4389.16</v>
+        <v>4397.49</v>
       </c>
       <c r="J40" t="n">
-        <v>4302.81</v>
+        <v>4341.97</v>
       </c>
       <c r="K40" t="n">
-        <v>34.92</v>
+        <v>-9.31237544006126</v>
       </c>
       <c r="L40" t="n">
-        <v>0.80321</v>
+        <v>-0.31546</v>
       </c>
       <c r="M40" t="n">
         <v>612823.6595320001</v>
@@ -3121,19 +3121,19 @@
         <v>46050.66666666666</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001369529619925278</v>
+        <v>0.001357078743688658</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3155,7 +3155,7 @@
         <v>1.14</v>
       </c>
       <c r="F41" t="n">
-        <v>2605358571</v>
+        <v>2605383630</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
@@ -3176,10 +3176,10 @@
         <v>0.02773</v>
       </c>
       <c r="M41" t="n">
-        <v>2291122606.297392</v>
+        <v>2291144643.386653</v>
       </c>
       <c r="N41" t="n">
-        <v>2291122606.297392</v>
+        <v>2291144643.386653</v>
       </c>
       <c r="O41" t="n">
         <v>1.14</v>
@@ -3188,19 +3188,19 @@
         <v>46276.53819444445</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.001318535134866854</v>
+        <v>0.001319176406223556</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3219,34 +3219,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.999924</v>
+        <v>0.999974</v>
       </c>
       <c r="F42" t="n">
-        <v>2405187563</v>
+        <v>2422784833</v>
       </c>
       <c r="G42" t="n">
         <v>41</v>
       </c>
       <c r="H42" t="n">
-        <v>257216446</v>
+        <v>149871915</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0.999785</v>
+        <v>0.999803</v>
       </c>
       <c r="K42" t="n">
-        <v>-8.0108728248263e-05</v>
+        <v>4.397e-05</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.00801</v>
+        <v>-0.00181</v>
       </c>
       <c r="M42" t="n">
-        <v>2405335190.107209</v>
+        <v>2422848190.107193</v>
       </c>
       <c r="N42" t="n">
-        <v>2405335190.107207</v>
+        <v>2422848190.107191</v>
       </c>
       <c r="O42" t="n">
         <v>1.073</v>
@@ -3255,19 +3255,19 @@
         <v>45652.11518518518</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.001190185543289404</v>
+        <v>0.00120153505388749</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3286,28 +3286,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>113.15</v>
+        <v>114.27</v>
       </c>
       <c r="F43" t="n">
-        <v>2378543687</v>
+        <v>2399752529</v>
       </c>
       <c r="G43" t="n">
         <v>42</v>
       </c>
       <c r="H43" t="n">
-        <v>34387010</v>
+        <v>22842507</v>
       </c>
       <c r="I43" t="n">
-        <v>114.36</v>
+        <v>115.9</v>
       </c>
       <c r="J43" t="n">
-        <v>108.12</v>
+        <v>112.58</v>
       </c>
       <c r="K43" t="n">
-        <v>2.83</v>
+        <v>0.404237</v>
       </c>
       <c r="L43" t="n">
-        <v>2.56088</v>
+        <v>0.35947</v>
       </c>
       <c r="M43" t="n">
         <v>21000000</v>
@@ -3322,19 +3322,19 @@
         <v>45934.66666666666</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.001173101497818443</v>
+        <v>0.001186696230004245</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3353,28 +3353,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>239.8</v>
+        <v>236.86</v>
       </c>
       <c r="F44" t="n">
-        <v>2301541936</v>
+        <v>2273295351</v>
       </c>
       <c r="G44" t="n">
         <v>43</v>
       </c>
       <c r="H44" t="n">
-        <v>225240727</v>
+        <v>183659571</v>
       </c>
       <c r="I44" t="n">
-        <v>244.36</v>
+        <v>246.82</v>
       </c>
       <c r="J44" t="n">
-        <v>230.01</v>
+        <v>232.66</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.785491097572077</v>
+        <v>-0.262096608194696</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.14823</v>
+        <v>-0.33097</v>
       </c>
       <c r="M44" t="n">
         <v>9597491</v>
@@ -3389,19 +3389,19 @@
         <v>45358.44833333333</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001123727997678011</v>
+        <v>0.001105224754414389</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3423,13 +3423,13 @@
         <v>1.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2221246321</v>
+        <v>2226911540</v>
       </c>
       <c r="G45" t="n">
         <v>44</v>
       </c>
       <c r="H45" t="n">
-        <v>3198815</v>
+        <v>1344243</v>
       </c>
       <c r="I45" t="n">
         <v>1.15</v>
@@ -3438,16 +3438,16 @@
         <v>1.14</v>
       </c>
       <c r="K45" t="n">
-        <v>0.00108932</v>
+        <v>0.00019397</v>
       </c>
       <c r="L45" t="n">
-        <v>0.09521</v>
+        <v>0.01413</v>
       </c>
       <c r="M45" t="n">
-        <v>1939633516.713295</v>
+        <v>1944367993.570987</v>
       </c>
       <c r="N45" t="n">
-        <v>1939633516.713294</v>
+        <v>1944367993.574475</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -3456,153 +3456,153 @@
         <v>45377.89175925926</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.00107224247290756</v>
+        <v>0.001075341456483678</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>mantle</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mnt</t>
+          <t>aave</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>Aave</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.586103</v>
+        <v>127.44</v>
       </c>
       <c r="F46" t="n">
-        <v>1936039659</v>
+        <v>1966054567</v>
       </c>
       <c r="G46" t="n">
         <v>45</v>
       </c>
       <c r="H46" t="n">
-        <v>27034282</v>
+        <v>210362355</v>
       </c>
       <c r="I46" t="n">
-        <v>0.587968</v>
+        <v>129.92</v>
       </c>
       <c r="J46" t="n">
-        <v>0.567507</v>
+        <v>123.42</v>
       </c>
       <c r="K46" t="n">
-        <v>0.008711989999999999</v>
+        <v>2.87</v>
       </c>
       <c r="L46" t="n">
-        <v>1.50885</v>
+        <v>1.51048</v>
       </c>
       <c r="M46" t="n">
-        <v>3302294382.53684</v>
+        <v>15427574.57809611</v>
       </c>
       <c r="N46" t="n">
-        <v>6219316794.889999</v>
+        <v>16000000</v>
       </c>
       <c r="O46" t="n">
-        <v>2.86</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>45938.71164351852</v>
+        <v>44334.55554398148</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0008893680449441083</v>
+        <v>0.0009072813839410718</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>mantle</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>aave</t>
+          <t>mnt</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aave</t>
+          <t>Mantle</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>124.99</v>
+        <v>0.5740690000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>1928768550</v>
+        <v>1895745258</v>
       </c>
       <c r="G47" t="n">
         <v>46</v>
       </c>
       <c r="H47" t="n">
-        <v>176763274</v>
+        <v>26568682</v>
       </c>
       <c r="I47" t="n">
-        <v>125.34</v>
+        <v>0.606896</v>
       </c>
       <c r="J47" t="n">
-        <v>120.57</v>
+        <v>0.57258</v>
       </c>
       <c r="K47" t="n">
-        <v>3.31</v>
+        <v>-0.009221854130325946</v>
       </c>
       <c r="L47" t="n">
-        <v>2.72166</v>
+        <v>-1.61632</v>
       </c>
       <c r="M47" t="n">
-        <v>15427562.51867931</v>
+        <v>3302294382.53684</v>
       </c>
       <c r="N47" t="n">
-        <v>16000000</v>
+        <v>6219316794.889999</v>
       </c>
       <c r="O47" t="n">
-        <v>661.6900000000001</v>
+        <v>2.86</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>44334.55554398148</v>
+        <v>45938.71164351852</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.00088470581198745</v>
+        <v>0.0008619838117310296</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3621,34 +3621,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4387.11</v>
+        <v>4352.79</v>
       </c>
       <c r="F48" t="n">
-        <v>1896775860</v>
+        <v>1884351020</v>
       </c>
       <c r="G48" t="n">
         <v>47</v>
       </c>
       <c r="H48" t="n">
-        <v>179797302</v>
+        <v>100832663</v>
       </c>
       <c r="I48" t="n">
-        <v>4392.22</v>
+        <v>4401.08</v>
       </c>
       <c r="J48" t="n">
-        <v>4309.71</v>
+        <v>4348.7</v>
       </c>
       <c r="K48" t="n">
-        <v>37.85</v>
+        <v>-8.094537499183389</v>
       </c>
       <c r="L48" t="n">
-        <v>0.87035</v>
+        <v>-0.25164</v>
       </c>
       <c r="M48" t="n">
-        <v>432503.320539</v>
+        <v>432906.598539</v>
       </c>
       <c r="N48" t="n">
-        <v>432503.320539</v>
+        <v>432906.598539</v>
       </c>
       <c r="O48" t="n">
         <v>5619.09</v>
@@ -3657,19 +3657,19 @@
         <v>46050.93814814815</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0008641921085496178</v>
+        <v>0.0008546429442708842</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3688,28 +3688,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.697635</v>
+        <v>0.686569</v>
       </c>
       <c r="F49" t="n">
-        <v>1887254347</v>
+        <v>1856531466</v>
       </c>
       <c r="G49" t="n">
         <v>48</v>
       </c>
       <c r="H49" t="n">
-        <v>127539997</v>
+        <v>115220006</v>
       </c>
       <c r="I49" t="n">
-        <v>0.711375</v>
+        <v>0.716822</v>
       </c>
       <c r="J49" t="n">
-        <v>0.678593</v>
+        <v>0.672749</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.004338511102796705</v>
+        <v>-0.0118206512966319</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.61805</v>
+        <v>-1.76831</v>
       </c>
       <c r="M49" t="n">
         <v>2704071066.799731</v>
@@ -3724,220 +3724,220 @@
         <v>45924.13766203704</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.0008580869172086751</v>
+        <v>0.0008367198801121088</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>polkadot</t>
+          <t>world-liberty-financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>dot</t>
+          <t>wlfi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.088</v>
+        <v>0.057204</v>
       </c>
       <c r="F50" t="n">
-        <v>1851932098</v>
+        <v>1817776264</v>
       </c>
       <c r="G50" t="n">
         <v>49</v>
       </c>
       <c r="H50" t="n">
-        <v>214878707</v>
+        <v>61693163</v>
       </c>
       <c r="I50" t="n">
-        <v>1.16</v>
+        <v>0.05773</v>
       </c>
       <c r="J50" t="n">
-        <v>1.073</v>
+        <v>0.052011</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.004645409720101634</v>
+        <v>0.0046668</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.42533</v>
+        <v>8.911820000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>1702250904.807482</v>
+        <v>31777210091</v>
       </c>
       <c r="N50" t="n">
-        <v>1702270902.550952</v>
+        <v>100000000000</v>
       </c>
       <c r="O50" t="n">
-        <v>54.98</v>
+        <v>0.331336</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>44504.25704861111</v>
+        <v>45901.18065972222</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.0008354383015173011</v>
+        <v>0.0008117514003179216</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ondo-finance</t>
+          <t>polkadot</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ondo</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ondo</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.354835</v>
+        <v>1.046</v>
       </c>
       <c r="F51" t="n">
-        <v>1729446777</v>
+        <v>1780719543</v>
       </c>
       <c r="G51" t="n">
         <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>93283877</v>
+        <v>156543168</v>
       </c>
       <c r="I51" t="n">
-        <v>0.358455</v>
+        <v>1.11</v>
       </c>
       <c r="J51" t="n">
-        <v>0.342359</v>
+        <v>1.031</v>
       </c>
       <c r="K51" t="n">
-        <v>0.00538958</v>
+        <v>-0.04921686161834615</v>
       </c>
       <c r="L51" t="n">
-        <v>1.54232</v>
+        <v>-4.73488</v>
       </c>
       <c r="M51" t="n">
-        <v>4869330647</v>
+        <v>1702414888.957769</v>
       </c>
       <c r="N51" t="n">
-        <v>10000000000</v>
+        <v>1702422593.621313</v>
       </c>
       <c r="O51" t="n">
-        <v>2.14</v>
+        <v>54.98</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>45641.69166666667</v>
+        <v>44504.25704861111</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.0007569007496427422</v>
+        <v>0.0007878771862310659</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>world-liberty-financial</t>
+          <t>ondo-finance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>wlfi</t>
+          <t>ondo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Ondo</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.05234</v>
+        <v>0.352305</v>
       </c>
       <c r="F52" t="n">
-        <v>1664166533</v>
+        <v>1715488264</v>
       </c>
       <c r="G52" t="n">
         <v>51</v>
       </c>
       <c r="H52" t="n">
-        <v>87281436</v>
+        <v>76577445</v>
       </c>
       <c r="I52" t="n">
-        <v>0.056965</v>
+        <v>0.3679</v>
       </c>
       <c r="J52" t="n">
-        <v>0.04828182</v>
+        <v>0.34678</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.003616400874016316</v>
+        <v>-0.002580851204815326</v>
       </c>
       <c r="L52" t="n">
-        <v>-6.46287</v>
+        <v>-0.94938</v>
       </c>
       <c r="M52" t="n">
-        <v>31777204151</v>
+        <v>4869330647</v>
       </c>
       <c r="N52" t="n">
-        <v>100000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O52" t="n">
-        <v>0.331336</v>
+        <v>2.14</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>45901.18065972222</v>
+        <v>45641.69166666667</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.000715043076350333</v>
+        <v>0.0007458511926196666</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3956,31 +3956,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="F53" t="n">
-        <v>1637472718</v>
+        <v>1579756865</v>
       </c>
       <c r="G53" t="n">
         <v>52</v>
       </c>
       <c r="H53" t="n">
-        <v>24546993</v>
+        <v>20563790</v>
       </c>
       <c r="I53" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="J53" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1261</v>
+        <v>-0.07578842279781606</v>
       </c>
       <c r="L53" t="n">
-        <v>5.61006</v>
+        <v>-3.29573</v>
       </c>
       <c r="M53" t="n">
-        <v>688937204.4827486</v>
+        <v>688986833.9200211</v>
       </c>
       <c r="N53" t="n">
         <v>1000000000</v>
@@ -3992,19 +3992,19 @@
         <v>45674.19883101852</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0006979270100072292</v>
+        <v>0.0006584046946406787</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4023,34 +4023,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="F54" t="n">
-        <v>1556817159</v>
+        <v>1532378165</v>
       </c>
       <c r="G54" t="n">
         <v>53</v>
       </c>
       <c r="H54" t="n">
-        <v>46260797</v>
+        <v>35111368</v>
       </c>
       <c r="I54" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="J54" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K54" t="n">
-        <v>0.052938</v>
+        <v>-0.05095835614630051</v>
       </c>
       <c r="L54" t="n">
-        <v>1.92892</v>
+        <v>-1.94273</v>
       </c>
       <c r="M54" t="n">
-        <v>556272745.1443182</v>
+        <v>556276725.9312513</v>
       </c>
       <c r="N54" t="n">
-        <v>556273142.5125661</v>
+        <v>556276747.3933151</v>
       </c>
       <c r="O54" t="n">
         <v>700.65</v>
@@ -4059,689 +4059,689 @@
         <v>44326.33741898148</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0006462106892496255</v>
+        <v>0.0006278804281531795</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pump-fun</t>
+          <t>htx-dao</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>htx</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>HTX DAO</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.00369072</v>
+        <v>1.71e-06</v>
       </c>
       <c r="F55" t="n">
-        <v>1531678178</v>
+        <v>1531747172</v>
       </c>
       <c r="G55" t="n">
         <v>54</v>
       </c>
       <c r="H55" t="n">
-        <v>216800001</v>
+        <v>58584790</v>
       </c>
       <c r="I55" t="n">
-        <v>0.00392038</v>
+        <v>1.71e-06</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00356584</v>
+        <v>1.66e-06</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.000189200679835274</v>
+        <v>2.483e-08</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.87641</v>
+        <v>1.41494</v>
       </c>
       <c r="M55" t="n">
-        <v>414503015998.9233</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="N55" t="n">
-        <v>834631199451.8402</v>
+        <v>898232728634017.2</v>
       </c>
       <c r="O55" t="n">
-        <v>0.00881908</v>
+        <v>3.75e-06</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>45914.36296296296</v>
+        <v>45629.67800925926</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0006300915820109626</v>
+        <v>0.0006274739037343216</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>htx-dao</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>htx</t>
+          <t>usdd</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HTX DAO</t>
+          <t>USDD</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.68e-06</v>
+        <v>0.997449</v>
       </c>
       <c r="F56" t="n">
-        <v>1509536401</v>
+        <v>1508480377</v>
       </c>
       <c r="G56" t="n">
         <v>55</v>
       </c>
       <c r="H56" t="n">
-        <v>63687124</v>
+        <v>2306401</v>
       </c>
       <c r="I56" t="n">
-        <v>1.7e-06</v>
+        <v>0.999555</v>
       </c>
       <c r="J56" t="n">
-        <v>1.68e-06</v>
+        <v>0.9954499999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>1.133e-09</v>
+        <v>-0.001296324483550215</v>
       </c>
       <c r="L56" t="n">
-        <v>0.06737</v>
+        <v>-0.10334</v>
       </c>
       <c r="M56" t="n">
-        <v>898232728634017.2</v>
+        <v>1512337957</v>
       </c>
       <c r="N56" t="n">
-        <v>898232728634017.2</v>
+        <v>1514499799</v>
       </c>
       <c r="O56" t="n">
-        <v>3.75e-06</v>
+        <v>1.24</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>45629.67800925926</v>
+        <v>46212.39942129629</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.000615894281097391</v>
+        <v>0.0006124840063565967</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>pump-fun</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>usdd</t>
+          <t>pump</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>USDD</t>
+          <t>Pump.fun</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.998903</v>
+        <v>0.0036227</v>
       </c>
       <c r="F57" t="n">
-        <v>1493031049</v>
+        <v>1501077364</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>7558824</v>
+        <v>174508980</v>
       </c>
       <c r="I57" t="n">
-        <v>0.999358</v>
+        <v>0.00387035</v>
       </c>
       <c r="J57" t="n">
-        <v>0.99427</v>
+        <v>0.00351746</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.000164509772873078</v>
+        <v>-0.000112795186921209</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.01647</v>
+        <v>-3.1487</v>
       </c>
       <c r="M57" t="n">
-        <v>1494666477</v>
+        <v>414353436173.9454</v>
       </c>
       <c r="N57" t="n">
-        <v>1497163797</v>
+        <v>834490255313.1332</v>
       </c>
       <c r="O57" t="n">
-        <v>1.24</v>
+        <v>0.00881908</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>46212.39942129629</v>
+        <v>45914.36296296296</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0006053110542394735</v>
+        <v>0.000607714531009607</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ethena</t>
+          <t>bitway</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>btw</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ethena</t>
+          <t>Bitway</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.147305</v>
+        <v>0.551997</v>
       </c>
       <c r="F58" t="n">
-        <v>1488701361</v>
+        <v>1494887005</v>
       </c>
       <c r="G58" t="n">
         <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>317283224</v>
+        <v>11630739</v>
       </c>
       <c r="I58" t="n">
-        <v>0.150054</v>
+        <v>0.569699</v>
       </c>
       <c r="J58" t="n">
-        <v>0.141387</v>
+        <v>0.495642</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00106833</v>
+        <v>0.04655557</v>
       </c>
       <c r="L58" t="n">
-        <v>0.73055</v>
+        <v>9.010249999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>10095312500</v>
+        <v>2708142280.000001</v>
       </c>
       <c r="N58" t="n">
-        <v>15000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O58" t="n">
-        <v>1.52</v>
+        <v>0.745279</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>45393.21892361111</v>
+        <v>46253.4</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0006025348595646793</v>
+        <v>0.0006037263217980987</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>worldcoin-wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wld</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.408621</v>
+        <v>0.06364</v>
       </c>
       <c r="F59" t="n">
-        <v>1489134201</v>
+        <v>1490714308</v>
       </c>
       <c r="G59" t="n">
         <v>58</v>
       </c>
       <c r="H59" t="n">
-        <v>141293490</v>
+        <v>22718656</v>
       </c>
       <c r="I59" t="n">
-        <v>0.410786</v>
+        <v>0.06393699999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>0.391882</v>
+        <v>0.057814</v>
       </c>
       <c r="K59" t="n">
-        <v>0.00333089</v>
+        <v>0.00425821</v>
       </c>
       <c r="L59" t="n">
-        <v>0.82185</v>
+        <v>7.12569</v>
       </c>
       <c r="M59" t="n">
-        <v>3642314682.371945</v>
+        <v>23424161538.38614</v>
       </c>
       <c r="N59" t="n">
-        <v>10000000000</v>
+        <v>23462665147.36596</v>
       </c>
       <c r="O59" t="n">
-        <v>11.74</v>
+        <v>0.100535</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>45360.67409722223</v>
+        <v>45630.09302083333</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0006028123964456365</v>
+        <v>0.0006010380142843935</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>worldcoin-wld</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>pepe</t>
+          <t>wld</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Pepe</t>
+          <t>Worldcoin</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3.35e-06</v>
+        <v>0.401719</v>
       </c>
       <c r="F60" t="n">
-        <v>1411275814</v>
+        <v>1467776366</v>
       </c>
       <c r="G60" t="n">
         <v>59</v>
       </c>
       <c r="H60" t="n">
-        <v>220807133</v>
+        <v>145431349</v>
       </c>
       <c r="I60" t="n">
-        <v>3.36e-06</v>
+        <v>0.427578</v>
       </c>
       <c r="J60" t="n">
-        <v>3.22e-06</v>
+        <v>0.395299</v>
       </c>
       <c r="K60" t="n">
-        <v>1.121e-08</v>
+        <v>-0.005559293841472135</v>
       </c>
       <c r="L60" t="n">
-        <v>0.33555</v>
+        <v>-1.43875</v>
       </c>
       <c r="M60" t="n">
-        <v>420690000000000</v>
+        <v>3653737094.945146</v>
       </c>
       <c r="N60" t="n">
-        <v>420690000000000</v>
+        <v>10000000000</v>
       </c>
       <c r="O60" t="n">
-        <v>2.803e-05</v>
+        <v>11.74</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>45635.35457175926</v>
+        <v>45360.67409722223</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0005528896215534354</v>
+        <v>0.0005862599841931752</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>ethena</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>usdgo</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>USDGO</t>
+          <t>Ethena</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0.141868</v>
       </c>
       <c r="F61" t="n">
-        <v>1383270977</v>
+        <v>1432198996</v>
       </c>
       <c r="G61" t="n">
         <v>60</v>
       </c>
       <c r="H61" t="n">
-        <v>28018522</v>
+        <v>377246978</v>
       </c>
       <c r="I61" t="n">
+        <v>0.157211</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.138292</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-0.005293080626809415</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-3.8544</v>
+      </c>
+      <c r="M61" t="n">
+        <v>10095312500</v>
+      </c>
+      <c r="N61" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P61" s="1" t="n">
+        <v>45393.21892361111</v>
+      </c>
+      <c r="Q61" s="1" t="n">
+        <v>46277.53078703704</v>
+      </c>
+      <c r="R61" t="b">
         <v>1</v>
       </c>
-      <c r="J61" t="n">
-        <v>0.999893</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0.00012525</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.01252</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1382942040.16</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1382942045.16</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1.002</v>
-      </c>
-      <c r="P61" s="1" t="n">
-        <v>46092.00303240741</v>
-      </c>
-      <c r="Q61" s="1" t="n">
-        <v>46276.55914351852</v>
-      </c>
-      <c r="R61" t="b">
-        <v>0</v>
-      </c>
       <c r="S61" t="n">
-        <v>0.0005349329282887293</v>
+        <v>0.0005633388588181785</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bitget-token</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bgb</t>
+          <t>pepe</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bitget Token</t>
+          <t>Pepe</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.96</v>
+        <v>3.4e-06</v>
       </c>
       <c r="F62" t="n">
-        <v>1374457843</v>
+        <v>1428671176</v>
       </c>
       <c r="G62" t="n">
         <v>61</v>
       </c>
       <c r="H62" t="n">
-        <v>9190660</v>
+        <v>243786948</v>
       </c>
       <c r="I62" t="n">
-        <v>1.97</v>
+        <v>3.55e-06</v>
       </c>
       <c r="J62" t="n">
-        <v>1.93</v>
+        <v>3.25e-06</v>
       </c>
       <c r="K62" t="n">
-        <v>0.02435951</v>
+        <v>5.7378e-08</v>
       </c>
       <c r="L62" t="n">
-        <v>1.25617</v>
+        <v>1.73265</v>
       </c>
       <c r="M62" t="n">
-        <v>699992029.6481038</v>
+        <v>420690000000000</v>
       </c>
       <c r="N62" t="n">
-        <v>910920874.6481038</v>
+        <v>420690000000000</v>
       </c>
       <c r="O62" t="n">
-        <v>8.449999999999999</v>
+        <v>2.803e-05</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>45653.15375</v>
+        <v>45635.35457175926</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0005292819493546704</v>
+        <v>0.0005610660206482851</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>usdgo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sky</t>
+          <t>USDGO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.058158</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1365122165</v>
+        <v>1383105673</v>
       </c>
       <c r="G63" t="n">
         <v>62</v>
       </c>
       <c r="H63" t="n">
-        <v>14829654</v>
+        <v>20105463</v>
       </c>
       <c r="I63" t="n">
-        <v>0.061385</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0.058078</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.000474670622074118</v>
+        <v>3.754e-05</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.80957</v>
+        <v>-0.00259</v>
       </c>
       <c r="M63" t="n">
-        <v>23425278090.46795</v>
+        <v>1382792045.16</v>
       </c>
       <c r="N63" t="n">
-        <v>23462665147.36596</v>
+        <v>1382792045.16</v>
       </c>
       <c r="O63" t="n">
-        <v>0.100535</v>
+        <v>1.002</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>45630.09302083333</v>
+        <v>46092.00303240741</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0005232959153611833</v>
+        <v>0.0005317099269562053</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>bitway</t>
+          <t>bitget-token</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>btw</t>
+          <t>bgb</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bitway</t>
+          <t>Bitget Token</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.499741</v>
+        <v>1.95</v>
       </c>
       <c r="F64" t="n">
-        <v>1352987499</v>
+        <v>1365892496</v>
       </c>
       <c r="G64" t="n">
         <v>63</v>
       </c>
       <c r="H64" t="n">
-        <v>14777585</v>
+        <v>12523335</v>
       </c>
       <c r="I64" t="n">
-        <v>0.516378</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
-        <v>0.451093</v>
+        <v>1.92</v>
       </c>
       <c r="K64" t="n">
-        <v>0.03125239</v>
+        <v>-0.005742599409946703</v>
       </c>
       <c r="L64" t="n">
-        <v>6.6709</v>
+        <v>-0.2626</v>
       </c>
       <c r="M64" t="n">
-        <v>2708142280.000001</v>
+        <v>699992029.6481038</v>
       </c>
       <c r="N64" t="n">
-        <v>10000000000</v>
+        <v>910920874.6481038</v>
       </c>
       <c r="O64" t="n">
-        <v>0.745279</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46253.4</v>
+        <v>45653.15375</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0005155151710836267</v>
+        <v>0.0005206201418450796</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4760,28 +4760,28 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.996268</v>
+        <v>0.996233</v>
       </c>
       <c r="F65" t="n">
-        <v>1339475574</v>
+        <v>1339425000</v>
       </c>
       <c r="G65" t="n">
         <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>410919</v>
+        <v>481917</v>
       </c>
       <c r="I65" t="n">
-        <v>1.002</v>
+        <v>0.997675</v>
       </c>
       <c r="J65" t="n">
-        <v>0.992092</v>
+        <v>0.977391</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.000302944713080122</v>
+        <v>6.295999999999999e-05</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.0304</v>
+        <v>-6e-05</v>
       </c>
       <c r="M65" t="n">
         <v>1344489118.116781</v>
@@ -4796,19 +4796,19 @@
         <v>45785.55951388889</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0005068513287395089</v>
+        <v>0.0005035681564347408</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4830,7 +4830,7 @@
         <v>1.17</v>
       </c>
       <c r="F66" t="n">
-        <v>1332238102</v>
+        <v>1334376241</v>
       </c>
       <c r="G66" t="n">
         <v>65</v>
@@ -4845,16 +4845,16 @@
         <v>1.17</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.7045165355586e-05</v>
+        <v>0.00180267</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.00401</v>
+        <v>0.1537</v>
       </c>
       <c r="M66" t="n">
-        <v>1134566984.99023</v>
+        <v>1135960146.90006</v>
       </c>
       <c r="N66" t="n">
-        <v>1134566984.99023</v>
+        <v>1135960146.90006</v>
       </c>
       <c r="O66" t="n">
         <v>1.18</v>
@@ -4863,19 +4863,19 @@
         <v>46255.48263888889</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0005022106638173779</v>
+        <v>0.000500315436010855</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4894,28 +4894,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.999538</v>
+        <v>0.999646</v>
       </c>
       <c r="F67" t="n">
-        <v>1319394082</v>
+        <v>1319533294</v>
       </c>
       <c r="G67" t="n">
         <v>66</v>
       </c>
       <c r="H67" t="n">
-        <v>4259383</v>
+        <v>1059898</v>
       </c>
       <c r="I67" t="n">
-        <v>0.999725</v>
+        <v>0.999877</v>
       </c>
       <c r="J67" t="n">
-        <v>0.999358</v>
+        <v>0.999486</v>
       </c>
       <c r="K67" t="n">
-        <v>2.154e-05</v>
+        <v>0.00017403</v>
       </c>
       <c r="L67" t="n">
-        <v>0.00216</v>
+        <v>0.01437</v>
       </c>
       <c r="M67" t="n">
         <v>1320000000</v>
@@ -4930,19 +4930,19 @@
         <v>45940.56990740741</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0004939750819632235</v>
+        <v>0.0004907526985425871</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4961,31 +4961,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.999318</v>
+        <v>0.999305</v>
       </c>
       <c r="F68" t="n">
-        <v>1283500273</v>
+        <v>1285106288</v>
       </c>
       <c r="G68" t="n">
         <v>67</v>
       </c>
       <c r="H68" t="n">
-        <v>162320060</v>
+        <v>171246171</v>
       </c>
       <c r="I68" t="n">
-        <v>0.999425</v>
+        <v>0.999557</v>
       </c>
       <c r="J68" t="n">
-        <v>0.99893</v>
+        <v>0.99905</v>
       </c>
       <c r="K68" t="n">
-        <v>4.72e-05</v>
+        <v>0.0002578</v>
       </c>
       <c r="L68" t="n">
-        <v>0.00472</v>
+        <v>0.02343</v>
       </c>
       <c r="M68" t="n">
-        <v>1284500007.8</v>
+        <v>1286000007.8</v>
       </c>
       <c r="N68" t="n">
         <v>1286000007.8</v>
@@ -4997,153 +4997,153 @@
         <v>46058.54591435185</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004709599821676079</v>
+        <v>0.000468572708261918</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>venice-token</t>
+          <t>ethereum-classic</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>vvv</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Venice Token</t>
+          <t>Ethereum Classic</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>26.08</v>
+        <v>7.78</v>
       </c>
       <c r="F69" t="n">
-        <v>1249707775</v>
+        <v>1229960904</v>
       </c>
       <c r="G69" t="n">
         <v>68</v>
       </c>
       <c r="H69" t="n">
-        <v>102651981</v>
+        <v>50428712</v>
       </c>
       <c r="I69" t="n">
-        <v>25.6</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>22.72</v>
+        <v>7.56</v>
       </c>
       <c r="K69" t="n">
-        <v>2.02</v>
+        <v>0.148372</v>
       </c>
       <c r="L69" t="n">
-        <v>8.415760000000001</v>
+        <v>1.65537</v>
       </c>
       <c r="M69" t="n">
-        <v>47928096.04257578</v>
+        <v>158147055.6165969</v>
       </c>
       <c r="N69" t="n">
-        <v>80986596.52104242</v>
+        <v>158147807.8469969</v>
       </c>
       <c r="O69" t="n">
-        <v>29.19</v>
+        <v>167.09</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>46274.32083333333</v>
+        <v>44322.44053240741</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.000449292242368437</v>
+        <v>0.0004330446672483092</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ethereum-classic</t>
+          <t>venice-token</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>vvv</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ethereum Classic</t>
+          <t>Venice Token</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7.71</v>
+        <v>23.26</v>
       </c>
       <c r="F70" t="n">
-        <v>1218614410</v>
+        <v>1115260871</v>
       </c>
       <c r="G70" t="n">
         <v>69</v>
       </c>
       <c r="H70" t="n">
-        <v>52635522</v>
+        <v>64886551</v>
       </c>
       <c r="I70" t="n">
-        <v>7.78</v>
+        <v>26.96</v>
       </c>
       <c r="J70" t="n">
-        <v>7.43</v>
+        <v>22.9</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.003077005696481727</v>
+        <v>-2.111842464813492</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.03991</v>
+        <v>-8.392390000000001</v>
       </c>
       <c r="M70" t="n">
-        <v>158140942.4707831</v>
+        <v>47938677.12722591</v>
       </c>
       <c r="N70" t="n">
-        <v>158141763.9747831</v>
+        <v>80993152.67908402</v>
       </c>
       <c r="O70" t="n">
-        <v>167.09</v>
+        <v>29.19</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>44322.44053240741</v>
+        <v>46274.32083333333</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0.0004293551858566441</v>
+        <v>0.0003591478660820267</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5162,28 +5162,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.66</v>
+        <v>4.38</v>
       </c>
       <c r="F71" t="n">
-        <v>1163955696</v>
+        <v>1094810297</v>
       </c>
       <c r="G71" t="n">
         <v>70</v>
       </c>
       <c r="H71" t="n">
-        <v>96426083</v>
+        <v>75118887</v>
       </c>
       <c r="I71" t="n">
-        <v>4.67</v>
+        <v>4.89</v>
       </c>
       <c r="J71" t="n">
         <v>4.29</v>
       </c>
       <c r="K71" t="n">
-        <v>0.121124</v>
+        <v>-0.2442743405838863</v>
       </c>
       <c r="L71" t="n">
-        <v>2.66667</v>
+        <v>-5.57308</v>
       </c>
       <c r="M71" t="n">
         <v>250000000</v>
@@ -5198,19 +5198,19 @@
         <v>46021.04538194444</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.0003943080344827119</v>
+        <v>0.0003459723511228083</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5229,34 +5229,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.09493699999999999</v>
+        <v>0.09500699999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>1060010138</v>
+        <v>1061823224</v>
       </c>
       <c r="G72" t="n">
         <v>71</v>
       </c>
       <c r="H72" t="n">
-        <v>5562293</v>
+        <v>4189239</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09700499999999999</v>
+        <v>0.096189</v>
       </c>
       <c r="J72" t="n">
-        <v>0.093487</v>
+        <v>0.09408999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.001126560587777992</v>
+        <v>0.00025705</v>
       </c>
       <c r="L72" t="n">
-        <v>-1.17272</v>
+        <v>0.2691</v>
       </c>
       <c r="M72" t="n">
-        <v>11162267022.98023</v>
+        <v>11176267335.13786</v>
       </c>
       <c r="N72" t="n">
-        <v>17172718496.89267</v>
+        <v>17193106891.0133</v>
       </c>
       <c r="O72" t="n">
         <v>2.99</v>
@@ -5265,19 +5265,19 @@
         <v>45714.36184027778</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0.000327658173202151</v>
+        <v>0.0003247200540590521</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5296,34 +5296,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.09686599999999999</v>
+        <v>0.09667100000000001</v>
       </c>
       <c r="F73" t="n">
-        <v>1038022867</v>
+        <v>1035629322</v>
       </c>
       <c r="G73" t="n">
         <v>72</v>
       </c>
       <c r="H73" t="n">
-        <v>79635826</v>
+        <v>76591456</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09592199999999999</v>
+        <v>0.098053</v>
       </c>
       <c r="J73" t="n">
-        <v>0.091382</v>
+        <v>0.09514599999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>0.00588087</v>
+        <v>0.00135837</v>
       </c>
       <c r="L73" t="n">
-        <v>6.46357</v>
+        <v>1.30768</v>
       </c>
       <c r="M73" t="n">
-        <v>10712360273.58979</v>
+        <v>10712941475.32286</v>
       </c>
       <c r="N73" t="n">
-        <v>10712360273.58979</v>
+        <v>10712941475.32286</v>
       </c>
       <c r="O73" t="n">
         <v>1.29</v>
@@ -5332,153 +5332,153 @@
         <v>45364.45493055556</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003135599414904304</v>
+        <v>0.0003078443346958058</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>kaspa</t>
+          <t>gatechain-token</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kas</t>
+          <t>gt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kaspa</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.03595403</v>
+        <v>9.43</v>
       </c>
       <c r="F74" t="n">
-        <v>994734819</v>
+        <v>1005188774</v>
       </c>
       <c r="G74" t="n">
         <v>73</v>
       </c>
       <c r="H74" t="n">
-        <v>21428726</v>
+        <v>3280701</v>
       </c>
       <c r="I74" t="n">
-        <v>0.03822965</v>
+        <v>9.5</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03396212</v>
+        <v>9.17</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.001802680228815516</v>
+        <v>0.343488</v>
       </c>
       <c r="L74" t="n">
-        <v>-4.77446</v>
+        <v>3.68606</v>
       </c>
       <c r="M74" t="n">
-        <v>27693237714.84791</v>
+        <v>106625412.8293429</v>
       </c>
       <c r="N74" t="n">
-        <v>27694208549.70138</v>
+        <v>118876736.8495598</v>
       </c>
       <c r="O74" t="n">
-        <v>0.207411</v>
+        <v>25.38</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>45504.69498842592</v>
+        <v>45682.66666666666</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.0002858036578182964</v>
+        <v>0.0002882326653343098</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gatechain-token</t>
+          <t>kaspa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>gt</t>
+          <t>kas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Kaspa</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>9.210000000000001</v>
+        <v>0.03560476</v>
       </c>
       <c r="F75" t="n">
-        <v>981524179</v>
+        <v>986010979</v>
       </c>
       <c r="G75" t="n">
         <v>74</v>
       </c>
       <c r="H75" t="n">
-        <v>5271661</v>
+        <v>11878093</v>
       </c>
       <c r="I75" t="n">
-        <v>9.51</v>
+        <v>0.03674793</v>
       </c>
       <c r="J75" t="n">
-        <v>9.029999999999999</v>
+        <v>0.0352174</v>
       </c>
       <c r="K75" t="n">
-        <v>0.241067</v>
+        <v>0.00048354</v>
       </c>
       <c r="L75" t="n">
-        <v>2.68682</v>
+        <v>1.14891</v>
       </c>
       <c r="M75" t="n">
-        <v>106624324.9792634</v>
+        <v>27693237714.84791</v>
       </c>
       <c r="N75" t="n">
-        <v>118875580.2820878</v>
+        <v>27696019387.569</v>
       </c>
       <c r="O75" t="n">
-        <v>25.38</v>
+        <v>0.207411</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>45682.66666666666</v>
+        <v>45504.69498842592</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.0002773329993277486</v>
+        <v>0.0002758771527258459</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5533,153 +5533,153 @@
         <v>46273.93067129629</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0002701672854730611</v>
+        <v>0.0002657865512952967</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>kucoin-shares</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kcs</t>
+          <t>arb</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KuCoin</t>
+          <t>Arbitrum</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>7.01</v>
+        <v>0.144492</v>
       </c>
       <c r="F77" t="n">
-        <v>961459699</v>
+        <v>964925627</v>
       </c>
       <c r="G77" t="n">
         <v>76</v>
       </c>
       <c r="H77" t="n">
-        <v>2770787</v>
+        <v>176225601</v>
       </c>
       <c r="I77" t="n">
-        <v>7.05</v>
+        <v>0.151528</v>
       </c>
       <c r="J77" t="n">
-        <v>6.83</v>
+        <v>0.137756</v>
       </c>
       <c r="K77" t="n">
-        <v>0.155616</v>
+        <v>0.00125256</v>
       </c>
       <c r="L77" t="n">
-        <v>2.27035</v>
+        <v>0.5424600000000001</v>
       </c>
       <c r="M77" t="n">
-        <v>137155021.2773955</v>
+        <v>6678075931</v>
       </c>
       <c r="N77" t="n">
-        <v>142155021.2773955</v>
+        <v>10000000000</v>
       </c>
       <c r="O77" t="n">
-        <v>28.83</v>
+        <v>2.39</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>44531.29832175926</v>
+        <v>45303.18748842592</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.0002644676606408699</v>
+        <v>0.0002622926748184588</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>kucoin-shares</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>arb</t>
+          <t>kcs</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Arbitrum</t>
+          <t>KuCoin</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.143521</v>
+        <v>6.9</v>
       </c>
       <c r="F78" t="n">
-        <v>958743093</v>
+        <v>946493499</v>
       </c>
       <c r="G78" t="n">
         <v>77</v>
       </c>
       <c r="H78" t="n">
-        <v>202835706</v>
+        <v>2806743</v>
       </c>
       <c r="I78" t="n">
-        <v>0.153242</v>
+        <v>7.2</v>
       </c>
       <c r="J78" t="n">
-        <v>0.138315</v>
+        <v>6.88</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00476547542386474</v>
+        <v>-0.06895540986525894</v>
       </c>
       <c r="L78" t="n">
-        <v>-3.2137</v>
+        <v>-0.99277</v>
       </c>
       <c r="M78" t="n">
-        <v>6678075931</v>
+        <v>137155021.2773955</v>
       </c>
       <c r="N78" t="n">
-        <v>10000000000</v>
+        <v>142155021.2773955</v>
       </c>
       <c r="O78" t="n">
-        <v>2.39</v>
+        <v>28.83</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>45303.18748842592</v>
+        <v>44531.29832175926</v>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0.0002627257736710204</v>
+        <v>0.0002504175666579627</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5698,28 +5698,28 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>64.81999999999999</v>
+        <v>64.47</v>
       </c>
       <c r="F79" t="n">
-        <v>942825988</v>
+        <v>937680591</v>
       </c>
       <c r="G79" t="n">
         <v>78</v>
       </c>
       <c r="H79" t="n">
-        <v>9224706</v>
+        <v>10154754</v>
       </c>
       <c r="I79" t="n">
-        <v>66.38</v>
+        <v>65.94</v>
       </c>
       <c r="J79" t="n">
-        <v>63.82</v>
+        <v>62.82</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.27550565831352</v>
+        <v>-0.4152476391461448</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.42321</v>
+        <v>-0.56288</v>
       </c>
       <c r="M79" t="n">
         <v>14544176.16408117</v>
@@ -5734,86 +5734,86 @@
         <v>44450.05208333334</v>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>0.0002525197306168465</v>
+        <v>0.0002447397504172931</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>cosmos</t>
+          <t>just</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>jst</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cosmos Hub</t>
+          <t>JUST</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.73</v>
+        <v>0.108937</v>
       </c>
       <c r="F80" t="n">
-        <v>916337794</v>
+        <v>892054189</v>
       </c>
       <c r="G80" t="n">
         <v>79</v>
       </c>
       <c r="H80" t="n">
-        <v>54228029</v>
+        <v>31577160</v>
       </c>
       <c r="I80" t="n">
-        <v>1.82</v>
+        <v>0.108792</v>
       </c>
       <c r="J80" t="n">
-        <v>1.7</v>
+        <v>0.102155</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.0601896227796066</v>
+        <v>0.00589916</v>
       </c>
       <c r="L80" t="n">
-        <v>-3.3649</v>
+        <v>5.79298</v>
       </c>
       <c r="M80" t="n">
-        <v>530093191.963316</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="N80" t="n">
-        <v>530111563.170892</v>
+        <v>8188743036.341737</v>
       </c>
       <c r="O80" t="n">
-        <v>43.84</v>
+        <v>0.193254</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>44458.66666666666</v>
+        <v>44290.85721064815</v>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" t="n">
-        <v>0.0002355355083985909</v>
+        <v>0.0002153444218516346</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5835,7 +5835,7 @@
         <v>1.23</v>
       </c>
       <c r="F81" t="n">
-        <v>880185352</v>
+        <v>880446339</v>
       </c>
       <c r="G81" t="n">
         <v>80</v>
@@ -5850,10 +5850,10 @@
         <v>1.23</v>
       </c>
       <c r="K81" t="n">
-        <v>-8.1966592208715e-05</v>
+        <v>0.00178684</v>
       </c>
       <c r="L81" t="n">
-        <v>-0.00667</v>
+        <v>0.14569</v>
       </c>
       <c r="M81" t="n">
         <v>716808406.83022</v>
@@ -5868,220 +5868,220 @@
         <v>46049.54175925926</v>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.0002123545731992866</v>
+        <v>0.000207865932430293</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>just</t>
+          <t>cosmos</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jst</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>Cosmos Hub</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.102603</v>
+        <v>1.64</v>
       </c>
       <c r="F82" t="n">
-        <v>840199045</v>
+        <v>870384550</v>
       </c>
       <c r="G82" t="n">
         <v>81</v>
       </c>
       <c r="H82" t="n">
-        <v>19464978</v>
+        <v>48583957</v>
       </c>
       <c r="I82" t="n">
-        <v>0.104605</v>
+        <v>1.76</v>
       </c>
       <c r="J82" t="n">
-        <v>0.102366</v>
+        <v>1.62</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.001171828866008306</v>
+        <v>-0.09507162704493877</v>
       </c>
       <c r="L82" t="n">
-        <v>-1.1292</v>
+        <v>-5.56627</v>
       </c>
       <c r="M82" t="n">
-        <v>8188743036.341737</v>
+        <v>530269185.354314</v>
       </c>
       <c r="N82" t="n">
-        <v>8188743036.341737</v>
+        <v>530292014.176179</v>
       </c>
       <c r="O82" t="n">
-        <v>0.193254</v>
+        <v>43.84</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>44290.85721064815</v>
+        <v>44458.66666666666</v>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" t="n">
-        <v>0.0001867153648872593</v>
+        <v>0.0002013835103972489</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>algorand</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>nexo</t>
+          <t>algo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NEXO</t>
+          <t>Algorand</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.832133</v>
+        <v>0.09302299999999999</v>
       </c>
       <c r="F83" t="n">
-        <v>832126414</v>
+        <v>840932378</v>
       </c>
       <c r="G83" t="n">
         <v>82</v>
       </c>
       <c r="H83" t="n">
-        <v>3345268</v>
+        <v>41412012</v>
       </c>
       <c r="I83" t="n">
-        <v>0.846696</v>
+        <v>0.094961</v>
       </c>
       <c r="J83" t="n">
-        <v>0.820491</v>
+        <v>0.090361</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.004223176933168871</v>
+        <v>0.00234688</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.50495</v>
+        <v>2.41763</v>
       </c>
       <c r="M83" t="n">
-        <v>1000000000</v>
+        <v>9040075710.158276</v>
       </c>
       <c r="N83" t="n">
-        <v>1000000000</v>
+        <v>9040413275.136045</v>
       </c>
       <c r="O83" t="n">
-        <v>4.07</v>
+        <v>3.56</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>44328.27623842593</v>
+        <v>43636.28563657407</v>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.0001815391962594555</v>
+        <v>0.0001824086135181944</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>algorand</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>algo</t>
+          <t>nexo</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Algorand</t>
+          <t>NEXO</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.09136900000000001</v>
+        <v>0.834313</v>
       </c>
       <c r="F84" t="n">
-        <v>826564762</v>
+        <v>834313461</v>
       </c>
       <c r="G84" t="n">
         <v>83</v>
       </c>
       <c r="H84" t="n">
-        <v>44325049</v>
+        <v>3488275</v>
       </c>
       <c r="I84" t="n">
-        <v>0.098091</v>
+        <v>0.846082</v>
       </c>
       <c r="J84" t="n">
-        <v>0.08820699999999999</v>
+        <v>0.825558</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.005872704953126001</v>
+        <v>0.007850930000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>-6.03931</v>
+        <v>0.8590100000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>9040075710.158276</v>
+        <v>1000000000</v>
       </c>
       <c r="N84" t="n">
-        <v>9040214132.26104</v>
+        <v>1000000000</v>
       </c>
       <c r="O84" t="n">
-        <v>3.56</v>
+        <v>4.07</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>43636.28563657407</v>
+        <v>44328.27623842593</v>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.0001779730666294548</v>
+        <v>0.0001781443009396171</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6100,34 +6100,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.242788</v>
+        <v>0.247551</v>
       </c>
       <c r="F85" t="n">
-        <v>805923333</v>
+        <v>821702438</v>
       </c>
       <c r="G85" t="n">
         <v>84</v>
       </c>
       <c r="H85" t="n">
-        <v>92695382</v>
+        <v>103867053</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2431</v>
+        <v>0.256569</v>
       </c>
       <c r="J85" t="n">
-        <v>0.22017</v>
+        <v>0.23951</v>
       </c>
       <c r="K85" t="n">
-        <v>0.01816376</v>
+        <v>0.008722809999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>8.0863</v>
+        <v>2.85164</v>
       </c>
       <c r="M85" t="n">
         <v>3319369204.37</v>
       </c>
       <c r="N85" t="n">
-        <v>6861487243.558427</v>
+        <v>6861487227.770792</v>
       </c>
       <c r="O85" t="n">
         <v>2</v>
@@ -6136,19 +6136,19 @@
         <v>45322.29359953704</v>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.0001647377884131164</v>
+        <v>0.0001700195059002433</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6170,7 +6170,7 @@
         <v>11.21</v>
       </c>
       <c r="F86" t="n">
-        <v>806196290</v>
+        <v>805069396</v>
       </c>
       <c r="G86" t="n">
         <v>85</v>
@@ -6191,567 +6191,567 @@
         <v>0.00979</v>
       </c>
       <c r="M86" t="n">
-        <v>71929405.877505</v>
+        <v>71828863.654614</v>
       </c>
       <c r="N86" t="n">
-        <v>71806917.885897</v>
+        <v>71828863.654614</v>
       </c>
       <c r="O86" t="n">
         <v>11.21</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46276.55543981482</v>
+        <v>46276.59027777778</v>
       </c>
       <c r="Q86" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0001649128083614008</v>
+        <v>0.0001593034793628802</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>stable-2</t>
+          <t>ether-fi</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>ethfi</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>​​Stable</t>
+          <t>Ether.fi</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.02873046</v>
+        <v>0.7649010000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>754085357</v>
+        <v>738397322</v>
       </c>
       <c r="G87" t="n">
         <v>86</v>
       </c>
       <c r="H87" t="n">
-        <v>10760536</v>
+        <v>154766747</v>
       </c>
       <c r="I87" t="n">
-        <v>0.03046497</v>
+        <v>0.774993</v>
       </c>
       <c r="J87" t="n">
-        <v>0.02650292</v>
+        <v>0.63907</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.000759855443758024</v>
+        <v>0.127353</v>
       </c>
       <c r="L87" t="n">
-        <v>-2.57663</v>
+        <v>19.69859</v>
       </c>
       <c r="M87" t="n">
-        <v>26223510631</v>
+        <v>965350000</v>
       </c>
       <c r="N87" t="n">
-        <v>100000000000</v>
+        <v>965350000</v>
       </c>
       <c r="O87" t="n">
-        <v>0.04323745</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46156.97986111111</v>
+        <v>45378.63525462963</v>
       </c>
       <c r="Q87" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>0.0001314992934168699</v>
+        <v>0.0001163492371812613</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-treasury-fund</t>
+          <t>stable-2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jtrsy</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund</t>
+          <t>​​Stable</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.12</v>
+        <v>0.02772471</v>
       </c>
       <c r="F88" t="n">
-        <v>750073481</v>
+        <v>727843516</v>
       </c>
       <c r="G88" t="n">
         <v>87</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>9957228</v>
       </c>
       <c r="I88" t="n">
-        <v>1.12</v>
+        <v>0.0291463</v>
       </c>
       <c r="J88" t="n">
-        <v>1.12</v>
+        <v>0.02702663</v>
       </c>
       <c r="K88" t="n">
-        <v>3.1e-05</v>
+        <v>0.0007886</v>
       </c>
       <c r="L88" t="n">
-        <v>0.00278</v>
+        <v>2.55751</v>
       </c>
       <c r="M88" t="n">
-        <v>672308860.001803</v>
+        <v>26252515775</v>
       </c>
       <c r="N88" t="n">
-        <v>672308860.001803</v>
+        <v>100000000000</v>
       </c>
       <c r="O88" t="n">
-        <v>1.12</v>
+        <v>0.04323745</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46276.55543981482</v>
+        <v>46156.97986111111</v>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0001289268797031948</v>
+        <v>0.0001095498275984453</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>render-token</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dash</t>
+          <t>render</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>57.03</v>
+        <v>1.4</v>
       </c>
       <c r="F89" t="n">
-        <v>731971802</v>
+        <v>727013232</v>
       </c>
       <c r="G89" t="n">
         <v>88</v>
       </c>
       <c r="H89" t="n">
-        <v>133468774</v>
+        <v>38956531</v>
       </c>
       <c r="I89" t="n">
-        <v>57.28</v>
+        <v>1.46</v>
       </c>
       <c r="J89" t="n">
-        <v>53.95</v>
+        <v>1.37</v>
       </c>
       <c r="K89" t="n">
-        <v>0.618684</v>
+        <v>0.00484286</v>
       </c>
       <c r="L89" t="n">
-        <v>1.09679</v>
+        <v>0.28892</v>
       </c>
       <c r="M89" t="n">
-        <v>12824705.2497973</v>
+        <v>518776241.2826915</v>
       </c>
       <c r="N89" t="n">
-        <v>12825258.12914009</v>
+        <v>533536414.5626915</v>
       </c>
       <c r="O89" t="n">
-        <v>1493.59</v>
+        <v>13.53</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>43088.66666666666</v>
+        <v>45368.35444444444</v>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0.0001173200884414149</v>
+        <v>0.0001090149076855666</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>render-token</t>
+          <t>janus-henderson-anemoy-treasury-fund</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>render</t>
+          <t>jtrsy</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Janus Henderson Anemoy Treasury Fund</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="F90" t="n">
-        <v>731771096</v>
+        <v>725070974</v>
       </c>
       <c r="G90" t="n">
         <v>89</v>
       </c>
       <c r="H90" t="n">
-        <v>45758488</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="J90" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="K90" t="n">
-        <v>0.00881273</v>
+        <v>3.1e-05</v>
       </c>
       <c r="L90" t="n">
-        <v>0.62924</v>
+        <v>0.00278</v>
       </c>
       <c r="M90" t="n">
-        <v>518776241.2826915</v>
+        <v>649898513.025921</v>
       </c>
       <c r="N90" t="n">
-        <v>533536414.5626915</v>
+        <v>649898513.025921</v>
       </c>
       <c r="O90" t="n">
-        <v>13.53</v>
+        <v>1.12</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>45368.35444444444</v>
+        <v>46276.55543981482</v>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0.0001171913958131241</v>
+        <v>0.000107763585872611</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>janus-henderson-anemoy-aaa-clo-fund</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jaaa</t>
+          <t>dash</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy AAA CLO Fund</t>
+          <t>Dash</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.049</v>
+        <v>56.46</v>
       </c>
       <c r="F91" t="n">
-        <v>713088227</v>
+        <v>724189441</v>
       </c>
       <c r="G91" t="n">
         <v>90</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>117062460</v>
       </c>
       <c r="I91" t="n">
-        <v>1.049</v>
+        <v>59.25</v>
       </c>
       <c r="J91" t="n">
-        <v>1.049</v>
+        <v>55.31</v>
       </c>
       <c r="K91" t="n">
-        <v>0.000132</v>
+        <v>-0.2610257403269927</v>
       </c>
       <c r="L91" t="n">
-        <v>0.01259</v>
+        <v>-0.49723</v>
       </c>
       <c r="M91" t="n">
-        <v>679791365.723425</v>
+        <v>12825646.1579011</v>
       </c>
       <c r="N91" t="n">
-        <v>679791365.723425</v>
+        <v>12825952.24479751</v>
       </c>
       <c r="O91" t="n">
-        <v>1.049</v>
+        <v>1493.59</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>46275.59733796296</v>
+        <v>43088.66666666666</v>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0.000105211945693929</v>
+        <v>0.0001071956482084386</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>pancakeswap-token</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>gho</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>GHO</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.99869</v>
+        <v>2.24</v>
       </c>
       <c r="F92" t="n">
-        <v>698086092</v>
+        <v>718311097</v>
       </c>
       <c r="G92" t="n">
         <v>91</v>
       </c>
       <c r="H92" t="n">
-        <v>3715987</v>
+        <v>68699327</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9987239999999999</v>
+        <v>2.27</v>
       </c>
       <c r="J92" t="n">
-        <v>0.998057</v>
+        <v>2.16</v>
       </c>
       <c r="K92" t="n">
-        <v>0.00016817</v>
+        <v>0.07718800000000001</v>
       </c>
       <c r="L92" t="n">
-        <v>0.01684</v>
+        <v>3.40602</v>
       </c>
       <c r="M92" t="n">
-        <v>699000000</v>
+        <v>320188615.5306796</v>
       </c>
       <c r="N92" t="n">
-        <v>699000000</v>
+        <v>331857365.0223532</v>
       </c>
       <c r="O92" t="n">
-        <v>1.03</v>
+        <v>43.96</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>45350.38608796296</v>
+        <v>44316.08914351852</v>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>9.559258113520257e-05</v>
+        <v>0.0001034084582103764</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>pancakeswap-token</t>
+          <t>janus-henderson-anemoy-aaa-clo-fund</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>cake</t>
+          <t>jaaa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Janus Henderson Anemoy AAA CLO Fund</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2.17</v>
+        <v>1.049</v>
       </c>
       <c r="F93" t="n">
-        <v>696423755</v>
+        <v>713695634</v>
       </c>
       <c r="G93" t="n">
         <v>92</v>
       </c>
       <c r="H93" t="n">
-        <v>63350640</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>2.18</v>
+        <v>1.049</v>
       </c>
       <c r="J93" t="n">
-        <v>2.07</v>
+        <v>1.049</v>
       </c>
       <c r="K93" t="n">
-        <v>0.077262</v>
+        <v>0.000158</v>
       </c>
       <c r="L93" t="n">
-        <v>3.68482</v>
+        <v>0.01506</v>
       </c>
       <c r="M93" t="n">
-        <v>320188212.4569827</v>
+        <v>680267946.936126</v>
       </c>
       <c r="N93" t="n">
-        <v>331857365.0223532</v>
+        <v>680267946.936126</v>
       </c>
       <c r="O93" t="n">
-        <v>43.96</v>
+        <v>1.049</v>
       </c>
       <c r="P93" s="1" t="n">
-        <v>44316.08914351852</v>
+        <v>46276.84375</v>
       </c>
       <c r="Q93" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>9.452669113871476e-05</v>
+        <v>0.0001004348936639622</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>filecoin</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>fil</t>
+          <t>gho</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>GHO</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.793442</v>
+        <v>0.998669</v>
       </c>
       <c r="F94" t="n">
-        <v>656647980</v>
+        <v>698069272</v>
       </c>
       <c r="G94" t="n">
         <v>93</v>
       </c>
       <c r="H94" t="n">
-        <v>76206740</v>
+        <v>7357160</v>
       </c>
       <c r="I94" t="n">
-        <v>0.806818</v>
+        <v>0.998995</v>
       </c>
       <c r="J94" t="n">
-        <v>0.773916</v>
+        <v>0.998175</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.008356446045602484</v>
+        <v>7.726e-05</v>
       </c>
       <c r="L94" t="n">
-        <v>-1.04221</v>
+        <v>0.00617</v>
       </c>
       <c r="M94" t="n">
-        <v>827606294</v>
+        <v>699000000</v>
       </c>
       <c r="N94" t="n">
-        <v>1957066751</v>
+        <v>699000000</v>
       </c>
       <c r="O94" t="n">
-        <v>236.84</v>
+        <v>1.03</v>
       </c>
       <c r="P94" s="1" t="n">
-        <v>44287.22894675926</v>
+        <v>45350.38608796296</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>6.902247588329421e-05</v>
+        <v>9.036743216927938e-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6770,28 +6770,28 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.00734403</v>
+        <v>0.00785427</v>
       </c>
       <c r="F95" t="n">
-        <v>631506549</v>
+        <v>675349478</v>
       </c>
       <c r="G95" t="n">
         <v>94</v>
       </c>
       <c r="H95" t="n">
-        <v>23069119</v>
+        <v>13302986</v>
       </c>
       <c r="I95" t="n">
-        <v>0.00841606</v>
+        <v>0.007819039999999999</v>
       </c>
       <c r="J95" t="n">
-        <v>0.00719802</v>
+        <v>0.00723474</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.000528154914175558</v>
+        <v>0.00046606</v>
       </c>
       <c r="L95" t="n">
-        <v>-6.70913</v>
+        <v>6.25405</v>
       </c>
       <c r="M95" t="n">
         <v>85985041177</v>
@@ -6806,86 +6806,86 @@
         <v>44304.71413194444</v>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>5.29017977053504e-05</v>
+        <v>7.572994640886207e-05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ether-fi</t>
+          <t>filecoin</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ethfi</t>
+          <t>fil</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ether.fi</t>
+          <t>Filecoin</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.642814</v>
+        <v>0.813648</v>
       </c>
       <c r="F96" t="n">
-        <v>620793377</v>
+        <v>673437387</v>
       </c>
       <c r="G96" t="n">
         <v>95</v>
       </c>
       <c r="H96" t="n">
-        <v>168575735</v>
+        <v>76557335</v>
       </c>
       <c r="I96" t="n">
-        <v>0.720922</v>
+        <v>0.825543</v>
       </c>
       <c r="J96" t="n">
-        <v>0.613161</v>
+        <v>0.775082</v>
       </c>
       <c r="K96" t="n">
-        <v>0.01528787</v>
+        <v>0.01862285</v>
       </c>
       <c r="L96" t="n">
-        <v>2.43621</v>
+        <v>2.18164</v>
       </c>
       <c r="M96" t="n">
-        <v>965350000</v>
+        <v>827677063</v>
       </c>
       <c r="N96" t="n">
-        <v>965350000</v>
+        <v>1957060739</v>
       </c>
       <c r="O96" t="n">
-        <v>8.529999999999999</v>
+        <v>236.84</v>
       </c>
       <c r="P96" s="1" t="n">
-        <v>45378.63525462963</v>
+        <v>44287.22894675926</v>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>4.603251496337129e-05</v>
+        <v>7.449806002885693e-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6904,34 +6904,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.077068</v>
+        <v>0.076846</v>
       </c>
       <c r="F97" t="n">
-        <v>606389450</v>
+        <v>604829349</v>
       </c>
       <c r="G97" t="n">
         <v>96</v>
       </c>
       <c r="H97" t="n">
-        <v>10575322</v>
+        <v>11285459</v>
       </c>
       <c r="I97" t="n">
-        <v>0.077185</v>
+        <v>0.07735300000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>0.07657</v>
+        <v>0.076713</v>
       </c>
       <c r="K97" t="n">
-        <v>0.00024138</v>
+        <v>-0.000132520480209841</v>
       </c>
       <c r="L97" t="n">
-        <v>0.31419</v>
+        <v>-0.19458</v>
       </c>
       <c r="M97" t="n">
-        <v>7870613218.707415</v>
+        <v>7870620289.70434</v>
       </c>
       <c r="N97" t="n">
-        <v>9939553386.621778</v>
+        <v>9939560336.1777</v>
       </c>
       <c r="O97" t="n">
         <v>0.450785</v>
@@ -6940,19 +6940,19 @@
         <v>43450.66666666666</v>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>3.679672119866491e-05</v>
+        <v>3.029655101538742e-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6971,28 +6971,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.93</v>
+        <v>5.95</v>
       </c>
       <c r="F98" t="n">
-        <v>594252980</v>
+        <v>595309141</v>
       </c>
       <c r="G98" t="n">
         <v>97</v>
       </c>
       <c r="H98" t="n">
-        <v>87829225</v>
+        <v>85558506</v>
       </c>
       <c r="I98" t="n">
-        <v>6.04</v>
+        <v>6.12</v>
       </c>
       <c r="J98" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0017728</v>
+        <v>0.04170575</v>
       </c>
       <c r="L98" t="n">
-        <v>0.02989</v>
+        <v>0.50802</v>
       </c>
       <c r="M98" t="n">
         <v>100000000</v>
@@ -7007,19 +7007,19 @@
         <v>45365.29608796296</v>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.90148201968377e-05</v>
+        <v>2.416304870298921e-05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7038,31 +7038,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.578779</v>
+        <v>0.578739</v>
       </c>
       <c r="F99" t="n">
-        <v>573351093</v>
+        <v>572272862</v>
       </c>
       <c r="G99" t="n">
         <v>98</v>
       </c>
       <c r="H99" t="n">
-        <v>34408838</v>
+        <v>60416766</v>
       </c>
       <c r="I99" t="n">
-        <v>0.57278</v>
+        <v>0.615443</v>
       </c>
       <c r="J99" t="n">
-        <v>0.539678</v>
+        <v>0.564084</v>
       </c>
       <c r="K99" t="n">
-        <v>0.03371139</v>
+        <v>0.01491191</v>
       </c>
       <c r="L99" t="n">
-        <v>6.18481</v>
+        <v>2.46761</v>
       </c>
       <c r="M99" t="n">
-        <v>988997908.4629087</v>
+        <v>988827052.1381764</v>
       </c>
       <c r="N99" t="n">
         <v>1978450301.483024</v>
@@ -7074,19 +7074,19 @@
         <v>45633.25043981482</v>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>1.561253638734621e-05</v>
+        <v>9.321663880772048e-06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7105,28 +7105,28 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.02806316</v>
+        <v>0.02802343</v>
       </c>
       <c r="F100" t="n">
-        <v>560440294</v>
+        <v>558974589</v>
       </c>
       <c r="G100" t="n">
         <v>99</v>
       </c>
       <c r="H100" t="n">
-        <v>6560353</v>
+        <v>6328854</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02856101</v>
+        <v>0.02852745</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02772397</v>
+        <v>0.02781623</v>
       </c>
       <c r="K100" t="n">
-        <v>-5.306641111116e-05</v>
+        <v>0.0002222</v>
       </c>
       <c r="L100" t="n">
-        <v>-0.18874</v>
+        <v>0.53825</v>
       </c>
       <c r="M100" t="n">
         <v>19946688440</v>
@@ -7141,74 +7141,74 @@
         <v>44428.86097222222</v>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>7.334135857992144e-06</v>
+        <v>7.541002102721244e-07</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260911T132734Z-a714b0</t>
+          <t>20260912T124740Z-cfa561</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>official-trump</t>
+          <t>flare-networks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>trump</t>
+          <t>flr</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Official Trump</t>
+          <t>Flare</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2.01</v>
+        <v>0.00641703</v>
       </c>
       <c r="F101" t="n">
-        <v>549002148</v>
+        <v>557804101</v>
       </c>
       <c r="G101" t="n">
         <v>100</v>
       </c>
       <c r="H101" t="n">
-        <v>177214327</v>
+        <v>1789194</v>
       </c>
       <c r="I101" t="n">
-        <v>2.02</v>
+        <v>0.00645471</v>
       </c>
       <c r="J101" t="n">
-        <v>1.91</v>
+        <v>0.00628271</v>
       </c>
       <c r="K101" t="n">
-        <v>0.04460472</v>
+        <v>9.946999999999999e-05</v>
       </c>
       <c r="L101" t="n">
-        <v>2.27177</v>
+        <v>1.54403</v>
       </c>
       <c r="M101" t="n">
-        <v>273137120.287634</v>
+        <v>86925636898.98215</v>
       </c>
       <c r="N101" t="n">
-        <v>1000000000</v>
+        <v>106531758480.7972</v>
       </c>
       <c r="O101" t="n">
-        <v>73.43000000000001</v>
+        <v>0.150073</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>45676.16011574074</v>
+        <v>44935.80144675926</v>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>46276.55914351852</v>
+        <v>46277.53078703704</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>
